--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,6 +511,948 @@
         <is>
           <t>candidate_rank</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>אביטל יונה רפפורט</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>avitalsr@tlvmc.gov.il</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/skornik-rapaport-avital/</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ר האישי AI צ'אט ד''ר אביטל סקורניק-רפפורט רופאה בכירה, המחלקה לרפואת האם והעובר, מנהלת המרפאה להריון בסיכון גבוה, ביה"ח "ליס" ליולדות ונשים איכילוב צוות איכילוב אביטל סקורניק-רפפורט השכלה 1994-2000 הפקולטה לרפואה ע"ש סאקלר אוניברסיטת תל אביב 2003-2004 לימודי המשך במיילדות וגיניקולוגיה בי"ס לרפואה אוניברסיטת ת"א. מומחיות מוכרת מומחית למיילדות וגינקולוגיה ניסיון קליני 2009 ואילך רופאה עצמאית במכבי שירותי בריאות. 2007 ואילך רופאה בכירה במחלקה לאשפוז טרום לידתי, ביה"ח ליס ליולודת, המרכז הרפואי ת"א. </t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>"אביטל יונה רפפורט" email site:tasmc.org.il</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>hospital_text</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>["https://www.tasmc.org.il/doctorssearch/dr/skornik-rapaport-avital/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/"]</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>איריס שהם</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>irissh@bgu.ac.il</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.bgu.ac.il/ar/people/irissh/</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">يل للجامعة موقع التسجيل شروط القبول للقب الأول معلومات شخصية للذين سجلوا للتعليم إجراءات دفع الرسوم الدراسية الأسئلة المتداولة حول الرسوم الدراسية عمادة شؤون الطلبة خدمات تُقدم لطلبة عمادة شؤون الطلاب قسم الخدمات للطلاب العرب منح دراسية وقروض قسم الخدمات النفسية للطلاب مركز التوجيه المهني أصحاب الوظائف مساعدة في قضايا اكاديمية خدمات مركز الدعم خدمات لطلاب مع إعاقة جسدية دائمة او مؤقتة معهد تشخيص وظائف تعليمية تسهيلات في حال الحمل والولادة ماذا كنت تريد البحث عنه؟ ماذا كنت تريد البحث عنه؟ الصفحة </t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>"איריס שהם" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.bgu.ac.il/people/irissh/", "https://www.bgu.ac.il/ar/people/irissh/", "https://www.yazamut360.bgu.ac.il/?utm_campaign=alongtheyear&amp;utm_medium=BGUwebsite&amp;utm_source=BGUwebsite&amp;utm_term=Botton&amp;utm_content=Botton", "https://www.bgu.ac.il/ar/general/registration-website/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%94%D7%9D-%D7%90%D7%99%D7%A8%D7%99%D7%A1/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>אלי גבע</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>drgeva@baby-ivf.com</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.baby-ivf.com/%D7%A6%D7%A8%D7%95-%D7%A7%D7%A9%D7%A8.html</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ו? לחץ ומשקל יתר: הסיבות לאי פוריות הורמונאליות אצל נשים הבדיקה הגורלית שתקבע את הטיפול באי פיריון אי פיריון: מאחורי כל גבר עומדת בדיקה פשוטה בן או בת? הטכנולוגיה שמזהה לבחור את מין העובר הפריה חוץ גופית: איך מעלים את הסיכוי להיריון? תרומת ביצית: כיצד להבטיח ילד בריא? לידיעת הנשים: מהו הגיל הנכון ביותר להרות? השיטה הרפואית שמאפשרת לנשים לשמר את הפוריות יש קליטה: כיצד להגדיל את הסיכוי להריון מתרומת ביציות? בן או בת? כיצד ניתן להשפיע על בחירת מן היילוד פוריות לטווח ארוך: כל מה שאתן צריכות לדעת על </t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>"אלי גבע" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אלי גבע\" מרפאה פרטית", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75504/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.baby-ivf.com/%D7%A6%D7%A8%D7%95-%D7%A7%D7%A9%D7%A8.html", "http://www.livecity.co.il/", "https://www.baby-ivf.com/About.html", "https://www.baby-ivf.com/Contact.html"]</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>אליזבטה שפריץ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yavne_office@mac.org.il</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=38E289452F7361F0752944377CCFD426FC1721FCE3529AC262E246A6A953B824&amp;RequestId=00000000-0000-0000-0001-000000000635</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>זבטה – נשים - גינקולוגיה יבנה גיבורי החיל 1/26 – איתור שירות | מכבי שירותי בריאות איתור שירות איתור שירות - ראשי רופאים/ות מעבדות, מכונים
+ומטפלים/ות משרדים מוקדי רפואה
+דחופה מרכזי ייעוץ וטיפול יום סדנאות מרכזים רפואיים מכבי פארם ובתי מרקחת מרפאות שיניים רפואה משלימה אופטומטריה דיור מוגן
+ואשפוז סיעודי חזרה לחיפוש הדפסה לאתר מכבי איתור שירות חיפוש רופאים/ות ד"ר שפריץ אליזבטה ד"ר שפריץ אליזבטה נשים - גינקולוגיה מס' רשיון : 1-135429 המתקן ממוגן תקנית וניתן בו שירות בהתאם לשעות הפעילות יש לתאם תור הת</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>"אליזבטה שפריץ" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.doctorita.co.il/experts/98793", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://drtor.co.il/doctor/735", "https://drtor.co.il/cdn-cgi/l/email-protection#a4c7cbcad0c5c7d0e4c0d6d0cbd68ac7cb8acdc8", "https://drtor.co.il/search/koopa/all/city/all/type/all/name/all/page/1", "https://drtor.co.il/doctor/11781", "https://drtor.co.il/doctor/11783", "https://drtor.co.il/cdn-cgi/l/email-protection#7d1e1213091c1e093d190f09120f531e12531411", "https://drtor.co.il/doctor/1", "https://drtor.co.il/doctor/2", "https://drtor.co.il/doctor/3", "https://drtor.co.il/doctor/4", "https://drtor.co.il/doctor/5", "https://drtor.co.il/doctor/6", "https://drtor.co.il/doctor/7", "https://drtor.co.il/doctor/8", "https://drtor.co.il/doctor/9", "https://drtor.co.il/doctor/10", "https://drtor.co.il/cdn-cgi/l/email-protection#ec8f8382988d8f98ac889e98839ec28f83c28580", "https://drtor.co.il/cdn-cgi/l/email-protection#5c3f3332283d3f281c382e28332e723f33723530", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=38E289452F7361F0752944377CCFD426FC1721FCE3529AC262E246A6A953B824&amp;RequestId=00000000-0000-0000-0001-000000000635", "https://www.maccabi4u.co.il/kosher", "https://go.serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%A9%D7%A4%D7%A8%D7%99%D7%A5%20%D7%90%D7%9C%D7%99%D7%96%D7%91%D7%98%D7%94", "https://go.serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=304485097&amp;ProviderProfession=1&amp;docClinic=4023089&amp;Service=1&amp;NewObjectId=70083756&amp;NewObjectType=S&amp;NewPerNr=90017266&amp;ol1=70083756&amp;ol2=S&amp;ol3=90017266&amp;isKosher=1&amp;beginDate=2026-08-31T21:51:34&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1"]</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>אלון טל</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>dralontal@gmail.com</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>95</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://dr-alontal.co.il/</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> בתהליך. קטלוג האתר שירותי העסק בלוג ומאמרים אודות ד״ר אלון טל כירורגיה גינקולוגית ואונקולוגית ד״ר אלון טל מתמחה בכירורגיה גינקולוגית ואונקולוגית ומנהל מרפאה גינקולוגית מתקדמת בחיפה. המרפאה מציעה שירותים מקצועיים בתחום הגינקולוגיה והגינקואונקולוגיה, לרבות ייעוץ גינקולוגי, ניתוחים מתקדמים, מרפאת צוואר הרחם, קולפוסקופיה, היסטרוסקופיות וקוניזציה של צוואר הרחם. המרפאה מספקת מענה רפואי מקיף לנשים מכל רחבי הארץ, בשיתוף פעולה עם קופות החולים מכבי, מאוחדת וכללית וביטוחים פרטיים, תוך הקפדה על איכות הטיפו</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>"אלון טל" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אלון טל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/153548/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://dr-alontal.co.il/", "https://dr-alontal.co.il/about"]</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>אלון קדם</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>doctorkedem@gmail.com</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>95</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.kedemalon.co.il/</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ים לא שגרתיים בכל שאלה ותהיה שהיתה לי וידע תמיד לתת מענה מקצועי ואישי. להריון הראשון נכנסנו לאחר סבב הטיפולים השני ולאחר 9 חודשים נולדה לנו בת מדהימה, לאורך כל ההריון דוקטור קדם ליווה אותנו דרך כל הפחדים והלבטים שכל מי שעבר אינספור נסיונות כושלים וודאי מכיר. לאחר שנתיים, כשהחלטנו שאנחנו מוכנים לעוד 'תוספת' למשפחה, מיד חזרנו לד'ר קדם והפעם הוא הצליח אפילו יותר – ונכנסנו להריון כבר אחרי סבב טיפולים בודד. בתהליך הכל כך קשה ומורכב שעברנו עם אינספור טיפולים וגם הפלות ד'ר קדם היה האדם שהחזיר לנו את הא</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>"אלון קדם" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[{"email": "info@medico.co.il", "confidence": 95, "source_url": "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%A7%D7%93%D7%9D/", "evidence": "כז, השרון חברות ביטוח: פרטי 5.0/5 1 גולשים דירגו מעוניינים לדרג את ד\"ר אלון קדם במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד\"ר אלון קדם רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. שימור פוריות: מתי מומלץ להקפיא ביציות- סטטוסקופ להתייעצות עם ד\"ר אלון קדם השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל", "matched_query": "\"אלון קדם\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.kedemalon.co.il/", "https://www.waze.com/live-map/directions/il/tel-aviv-district/herzliya/ramat-yam-st-4?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.ChIJc2kUjZtIHRURffNez5FjSTo", "https://www.waze.com/live-map/directions/il/tel-aviv-district/%D7%A8%D7%92/shalem-st-3?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.ChIJ48cAeANLHRURhP10NlTZb-k", "https://www.kedemalon.co.il/about", "https://www.kedemalon.co.il/contact", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%A7%D7%93%D7%9D/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%94%D7%A8%D7%A6%D7%9C%D7%99%D7%94/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>אביעד כהן</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>usw@tlvmc.gov.il</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>90</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון </t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>"אביעד כהן" יילוד גינקולוג site:tasmc.org.il</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>hospital_text</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>["https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/"]</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>איתי גת</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>itaigatclinic@gmail.com</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>90</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://prof-itaigat.co.il/</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ני וטיפולים רפואיים מתישים אלא גם בהתמודדות רגשית מורכב ביותר בהיבטים מגוונים -אישי, זוגי, משפחתי וחברתי. הטכנולוגיה הרפואית אמנם מאפשרת השגת הריון ולידה במרבית המקרים אולם לעיתים קרובות מחייבת התמדה וסבלנות וגם יכולות להתמודד עם חוסר הצלחה עד השגת התוצאה המיוחלת. רופא פוריות חייב בעיני להיות בעל שילוב תכונות. נדרשת מקצוענות מהשורה הראשונה, דיוק וקפדנות בפרטי הטיפול תוך התעדכנות שוטפת בחידושים הרפואיים. בנוסף יש צורך לשמור על הפרספקטיבה הרחבה – לראות את מכלול התמונה של שני בני הזוג ונתוניהם הביו</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>"איתי גת" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"איתי גת\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/איתי-גת", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%AA-%D7%90%D7%99%D7%AA%D7%99/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://doctors.assuta.co.il/search/doctor/itai-gat-38246", "https://www.facebook.com/itaigatfertility/", "https://www.infomed.co.il/experts/146101/", "https://prof-itaigat.co.il/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/146101/#clinics", "https://www.infomed.co.il/experts/146101/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>איתן גלעדי יעקובי</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>gen-c@tlvmc.gov.il</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>90</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>"איתן גלעדי יעקובי" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[{"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>איתן גלעדי יעקובי</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>og-clinic@tlvmc.gov.il</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>90</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>"איתן גלעדי יעקובי" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>[{"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>איתמר זילברמן רון</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>info@medreviews.co.il</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>75</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.medreviews.co.il/contact-us</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MedReviews - יצירת קשר יצירת קשר קשר עם MedReviews פנחס ספיר 8, נס ציונה 055-4548554 info@medreviews.co.il Loading... מלאו  פרטים ונציג שלנו יצור עמך קשר בהקדם שם * שם * טלפון * טלפון * אימייל אימייל הערות * הערות * בהשארת פרטים אני מאשר כי אני מעוניין לקבל התקשרות חוזרת מהמרפאה, וכן מאשר את תנאי השימוש ומדיניות הפרטיות באתר MedReviews. אני מעוניין לקבל דברי פרסומת כהגדרתם בחוק מ-MedReviews ומהמרפאה ובאפשרותי לחזור בי מהסכמה זו בכל עת. שליחה אודות MedReviews היא אינדקס לרופאים המתקדם והאמין בישר</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>"איתמר זילברמן רון" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://itamar-clinic.co.il/", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/1.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/6.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/3.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/5.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/4.jpg", "https://www.medreviews.co.il/provider/dr-zilberman-ron-itamar", "https://clinica-med.co.il/doctors/%D7%93%D7%B4%D7%A8-%D7%90%D7%99%D7%AA%D7%9E%D7%A8-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%95%D7%9F/", "https://www.medreviews.co.il/provider/dr-zilberman-ron-itamar#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://clinica-med.co.il/", "https://www.doctorita.co.il/experts/97780", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors"]</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,7 +864,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>אלון טל</t>
+          <t>אמל תורעאני</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>dralontal@gmail.com</t>
+          <t>amalto@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://dr-alontal.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/amal-tourani/</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בתהליך. קטלוג האתר שירותי העסק בלוג ומאמרים אודות ד״ר אלון טל כירורגיה גינקולוגית ואונקולוגית ד״ר אלון טל מתמחה בכירורגיה גינקולוגית ואונקולוגית ומנהל מרפאה גינקולוגית מתקדמת בחיפה. המרפאה מציעה שירותים מקצועיים בתחום הגינקולוגיה והגינקואונקולוגיה, לרבות ייעוץ גינקולוגי, ניתוחים מתקדמים, מרפאת צוואר הרחם, קולפוסקופיה, היסטרוסקופיות וקוניזציה של צוואר הרחם. המרפאה מספקת מענה רפואי מקיף לנשים מכל רחבי הארץ, בשיתוף פעולה עם קופות החולים מכבי, מאוחדת וכללית וביטוחים פרטיים, תוך הקפדה על איכות הטיפו</t>
+          <t>המטולוגיה פודקאסט שימו לב פודקאסט נוירולוגיה 1:1 פודקאסט וואלה אטמוספירה פגישות סגל 2026 פגישות סגל 25 פגישות סגל 23-24 פגישות סגל 21-22 הדרכה המטולוגיה מחויבים להעניק רפואה מובילה ואנושית באופן שווה לכל באמצעות טובי הרופאים והצוות הרפואי כולו, תוך הצטיינות בהוראה, מחקר ופיתוח ולמען בריאות כלל התושבים בארץ ובעולם. צור קשר עמותת הידידים עברית English العربية русский https://tasmc-search-82c272.ent.westeurope.azure.elastic-cloud.com tasmcprod search-zickmtrj5fe9qg3zgt8o8y2e /search-result/ /api/as</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>"אלון טל" יילוד גינקולוג</t>
+          <t>"אמל תורעאני" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -927,15 +927,15 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אלון טל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[{"email": "gen-c@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל", "matched_query": "\"אמל תורעאני\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"אמל תורעאני\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"אמל תורעאני\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/153548/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://dr-alontal.co.il/", "https://dr-alontal.co.il/about"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://medpage.co.il/doctors/%D7%90%D7%9E%D7%9C-%D7%AA%D7%95%D7%A8%D7%A2%D7%90%D7%A0%D7%99-25696/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/", "https://www.tasmc.org.il/doctorssearch/dr/amal-tourani/", "https://www.tasmc.org.il/doctorssearch/dr/amal-tourani/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>אלון קדם</t>
+          <t>אנה פטרוסב</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>doctorkedem@gmail.com</t>
+          <t>a_petruseva@rmc.gov.il</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.kedemalon.co.il/</t>
+          <t>https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -997,30 +997,30 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ים לא שגרתיים בכל שאלה ותהיה שהיתה לי וידע תמיד לתת מענה מקצועי ואישי. להריון הראשון נכנסנו לאחר סבב הטיפולים השני ולאחר 9 חודשים נולדה לנו בת מדהימה, לאורך כל ההריון דוקטור קדם ליווה אותנו דרך כל הפחדים והלבטים שכל מי שעבר אינספור נסיונות כושלים וודאי מכיר. לאחר שנתיים, כשהחלטנו שאנחנו מוכנים לעוד 'תוספת' למשפחה, מיד חזרנו לד'ר קדם והפעם הוא הצליח אפילו יותר – ונכנסנו להריון כבר אחרי סבב טיפולים בודד. בתהליך הכל כך קשה ומורכב שעברנו עם אינספור טיפולים וגם הפלות ד'ר קדם היה האדם שהחזיר לנו את הא</t>
+          <t>דואר אלקטרוני ד"ר אנה פטרוסב [email protected]</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>"אלון קדם" יילוד גינקולוג</t>
+          <t>"אנה פטרוסב" מרפאה פרטית</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[{"email": "info@medico.co.il", "confidence": 95, "source_url": "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%A7%D7%93%D7%9D/", "evidence": "כז, השרון חברות ביטוח: פרטי 5.0/5 1 גולשים דירגו מעוניינים לדרג את ד\"ר אלון קדם במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד\"ר אלון קדם רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. שימור פוריות: מתי מומלץ להקפיא ביציות- סטטוסקופ להתייעצות עם ד\"ר אלון קדם השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל", "matched_query": "\"אלון קדם\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+          <t>[{"email": "ks.m@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/contact-for-doctors/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "officeks@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "office@sharapplus.co.il", "confidence": 75, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.kedemalon.co.il/", "https://www.waze.com/live-map/directions/il/tel-aviv-district/herzliya/ramat-yam-st-4?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.ChIJc2kUjZtIHRURffNez5FjSTo", "https://www.waze.com/live-map/directions/il/tel-aviv-district/%D7%A8%D7%92/shalem-st-3?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.ChIJ48cAeANLHRURhP10NlTZb-k", "https://www.kedemalon.co.il/about", "https://www.kedemalon.co.il/contact", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%A7%D7%93%D7%9D/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%94%D7%A8%D7%A6%D7%9C%D7%99%D7%94/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://sharapplus.co.il/doctors/anna-petruseva/", "https://sharapplus.co.il/terms-and-conditions/", "https://sharapplus.co.il/all-doctors/", "https://sharapplus.co.il/contact-for-doctors/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#f19e9797989294b1829990839081819d8482df929edf989d", "https://sharapplus.co.il/cdn-cgi/l/email-protection#84ebe2e2ede7e1c4f7ece5f6e5f4f4e8f1f7aae7ebaaede8", "https://sharapplus.co.il/about/", "https://sharapplus.co.il/contact-us/", "https://sharapplus.co.il/doctors/%D7%98%D7%9C%D7%99-%D7%90%D7%A0%D7%92%D7%95%D7%A8/", "https://sharapplus.co.il/doctors/moaad-slieman/", "https://sharapplus.co.il/doctors/dr_eti_fiora/", "https://sharapplus.co.il/doctors/dr_manevitz/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%90%D7%99%D7%A8-%D7%A7%D7%A1%D7%98%D7%A0%D7%91%D7%90%D7%95%D7%9D/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%A8%D7%96/", "https://sharapplus.co.il/doctors/nail-abaya/", "https://sharapplus.co.il/doctors/med-balance-institute/", "https://sharapplus.co.il/doctors/nahum-eliyahu/", "https://sharapplus.co.il/doctors/eyal-zipman/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#551e067b3815263d34273425253920267b363a7b3c39", "https://sharapplus.co.il/cdn-cgi/l/email-protection", "https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/entandheadandnecksurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/ambulatory_operating_room/", "https://www.rambam.org.il/departmentsandclinics/trauma-and-emergency-surgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/generalsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/breastsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/vascularsurgeryandtransplantation/"]</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>אביעד כהן</t>
+          <t>אסנת גרוץ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>usw@tlvmc.gov.il</t>
+          <t>asnatg@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/garuz-osnat/</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1082,35 +1082,33 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון </t>
+          <t>ך - פרופסור חבר קליני, בית הספר לרפואה ע"ש סאקלר, אוניברסיטת תל אביב 2002-2011 מרצה בכירה, בית הספר לרפואה ע"ש סאקלר, אוניברסיטת תל אביב פרסומים מקצועיים ​מעל 100 פרסומים בנושאי אורוגינקולוגיה ורצפת אגן בכתבי עת מקצועיים בינלאומיים רשימת פרסומים באתר PUBMED חברות באיגודים מקצועיים ההסתדרות הרפואית האיגוד הישראלי לגינקולוגיה ומיילדות האיגוד הישראלי לאורוגינקולוגיה איגודים מקצועיים בינלאומיים:  ICS, AUA, SUFU, IUGA שטחי התעניינות ועיסוק מיוחדים ​דליפת שתן צניחת אברי אגן זיהומים בשתן ניתוחי שיקום ר</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>"אביעד כהן" יילוד גינקולוג site:tasmc.org.il</t>
+          <t>"אסנת גרוץ" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>hospital_text</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "gen-c@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל", "matched_query": "\"אסנת גרוץ\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"אסנת גרוץ\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"אסנת גרוץ\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אסנת גרוץ\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>["https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/"]</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctors.assuta.co.il/doctor/osnat-groutz-21406?readmore=true", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=BAC416C76666AA9839921027807F370D31B95A90A98BBF38FC3ED4D51A7FB863&amp;RequestId=00000000-0000-0000-0001-000000000300", "https://www.maccabi4u.co.il/kosher", "https://go.serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%92%D7%A8%D7%95%D7%A5%20%D7%90%D7%A1%D7%A0%D7%AA", "https://go.serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=57323214&amp;ProviderProfession=W&amp;docClinic=74053&amp;Service=1&amp;NewObjectId=70028074&amp;NewObjectType=S&amp;NewPerNr=90002206&amp;ol1=70028074&amp;ol2=S&amp;ol3=90002206&amp;isKosher=1&amp;beginDate=2026-09-01T01:25:02&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.infomed.co.il/experts/93699/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.tasmc.org.il/doctorssearch/dr/garuz-osnat/", "https://www.tasmc.org.il/doctorssearch/dr/garuz-osnat/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
         <v>1</v>
       </c>
@@ -1121,7 +1119,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>איתי גת</t>
+          <t>אלון טל</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1146,7 +1144,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>itaigatclinic@gmail.com</t>
+          <t>dralontal@gmail.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1155,11 +1153,11 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://prof-itaigat.co.il/</t>
+          <t>https://dr-alontal.co.il/</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1169,12 +1167,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ני וטיפולים רפואיים מתישים אלא גם בהתמודדות רגשית מורכב ביותר בהיבטים מגוונים -אישי, זוגי, משפחתי וחברתי. הטכנולוגיה הרפואית אמנם מאפשרת השגת הריון ולידה במרבית המקרים אולם לעיתים קרובות מחייבת התמדה וסבלנות וגם יכולות להתמודד עם חוסר הצלחה עד השגת התוצאה המיוחלת. רופא פוריות חייב בעיני להיות בעל שילוב תכונות. נדרשת מקצוענות מהשורה הראשונה, דיוק וקפדנות בפרטי הטיפול תוך התעדכנות שוטפת בחידושים הרפואיים. בנוסף יש צורך לשמור על הפרספקטיבה הרחבה – לראות את מכלול התמונה של שני בני הזוג ונתוניהם הביו</t>
+          <t xml:space="preserve"> בתהליך. קטלוג האתר שירותי העסק בלוג ומאמרים אודות ד״ר אלון טל כירורגיה גינקולוגית ואונקולוגית ד״ר אלון טל מתמחה בכירורגיה גינקולוגית ואונקולוגית ומנהל מרפאה גינקולוגית מתקדמת בחיפה. המרפאה מציעה שירותים מקצועיים בתחום הגינקולוגיה והגינקואונקולוגיה, לרבות ייעוץ גינקולוגי, ניתוחים מתקדמים, מרפאת צוואר הרחם, קולפוסקופיה, היסטרוסקופיות וקוניזציה של צוואר הרחם. המרפאה מספקת מענה רפואי מקיף לנשים מכל רחבי הארץ, בשיתוף פעולה עם קופות החולים מכבי, מאוחדת וכללית וביטוחים פרטיים, תוך הקפדה על איכות הטיפו</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>"איתי גת" יילוד גינקולוג</t>
+          <t>"אלון טל" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1184,7 +1182,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"איתי גת\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אלון טל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1192,7 +1190,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/איתי-גת", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%AA-%D7%90%D7%99%D7%AA%D7%99/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://doctors.assuta.co.il/search/doctor/itai-gat-38246", "https://www.facebook.com/itaigatfertility/", "https://www.infomed.co.il/experts/146101/", "https://prof-itaigat.co.il/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/146101/#clinics", "https://www.infomed.co.il/experts/146101/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/153548/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://dr-alontal.co.il/", "https://dr-alontal.co.il/about"]</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1206,7 +1204,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>איתן גלעדי יעקובי</t>
+          <t>אלון קדם</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1231,7 +1229,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>gen-c@tlvmc.gov.il</t>
+          <t>doctorkedem@gmail.com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1240,11 +1238,11 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
+          <t>https://www.kedemalon.co.il/</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1254,12 +1252,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל</t>
+          <t>ים לא שגרתיים בכל שאלה ותהיה שהיתה לי וידע תמיד לתת מענה מקצועי ואישי. להריון הראשון נכנסנו לאחר סבב הטיפולים השני ולאחר 9 חודשים נולדה לנו בת מדהימה, לאורך כל ההריון דוקטור קדם ליווה אותנו דרך כל הפחדים והלבטים שכל מי שעבר אינספור נסיונות כושלים וודאי מכיר. לאחר שנתיים, כשהחלטנו שאנחנו מוכנים לעוד 'תוספת' למשפחה, מיד חזרנו לד'ר קדם והפעם הוא הצליח אפילו יותר – ונכנסנו להריון כבר אחרי סבב טיפולים בודד. בתהליך הכל כך קשה ומורכב שעברנו עם אינספור טיפולים וגם הפלות ד'ר קדם היה האדם שהחזיר לנו את הא</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>"איתן גלעדי יעקובי" יילוד גינקולוג</t>
+          <t>"אלון קדם" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1269,15 +1267,15 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[{"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+          <t>[{"email": "info@medico.co.il", "confidence": 95, "source_url": "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%A7%D7%93%D7%9D/", "evidence": "כז, השרון חברות ביטוח: פרטי 5.0/5 1 גולשים דירגו מעוניינים לדרג את ד\"ר אלון קדם במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד\"ר אלון קדם רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. שימור פוריות: מתי מומלץ להקפיא ביציות- סטטוסקופ להתייעצות עם ד\"ר אלון קדם השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל", "matched_query": "\"אלון קדם\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.kedemalon.co.il/", "https://www.waze.com/live-map/directions/il/tel-aviv-district/herzliya/ramat-yam-st-4?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.ChIJc2kUjZtIHRURffNez5FjSTo", "https://www.waze.com/live-map/directions/il/tel-aviv-district/%D7%A8%D7%92/shalem-st-3?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.ChIJ48cAeANLHRURhP10NlTZb-k", "https://www.kedemalon.co.il/about", "https://www.kedemalon.co.il/contact", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%A7%D7%93%D7%9D/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%94%D7%A8%D7%A6%D7%9C%D7%99%D7%94/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1291,7 +1289,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>איתן גלעדי יעקובי</t>
+          <t>אריאל זילברליכט</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1316,7 +1314,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>og-clinic@tlvmc.gov.il</t>
+          <t>arielzilberlicht@gmail.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1325,11 +1323,11 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
+          <t>https://doctor-ariel.co.il/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1339,12 +1337,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו</t>
+          <t xml:space="preserve"> גיל המעבר אסתטיקה גינקולוגית אודות בלוג מתוך התקשורת יצירת קשר דף הבית שירותי המרפאה גינקולוגיה כללית אורוגינקולוגיה גיל המעבר אסתטיקה גינקולוגית אודות בלוג מתוך התקשורת יצירת קשר 073-3990235 להזמנת תור דף הבית שירותי המרפאה גינקולוגיה כללית אורוגינקולוגיה גיל המעבר אסתטיקה גינקולוגית אודות בלוג מתוך התקשורת יצירת קשר דף הבית שירותי המרפאה גינקולוגיה כללית אורוגינקולוגיה גיל המעבר אסתטיקה גינקולוגית אודות בלוג מתוך התקשורת יצירת קשר דף הבית שירותי המרפאה גינקולוגיה כללית אורוגינקולוגיה גיל המעב</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>"איתן גלעדי יעקובי" יילוד גינקולוג</t>
+          <t>"אריאל זילברליכט" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1354,20 +1352,20 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>[{"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+          <t>[{"email": "doctor.zilberlicht@gmail.com", "confidence": 95, "source_url": "https://doctor-ariel.co.il/", "evidence": "צמוד, החל משלב התשאול הראשוני, ביצוע ניתוחים ועד לסיום המעקבים לאחר הטיפול. להמשך קריאה אני מאמין: רפואה בגובה העיניים​ הזכות ללוות נשים בכל אחד משלבי חייהן צופנת בחובה אחריות כבדה מאוד. הגישה שלי מבוססת על אוזן קשבת, הישרת מבט ומתן אפשרות לכל מטופלת לספר את סיפורה בקצב שלה. המפגש עם רופא הנשים חייב להיות מכבד, לא שיפוטי ומותאם אישית בשפה ברורה. אני סבור כי תחושת הביטחון והאמון של המטופלת הן בעלות חשיבות מכרעת להצלחת הטיפול הרפואי. שירותי המרפאה גינקולוגיה אורוגינקולוגיה גיל המעבר אסתטיקה גינקול", "matched_query": "\"אריאל זילברליכט\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctor-ariel.co.il/", "https://yosseftiran.com/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%90%D7%95%D7%A8%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%92%D7%99%D7%9C-%D7%94%D7%9E%D7%A2%D7%91%D7%A8/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%90%D7%A1%D7%AA%D7%98%D7%99%D7%A7%D7%94-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://doctor-ariel.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://doctor-ariel.co.il/%D7%91%D7%9C%D7%95%D7%92/", "https://doctor-ariel.co.il/%D7%9E%D7%9F-%D7%94%D7%AA%D7%A7%D7%A9%D7%95%D7%A8%D7%AA/", "https://doctor-ariel.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://doctor-ariel.co.il/%d7%a9%d7%99%d7%a8%d7%95%d7%aa%d7%99-%d7%94%d7%9e%d7%a8%d7%a4%d7%90%d7%94/%d7%92%d7%99%d7%a0%d7%a7%d7%95%d7%9c%d7%95%d7%92%d7%99%d7%94/", "https://doctor-ariel.co.il/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA/", "https://doctor-ariel.co.il/%d7%a9%d7%99%d7%a8%d7%95%d7%aa%d7%99-%d7%94%d7%9e%d7%a8%d7%a4%d7%90%d7%94/%d7%90%d7%95%d7%a8%d7%95%d7%92%d7%99%d7%a0%d7%a7%d7%95%d7%9c%d7%95%d7%92%d7%99%d7%94/%d7%a6%d7%a0%d7%99%d7%97%d7%aa-%d7%a8%d7%97%d7%9d/", "https://doctor-ariel.co.il/wp-content/uploads/2022/04/updated-CV-nov-2021.pdf", "https://doctor-ariel.co.il/dr-zilberlicht-clinic-faq/"]</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1376,7 +1374,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>איתמר זילברמן רון</t>
+          <t>אריאל זילברליכט</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1401,20 +1399,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>info@medreviews.co.il</t>
+          <t>doctor.zilberlicht@gmail.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.medreviews.co.il/contact-us</t>
+          <t>https://doctor-ariel.co.il/</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1424,12 +1422,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MedReviews - יצירת קשר יצירת קשר קשר עם MedReviews פנחס ספיר 8, נס ציונה 055-4548554 info@medreviews.co.il Loading... מלאו  פרטים ונציג שלנו יצור עמך קשר בהקדם שם * שם * טלפון * טלפון * אימייל אימייל הערות * הערות * בהשארת פרטים אני מאשר כי אני מעוניין לקבל התקשרות חוזרת מהמרפאה, וכן מאשר את תנאי השימוש ומדיניות הפרטיות באתר MedReviews. אני מעוניין לקבל דברי פרסומת כהגדרתם בחוק מ-MedReviews ומהמרפאה ובאפשרותי לחזור בי מהסכמה זו בכל עת. שליחה אודות MedReviews היא אינדקס לרופאים המתקדם והאמין בישר</t>
+          <t>צמוד, החל משלב התשאול הראשוני, ביצוע ניתוחים ועד לסיום המעקבים לאחר הטיפול. להמשך קריאה אני מאמין: רפואה בגובה העיניים​ הזכות ללוות נשים בכל אחד משלבי חייהן צופנת בחובה אחריות כבדה מאוד. הגישה שלי מבוססת על אוזן קשבת, הישרת מבט ומתן אפשרות לכל מטופלת לספר את סיפורה בקצב שלה. המפגש עם רופא הנשים חייב להיות מכבד, לא שיפוטי ומותאם אישית בשפה ברורה. אני סבור כי תחושת הביטחון והאמון של המטופלת הן בעלות חשיבות מכרעת להצלחת הטיפול הרפואי. שירותי המרפאה גינקולוגיה אורוגינקולוגיה גיל המעבר אסתטיקה גינקול</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>"איתמר זילברמן רון" יילוד גינקולוג</t>
+          <t>"אריאל זילברליכט" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1439,20 +1437,530 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "doctor.zilberlicht@gmail.com", "confidence": 95, "source_url": "https://doctor-ariel.co.il/", "evidence": "צמוד, החל משלב התשאול הראשוני, ביצוע ניתוחים ועד לסיום המעקבים לאחר הטיפול. להמשך קריאה אני מאמין: רפואה בגובה העיניים​ הזכות ללוות נשים בכל אחד משלבי חייהן צופנת בחובה אחריות כבדה מאוד. הגישה שלי מבוססת על אוזן קשבת, הישרת מבט ומתן אפשרות לכל מטופלת לספר את סיפורה בקצב שלה. המפגש עם רופא הנשים חייב להיות מכבד, לא שיפוטי ומותאם אישית בשפה ברורה. אני סבור כי תחושת הביטחון והאמון של המטופלת הן בעלות חשיבות מכרעת להצלחת הטיפול הרפואי. שירותי המרפאה גינקולוגיה אורוגינקולוגיה גיל המעבר אסתטיקה גינקול", "matched_query": "\"אריאל זילברליכט\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://itamar-clinic.co.il/", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/1.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/6.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/3.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/5.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/4.jpg", "https://www.medreviews.co.il/provider/dr-zilberman-ron-itamar", "https://clinica-med.co.il/doctors/%D7%93%D7%B4%D7%A8-%D7%90%D7%99%D7%AA%D7%9E%D7%A8-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%95%D7%9F/", "https://www.medreviews.co.il/provider/dr-zilberman-ron-itamar#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://clinica-med.co.il/", "https://www.doctorita.co.il/experts/97780", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctor-ariel.co.il/", "https://yosseftiran.com/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%90%D7%95%D7%A8%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%92%D7%99%D7%9C-%D7%94%D7%9E%D7%A2%D7%91%D7%A8/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%90%D7%A1%D7%AA%D7%98%D7%99%D7%A7%D7%94-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://doctor-ariel.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://doctor-ariel.co.il/%D7%91%D7%9C%D7%95%D7%92/", "https://doctor-ariel.co.il/%D7%9E%D7%9F-%D7%94%D7%AA%D7%A7%D7%A9%D7%95%D7%A8%D7%AA/", "https://doctor-ariel.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://doctor-ariel.co.il/%d7%a9%d7%99%d7%a8%d7%95%d7%aa%d7%99-%d7%94%d7%9e%d7%a8%d7%a4%d7%90%d7%94/%d7%92%d7%99%d7%a0%d7%a7%d7%95%d7%9c%d7%95%d7%92%d7%99%d7%94/", "https://doctor-ariel.co.il/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA/", "https://doctor-ariel.co.il/%d7%a9%d7%99%d7%a8%d7%95%d7%aa%d7%99-%d7%94%d7%9e%d7%a8%d7%a4%d7%90%d7%94/%d7%90%d7%95%d7%a8%d7%95%d7%92%d7%99%d7%a0%d7%a7%d7%95%d7%9c%d7%95%d7%92%d7%99%d7%94/%d7%a6%d7%a0%d7%99%d7%97%d7%aa-%d7%a8%d7%97%d7%9d/", "https://doctor-ariel.co.il/wp-content/uploads/2022/04/updated-CV-nov-2021.pdf", "https://doctor-ariel.co.il/dr-zilberlicht-clinic-faq/"]</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>אמיר רבהון</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ravhon.clinic@gmail.com</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>90</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://www.dr-ravhon.co.il/</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ד"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצירת קשר תפריט דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת בי</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>"אמיר רבהון" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>[{"email": "ravhon.clinic@gmail.com", "confidence": 90, "source_url": "https://www.dr-ravhon.co.il/", "evidence": "ד\"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצירת קשר תפריט דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת בי", "matched_query": "\"אמיר רבהון\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9E%D7%99%D7%A8-%D7%A8%D7%91%D7%94%D7%95%D7%9F/", "https://www.dr-ravhon.co.il/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%A8%D7%97%D7%95%D7%91%D7%95%D7%AA/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>איתי גת</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>itaigatclinic@gmail.com</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>90</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://prof-itaigat.co.il/</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ני וטיפולים רפואיים מתישים אלא גם בהתמודדות רגשית מורכב ביותר בהיבטים מגוונים -אישי, זוגי, משפחתי וחברתי. הטכנולוגיה הרפואית אמנם מאפשרת השגת הריון ולידה במרבית המקרים אולם לעיתים קרובות מחייבת התמדה וסבלנות וגם יכולות להתמודד עם חוסר הצלחה עד השגת התוצאה המיוחלת. רופא פוריות חייב בעיני להיות בעל שילוב תכונות. נדרשת מקצוענות מהשורה הראשונה, דיוק וקפדנות בפרטי הטיפול תוך התעדכנות שוטפת בחידושים הרפואיים. בנוסף יש צורך לשמור על הפרספקטיבה הרחבה – לראות את מכלול התמונה של שני בני הזוג ונתוניהם הביו</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>"איתי גת" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"איתי גת\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/איתי-גת", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%AA-%D7%90%D7%99%D7%AA%D7%99/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://doctors.assuta.co.il/search/doctor/itai-gat-38246", "https://www.facebook.com/itaigatfertility/", "https://www.infomed.co.il/experts/146101/", "https://prof-itaigat.co.il/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/146101/#clinics", "https://www.infomed.co.il/experts/146101/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>אנה פטרוסב</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ks.m@sharapplus.co.il</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>85</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://sharapplus.co.il/contact-for-doctors/</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>"אנה פטרוסב" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[{"email": "ks.m@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/contact-for-doctors/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "officeks@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "office@sharapplus.co.il", "confidence": 75, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://sharapplus.co.il/doctors/anna-petruseva/", "https://sharapplus.co.il/terms-and-conditions/", "https://sharapplus.co.il/all-doctors/", "https://sharapplus.co.il/contact-for-doctors/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#f19e9797989294b1829990839081819d8482df929edf989d", "https://sharapplus.co.il/cdn-cgi/l/email-protection#84ebe2e2ede7e1c4f7ece5f6e5f4f4e8f1f7aae7ebaaede8", "https://sharapplus.co.il/about/", "https://sharapplus.co.il/contact-us/", "https://sharapplus.co.il/doctors/%D7%98%D7%9C%D7%99-%D7%90%D7%A0%D7%92%D7%95%D7%A8/", "https://sharapplus.co.il/doctors/moaad-slieman/", "https://sharapplus.co.il/doctors/dr_eti_fiora/", "https://sharapplus.co.il/doctors/dr_manevitz/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%90%D7%99%D7%A8-%D7%A7%D7%A1%D7%98%D7%A0%D7%91%D7%90%D7%95%D7%9D/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%A8%D7%96/", "https://sharapplus.co.il/doctors/nail-abaya/", "https://sharapplus.co.il/doctors/med-balance-institute/", "https://sharapplus.co.il/doctors/nahum-eliyahu/", "https://sharapplus.co.il/doctors/eyal-zipman/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#551e067b3815263d34273425253920267b363a7b3c39", "https://sharapplus.co.il/cdn-cgi/l/email-protection", "https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/entandheadandnecksurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/ambulatory_operating_room/", "https://www.rambam.org.il/departmentsandclinics/trauma-and-emergency-surgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/generalsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/breastsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/vascularsurgeryandtransplantation/"]</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>אנה פטרוסב</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>officeks@sharapplus.co.il</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>85</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://sharapplus.co.il/doctors/anna-petruseva/</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>"אנה פטרוסב" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[{"email": "ks.m@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/contact-for-doctors/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "officeks@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "office@sharapplus.co.il", "confidence": 75, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://sharapplus.co.il/doctors/anna-petruseva/", "https://sharapplus.co.il/terms-and-conditions/", "https://sharapplus.co.il/all-doctors/", "https://sharapplus.co.il/contact-for-doctors/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#f19e9797989294b1829990839081819d8482df929edf989d", "https://sharapplus.co.il/cdn-cgi/l/email-protection#84ebe2e2ede7e1c4f7ece5f6e5f4f4e8f1f7aae7ebaaede8", "https://sharapplus.co.il/about/", "https://sharapplus.co.il/contact-us/", "https://sharapplus.co.il/doctors/%D7%98%D7%9C%D7%99-%D7%90%D7%A0%D7%92%D7%95%D7%A8/", "https://sharapplus.co.il/doctors/moaad-slieman/", "https://sharapplus.co.il/doctors/dr_eti_fiora/", "https://sharapplus.co.il/doctors/dr_manevitz/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%90%D7%99%D7%A8-%D7%A7%D7%A1%D7%98%D7%A0%D7%91%D7%90%D7%95%D7%9D/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%A8%D7%96/", "https://sharapplus.co.il/doctors/nail-abaya/", "https://sharapplus.co.il/doctors/med-balance-institute/", "https://sharapplus.co.il/doctors/nahum-eliyahu/", "https://sharapplus.co.il/doctors/eyal-zipman/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#551e067b3815263d34273425253920267b363a7b3c39", "https://sharapplus.co.il/cdn-cgi/l/email-protection", "https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/entandheadandnecksurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/ambulatory_operating_room/", "https://www.rambam.org.il/departmentsandclinics/trauma-and-emergency-surgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/generalsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/breastsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/vascularsurgeryandtransplantation/"]</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>אלנה דיקופולצב</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>app@forty.co.il</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>85</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.forty.co.il/contact</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>app@forty.co.il fortyapp @fortyapp</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>"אלנה דיקופולצב" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[{"email": "info@medreviews.co.il", "confidence": 75, "source_url": "https://www.medreviews.co.il/contact-us", "evidence": "MedReviews - יצירת קשר יצירת קשר קשר עם MedReviews פנחס ספיר 8, נס ציונה 055-4548554 info@medreviews.co.il Loading... מלאו  פרטים ונציג שלנו יצור עמך קשר בהקדם שם * שם * טלפון * טלפון * אימייל אימייל הערות * הערות * בהשארת פרטים אני מאשר כי אני מעוניין לקבל התקשרות חוזרת מהמרפאה, וכן מאשר את תנאי השימוש ומדיניות הפרטיות באתר MedReviews. אני מעוניין לקבל דברי פרסומת כהגדרתם בחוק מ-MedReviews ומהמרפאה ובאפשרותי לחזור בי מהסכמה זו בכל עת. שליחה אודות MedReviews היא אינדקס לרופאים המתקדם והאמין בישר", "matched_query": "\"אלנה דיקופולצב\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלנה-דיקופולצב", "https://www.medreviews.co.il/provider/dr-dikopoltsev-elena", "https://www.medreviews.co.il/provider/dr-dikopoltsev-elena#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=692190DF7EC470C8FF9D9F2B9878620353AD1BEFAF4991E1A7C44949E6817E31&amp;RequestId=00000000-0000-0000-0001-000000000209", "https://www.maccabi4u.co.il/kosher", "https://go.serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%93%D7%99%D7%A7%D7%95%D7%A4%D7%95%D7%9C%D7%A6%D7%91%20%D7%90%D7%9C%D7%A0%D7%94", "https://go.serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=304433089&amp;ProviderProfession=1&amp;docClinic=4000709&amp;Service=1&amp;NewObjectId=70055539&amp;NewObjectType=S&amp;NewPerNr=90016439&amp;ol1=70055539&amp;ol2=S&amp;ol3=90016439&amp;isKosher=1&amp;beginDate=2026-08-31T23:33:18&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.meuhedet.co.il/poi/Doctors/001358170152100049000000000000_0", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/3fbb8ab2-b9bd-48f0-bc8e-2261da2804db", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21", "https://www.forty.co.il/contact", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/a1ead677-fdde-4351-8e64-db92c279edd1", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/39f9ebe2-8b41-4c7f-8af3-dfe03652f60a", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/3abed105-4564-4cc4-9587-718d9018a641", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/eb18fcb9-5088-4a87-8e32-7868b77de072", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/4027b022-22b5-4b14-8323-8f6590eaf560", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/405cdeae-9149-4a27-ac1b-2098a2d3abec", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/44f6e8d6-d3be-4757-8126-c3f3f76c2da9", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/e6c264ca-e2b6-4a27-87d9-2e993b557397", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/e4c95cc5-ddc5-4547-9a11-50f0d5e39641", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/74c7d262-c9cb-4900-8f25-7f7f5e9e402a", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/ce430b6f-9d65-4141-a213-16b3afb8f8c4", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/7f3bc8ba-dfa4-4767-aaae-b74e63af2650"]</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>אנה פטרוסב</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>office@sharapplus.co.il</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>75</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://sharapplus.co.il/doctors/anna-petruseva/</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>"אנה פטרוסב" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>[{"email": "ks.m@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/contact-for-doctors/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "officeks@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "office@sharapplus.co.il", "confidence": 75, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://sharapplus.co.il/doctors/anna-petruseva/", "https://sharapplus.co.il/terms-and-conditions/", "https://sharapplus.co.il/all-doctors/", "https://sharapplus.co.il/contact-for-doctors/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#f19e9797989294b1829990839081819d8482df929edf989d", "https://sharapplus.co.il/cdn-cgi/l/email-protection#84ebe2e2ede7e1c4f7ece5f6e5f4f4e8f1f7aae7ebaaede8", "https://sharapplus.co.il/about/", "https://sharapplus.co.il/contact-us/", "https://sharapplus.co.il/doctors/%D7%98%D7%9C%D7%99-%D7%90%D7%A0%D7%92%D7%95%D7%A8/", "https://sharapplus.co.il/doctors/moaad-slieman/", "https://sharapplus.co.il/doctors/dr_eti_fiora/", "https://sharapplus.co.il/doctors/dr_manevitz/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%90%D7%99%D7%A8-%D7%A7%D7%A1%D7%98%D7%A0%D7%91%D7%90%D7%95%D7%9D/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%A8%D7%96/", "https://sharapplus.co.il/doctors/nail-abaya/", "https://sharapplus.co.il/doctors/med-balance-institute/", "https://sharapplus.co.il/doctors/nahum-eliyahu/", "https://sharapplus.co.il/doctors/eyal-zipman/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#551e067b3815263d34273425253920267b363a7b3c39", "https://sharapplus.co.il/cdn-cgi/l/email-protection", "https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/entandheadandnecksurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/ambulatory_operating_room/", "https://www.rambam.org.il/departmentsandclinics/trauma-and-emergency-surgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/generalsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/breastsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/vascularsurgeryandtransplantation/"]</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,15 +499,30 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>search_queries</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>search_errors</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>search_results</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>hospital_pass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>candidate_rank</t>
         </is>
@@ -515,11 +530,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>אביטל יונה רפפורט</t>
+          <t>אבי בן-הרוש</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -544,7 +559,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>avitalsr@tlvmc.gov.il</t>
+          <t>benharoush@gmail.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,7 +572,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/skornik-rapaport-avital/</t>
+          <t>https://med.tau.ac.il/profile/avibenh</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -567,46 +582,47 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ר האישי AI צ'אט ד''ר אביטל סקורניק-רפפורט רופאה בכירה, המחלקה לרפואת האם והעובר, מנהלת המרפאה להריון בסיכון גבוה, ביה"ח "ליס" ליולדות ונשים איכילוב צוות איכילוב אביטל סקורניק-רפפורט השכלה 1994-2000 הפקולטה לרפואה ע"ש סאקלר אוניברסיטת תל אביב 2003-2004 לימודי המשך במיילדות וגיניקולוגיה בי"ס לרפואה אוניברסיטת ת"א. מומחיות מוכרת מומחית למיילדות וגינקולוגיה ניסיון קליני 2009 ואילך רופאה עצמאית במכבי שירותי בריאות. 2007 ואילך רופאה בכירה במחלקה לאשפוז טרום לידתי, ביה"ח ליס ליולודת, המרכז הרפואי ת"א. </t>
+          <t xml:space="preserve"> מוריס וגבריאלה גולדשלגר מכון לחקר הלב ע"ש נויפלד המכון למחקר רפואי ע"ש פלסנשטיין מינהל ושירותים מינהל ושירותים מערכות מידע יחידת רכש ואינוונטר משרד אב הבית המעבדה לצילום מועמדים תוכניות חדשות תכנית למוסמך במחקר ביו-רפואי BRAVO-MSc מסלול BRAVO לדוקטורט במחקר ביו רפואי תואר שני בפיתוח ויישום תרופתי תואר שני (M.Sc) בבריאות דיגיטלית קישורים חשובים חוברת החוקרים ידיעונים 2025/26, תשפ"ו מנחים לתואר שני / שלישי הנחיות חירום הינך נמצא כאן לדף הבית של אוניברסיטת תל אביב &gt; הפקולטה למדעי הרפואה והבריאות ע</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>"אביטל יונה רפפורט" email site:tasmc.org.il</t>
+          <t>"אבי בן-הרוש" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>hospital_text</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "baruchik@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/Information_for_dentists", "evidence": "ברוך קסנטיני baruchik@tauex.tau.ac.il 03-6409187/5980", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "erezavis@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "galavishai@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "haniabutziam@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>["https://www.tasmc.org.il/doctorssearch/dr/skornik-rapaport-avital/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/"]</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>["https://www.doctorim.co.il/doctor-35894/פרופ-אבי-בןהרוש/מומחה-יילוד-וגניקולוגיה", "https://med.tau.ac.il/profile/avibenh", "http://www.avibh.co.il", "https://med.tau.ac.il/HR-%20academic-staff-2019", "https://med.tau.ac.il/info-HR-administration-new-staff-2019", "https://med.tau.ac.il/research-projects-staff-2019", "https://med.tau.ac.il/HR-%20academic-new-staff-2019", "https://med.tau.ac.il/staff-faculty-of-medicine", "https://med.tau.ac.il/profile/avibenh#anchor_general_info", "https://med.tau.ac.il/profile/avibenh#anchor_cv", "https://med.tau.ac.il/profile/avibenh#anchor_publications", "http://new.tau.ac.il/about", "https://medicine-cms.tau.ac.il/HR- academic-staff-2019", "https://med.tau.ac.il/Information_for_dentists", "https://medicine-cms.tau.ac.il/HR- academic-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-pre-clinical-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-administrativ-new-staff-2019", "https://medicine-cms.tau.ac.il/new-research-projects-staff-2019", "https://medicine-cms.tau.ac.il/HR-junior-acdemic-staff-2019", "https://med.tau.ac.il/info-pre-clinical-researcers-2019", "https://med.tau.ac.il/info-pre-clinical-teachers-2019"]</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>איריס שהם</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -631,7 +647,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>irissh@bgu.ac.il</t>
+          <t>aflek1@yahoo.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -644,7 +660,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/irissh/</t>
+          <t>https://www.szmc.org.il/doctors/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -654,12 +670,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">يل للجامعة موقع التسجيل شروط القبول للقب الأول معلومات شخصية للذين سجلوا للتعليم إجراءات دفع الرسوم الدراسية الأسئلة المتداولة حول الرسوم الدراسية عمادة شؤون الطلبة خدمات تُقدم لطلبة عمادة شؤون الطلاب قسم الخدمات للطلاب العرب منح دراسية وقروض قسم الخدمات النفسية للطلاب مركز التوجيه المهني أصحاب الوظائف مساعدة في قضايا اكاديمية خدمات مركز الدعم خدمات لطلاب مع إعاقة جسدية دائمة او مؤقتة معهد تشخيص وظائف تعليمية تسهيلات في حال الحمل والولادة ماذا كنت تريد البحث عنه؟ ماذا كنت تريد البحث عنه؟ الصفحة </t>
+          <t>ר  בוריס צוקרמן מנהל יחידה לאנדוסקופיה גינקולוגית + + ד"ר  בתיה  צוקרמן רופאה בכירה + + ד"ר  רות  ציטר קוינט מנהלת היחידה לרדיולוגית ילדים + + ד"ר  אבי צפריר רופא בכיר ivfrec@szmc.org.il ivfrec@szmc.org.il + + ד"ר בלאל קוטינה רופא בכיר + + ד"ר  דמיטרי קוליקוב מנהל שירות אונקו-אורולוגיה dmitryk@szmc.org.il dmitryk@szmc.org.il מחלקה 02-6555556 מחלקה: 02-6555556 + + פרופ' נעמה קונסטנטיני מנהלת המרכז לרפואת ספורט ע"ש היידי רוטברג naamac@szmc.org.il naamac@szmc.org.il משרד 02-5325590 משרד: 02-5325590</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>"איריס שהם" מרפאה פרטית</t>
+          <t>"אבי צפריר" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,29 +685,32 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "chernyn@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "י + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר מיכאל פשרסטניק רופא בכיר + + ד\"ר בשאר פתיחה מתמחה על + + ד\"ר  איליה צ'חנוביץ רופא בכיר + + ד\"ר נטליה צ'פל מתמחה על + + פרופ' בוריס צ'רטין מנ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "chertinb@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "\"ר מאיר  פרנקל מנהל היחידה לאנדוקרינולוגיה, סוכרת ומטבוליזם meirf@szmc.org.il meirf@szmc.org.il מחלקה 02-6555111 מחלקה: 02-6555111 + + ד\"ר סופיה פרנקל רופא תחומי + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה:", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "dmitryk@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": " הילד chertinb@szmc.org.il chertinb@szmc.org.il מחלקה 02-6666763 מחלקה: 02-6666763 + + פרופ'  טלי  צ'רנוביצקי רופאה בכירה + + פרופ' נתן צ'רני מנהל היחידה לטיפול תומך chernyn@szmc.org.il chernyn@szmc.org.il 02-6555682 02-6555682 + + ד\"ר  שמרית  צבי-בר רופאה בכירה shimrittb@szmc.org.il shimrittb@szmc.org.il + + פרופ' דויד  צדוק מנהל מחלקת עיניים deyes@szmc.org.il deyes@szmc.org.il 02-6555897 :  02-6555897 + + ד\"ר  בוריס צוקרמן מנהל יחידה לאנדוסקופיה גינקולוגית + + ד\"ר  בתיה  צוקרמן רופאה בכירה + +", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "ivfrec@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/tsafrir-avi/", "evidence": "אות הוראה תכנית הסטאז' בשערי צדק התמחות בית הספר האקדמי לאֲחָיוּת יחידת ההוראה לחינוך רפואי ספרייה רפואית מחקר הרשות למחקר ופיתוח ועדת הלסינקי תרומות יצירת קשר כל הזכויות שמורות © 2023 | חלק מן התמונות באדיבות יגאל סלבין Facebook Facebook YouTube YouTube twitter twitter Instagram Instagram Linkedin Linkedin Tiktok Tiktok נגישות נגישות עברית עברית עברית English عربيه Русский חיפוש מה אתם מחפשים? זימון תור מחלקות ויחידות הרופא.ה שלי הגעה והתמצאות נגישות עברית עברית עברית English عربيه Русский צרו ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.bgu.ac.il/people/irissh/", "https://www.bgu.ac.il/ar/people/irissh/", "https://www.yazamut360.bgu.ac.il/?utm_campaign=alongtheyear&amp;utm_medium=BGUwebsite&amp;utm_source=BGUwebsite&amp;utm_term=Botton&amp;utm_content=Botton", "https://www.bgu.ac.il/ar/general/registration-website/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%94%D7%9D-%D7%90%D7%99%D7%A8%D7%99%D7%A1/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.beok.co.il/doctors/Doctors-131383/", "https://knowmore.co.il/doctors/אבי-צפריר/", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.tiktok.com/@szmcwebsite", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.szmc.org.il/departments/clinics-and-institutes/", "https://www.szmc.org.il/doctors/", "https://www.szmc.org.il/contact/", "https://www.szmc.org.il/about/tney-hashimush-baatar/", "https://www.szmc.org.il/doctors/merin-ofer/", "https://www.szmc.org.il/doctors/halevy-jonathan/", "https://www.szmc.org.il/doctors/blumberg-nehemia/", "https://www.szmc.org.il/about/about-us/#anchor-1", "https://www.szmc.org.il/about/about-us/#anchor-4", "https://www.szmc.org.il/about/units/pituach-mashabim-vekishrey-chutz/", "https://www.szmc.org.il/about/units/hanhalat-hasiud/", "https://www.szmc.org.il/about/units/agaf-ksafim/"]</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>אלי גבע</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -716,7 +735,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>drgeva@baby-ivf.com</t>
+          <t>chernyn@szmc.org.il</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -729,7 +748,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.baby-ivf.com/%D7%A6%D7%A8%D7%95-%D7%A7%D7%A9%D7%A8.html</t>
+          <t>https://www.szmc.org.il/doctors/</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -739,12 +758,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ו? לחץ ומשקל יתר: הסיבות לאי פוריות הורמונאליות אצל נשים הבדיקה הגורלית שתקבע את הטיפול באי פיריון אי פיריון: מאחורי כל גבר עומדת בדיקה פשוטה בן או בת? הטכנולוגיה שמזהה לבחור את מין העובר הפריה חוץ גופית: איך מעלים את הסיכוי להיריון? תרומת ביצית: כיצד להבטיח ילד בריא? לידיעת הנשים: מהו הגיל הנכון ביותר להרות? השיטה הרפואית שמאפשרת לנשים לשמר את הפוריות יש קליטה: כיצד להגדיל את הסיכוי להריון מתרומת ביציות? בן או בת? כיצד ניתן להשפיע על בחירת מן היילוד פוריות לטווח ארוך: כל מה שאתן צריכות לדעת על </t>
+          <t>י + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד"ר מיכאל פשרסטניק רופא בכיר + + ד"ר בשאר פתיחה מתמחה על + + ד"ר  איליה צ'חנוביץ רופא בכיר + + ד"ר נטליה צ'פל מתמחה על + + פרופ' בוריס צ'רטין מנ</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>"אלי גבע" מרפאה פרטית</t>
+          <t>"אבי צפריר" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -754,29 +773,32 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אלי גבע\" מרפאה פרטית", "extraction_method": "mailto"}]</t>
+          <t>[{"email": "chernyn@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "י + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר מיכאל פשרסטניק רופא בכיר + + ד\"ר בשאר פתיחה מתמחה על + + ד\"ר  איליה צ'חנוביץ רופא בכיר + + ד\"ר נטליה צ'פל מתמחה על + + פרופ' בוריס צ'רטין מנ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "chertinb@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "\"ר מאיר  פרנקל מנהל היחידה לאנדוקרינולוגיה, סוכרת ומטבוליזם meirf@szmc.org.il meirf@szmc.org.il מחלקה 02-6555111 מחלקה: 02-6555111 + + ד\"ר סופיה פרנקל רופא תחומי + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה:", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "dmitryk@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": " הילד chertinb@szmc.org.il chertinb@szmc.org.il מחלקה 02-6666763 מחלקה: 02-6666763 + + פרופ'  טלי  צ'רנוביצקי רופאה בכירה + + פרופ' נתן צ'רני מנהל היחידה לטיפול תומך chernyn@szmc.org.il chernyn@szmc.org.il 02-6555682 02-6555682 + + ד\"ר  שמרית  צבי-בר רופאה בכירה shimrittb@szmc.org.il shimrittb@szmc.org.il + + פרופ' דויד  צדוק מנהל מחלקת עיניים deyes@szmc.org.il deyes@szmc.org.il 02-6555897 :  02-6555897 + + ד\"ר  בוריס צוקרמן מנהל יחידה לאנדוסקופיה גינקולוגית + + ד\"ר  בתיה  צוקרמן רופאה בכירה + +", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "ivfrec@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/tsafrir-avi/", "evidence": "אות הוראה תכנית הסטאז' בשערי צדק התמחות בית הספר האקדמי לאֲחָיוּת יחידת ההוראה לחינוך רפואי ספרייה רפואית מחקר הרשות למחקר ופיתוח ועדת הלסינקי תרומות יצירת קשר כל הזכויות שמורות © 2023 | חלק מן התמונות באדיבות יגאל סלבין Facebook Facebook YouTube YouTube twitter twitter Instagram Instagram Linkedin Linkedin Tiktok Tiktok נגישות נגישות עברית עברית עברית English عربيه Русский חיפוש מה אתם מחפשים? זימון תור מחלקות ויחידות הרופא.ה שלי הגעה והתמצאות נגישות עברית עברית עברית English عربيه Русский צרו ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P4" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.beok.co.il/doctors/Doctors-131383/", "https://knowmore.co.il/doctors/אבי-צפריר/", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.tiktok.com/@szmcwebsite", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.szmc.org.il/departments/clinics-and-institutes/", "https://www.szmc.org.il/doctors/", "https://www.szmc.org.il/contact/", "https://www.szmc.org.il/about/tney-hashimush-baatar/", "https://www.szmc.org.il/doctors/merin-ofer/", "https://www.szmc.org.il/doctors/halevy-jonathan/", "https://www.szmc.org.il/doctors/blumberg-nehemia/", "https://www.szmc.org.il/about/about-us/#anchor-1", "https://www.szmc.org.il/about/about-us/#anchor-4", "https://www.szmc.org.il/about/units/pituach-mashabim-vekishrey-chutz/", "https://www.szmc.org.il/about/units/hanhalat-hasiud/", "https://www.szmc.org.il/about/units/agaf-ksafim/"]</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>2</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75504/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.baby-ivf.com/%D7%A6%D7%A8%D7%95-%D7%A7%D7%A9%D7%A8.html", "http://www.livecity.co.il/", "https://www.baby-ivf.com/About.html", "https://www.baby-ivf.com/Contact.html"]</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>אליזבטה שפריץ</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -801,7 +823,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yavne_office@mac.org.il</t>
+          <t>chertinb@szmc.org.il</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -814,7 +836,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=38E289452F7361F0752944377CCFD426FC1721FCE3529AC262E246A6A953B824&amp;RequestId=00000000-0000-0000-0001-000000000635</t>
+          <t>https://www.szmc.org.il/doctors/</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -824,15 +846,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>זבטה – נשים - גינקולוגיה יבנה גיבורי החיל 1/26 – איתור שירות | מכבי שירותי בריאות איתור שירות איתור שירות - ראשי רופאים/ות מעבדות, מכונים
-ומטפלים/ות משרדים מוקדי רפואה
-דחופה מרכזי ייעוץ וטיפול יום סדנאות מרכזים רפואיים מכבי פארם ובתי מרקחת מרפאות שיניים רפואה משלימה אופטומטריה דיור מוגן
-ואשפוז סיעודי חזרה לחיפוש הדפסה לאתר מכבי איתור שירות חיפוש רופאים/ות ד"ר שפריץ אליזבטה ד"ר שפריץ אליזבטה נשים - גינקולוגיה מס' רשיון : 1-135429 המתקן ממוגן תקנית וניתן בו שירות בהתאם לשעות הפעילות יש לתאם תור הת</t>
+          <t>"ר מאיר  פרנקל מנהל היחידה לאנדוקרינולוגיה, סוכרת ומטבוליזם meirf@szmc.org.il meirf@szmc.org.il מחלקה 02-6555111 מחלקה: 02-6555111 + + ד"ר סופיה פרנקל רופא תחומי + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה:</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>"אליזבטה שפריץ" יילוד גינקולוג</t>
+          <t>"אבי צפריר" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -842,29 +861,32 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "chernyn@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "י + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר מיכאל פשרסטניק רופא בכיר + + ד\"ר בשאר פתיחה מתמחה על + + ד\"ר  איליה צ'חנוביץ רופא בכיר + + ד\"ר נטליה צ'פל מתמחה על + + פרופ' בוריס צ'רטין מנ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "chertinb@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "\"ר מאיר  פרנקל מנהל היחידה לאנדוקרינולוגיה, סוכרת ומטבוליזם meirf@szmc.org.il meirf@szmc.org.il מחלקה 02-6555111 מחלקה: 02-6555111 + + ד\"ר סופיה פרנקל רופא תחומי + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה:", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "dmitryk@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": " הילד chertinb@szmc.org.il chertinb@szmc.org.il מחלקה 02-6666763 מחלקה: 02-6666763 + + פרופ'  טלי  צ'רנוביצקי רופאה בכירה + + פרופ' נתן צ'רני מנהל היחידה לטיפול תומך chernyn@szmc.org.il chernyn@szmc.org.il 02-6555682 02-6555682 + + ד\"ר  שמרית  צבי-בר רופאה בכירה shimrittb@szmc.org.il shimrittb@szmc.org.il + + פרופ' דויד  צדוק מנהל מחלקת עיניים deyes@szmc.org.il deyes@szmc.org.il 02-6555897 :  02-6555897 + + ד\"ר  בוריס צוקרמן מנהל יחידה לאנדוסקופיה גינקולוגית + + ד\"ר  בתיה  צוקרמן רופאה בכירה + +", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "ivfrec@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/tsafrir-avi/", "evidence": "אות הוראה תכנית הסטאז' בשערי צדק התמחות בית הספר האקדמי לאֲחָיוּת יחידת ההוראה לחינוך רפואי ספרייה רפואית מחקר הרשות למחקר ופיתוח ועדת הלסינקי תרומות יצירת קשר כל הזכויות שמורות © 2023 | חלק מן התמונות באדיבות יגאל סלבין Facebook Facebook YouTube YouTube twitter twitter Instagram Instagram Linkedin Linkedin Tiktok Tiktok נגישות נגישות עברית עברית עברית English عربيه Русский חיפוש מה אתם מחפשים? זימון תור מחלקות ויחידות הרופא.ה שלי הגעה והתמצאות נגישות עברית עברית עברית English عربيه Русский צרו ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.doctorita.co.il/experts/98793", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://drtor.co.il/doctor/735", "https://drtor.co.il/cdn-cgi/l/email-protection#a4c7cbcad0c5c7d0e4c0d6d0cbd68ac7cb8acdc8", "https://drtor.co.il/search/koopa/all/city/all/type/all/name/all/page/1", "https://drtor.co.il/doctor/11781", "https://drtor.co.il/doctor/11783", "https://drtor.co.il/cdn-cgi/l/email-protection#7d1e1213091c1e093d190f09120f531e12531411", "https://drtor.co.il/doctor/1", "https://drtor.co.il/doctor/2", "https://drtor.co.il/doctor/3", "https://drtor.co.il/doctor/4", "https://drtor.co.il/doctor/5", "https://drtor.co.il/doctor/6", "https://drtor.co.il/doctor/7", "https://drtor.co.il/doctor/8", "https://drtor.co.il/doctor/9", "https://drtor.co.il/doctor/10", "https://drtor.co.il/cdn-cgi/l/email-protection#ec8f8382988d8f98ac889e98839ec28f83c28580", "https://drtor.co.il/cdn-cgi/l/email-protection#5c3f3332283d3f281c382e28332e723f33723530", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=38E289452F7361F0752944377CCFD426FC1721FCE3529AC262E246A6A953B824&amp;RequestId=00000000-0000-0000-0001-000000000635", "https://www.maccabi4u.co.il/kosher", "https://go.serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%A9%D7%A4%D7%A8%D7%99%D7%A5%20%D7%90%D7%9C%D7%99%D7%96%D7%91%D7%98%D7%94", "https://go.serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=304485097&amp;ProviderProfession=1&amp;docClinic=4023089&amp;Service=1&amp;NewObjectId=70083756&amp;NewObjectType=S&amp;NewPerNr=90017266&amp;ol1=70083756&amp;ol2=S&amp;ol3=90017266&amp;isKosher=1&amp;beginDate=2026-08-31T21:51:34&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1"]</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>1</v>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.beok.co.il/doctors/Doctors-131383/", "https://knowmore.co.il/doctors/אבי-צפריר/", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.tiktok.com/@szmcwebsite", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.szmc.org.il/departments/clinics-and-institutes/", "https://www.szmc.org.il/doctors/", "https://www.szmc.org.il/contact/", "https://www.szmc.org.il/about/tney-hashimush-baatar/", "https://www.szmc.org.il/doctors/merin-ofer/", "https://www.szmc.org.il/doctors/halevy-jonathan/", "https://www.szmc.org.il/doctors/blumberg-nehemia/", "https://www.szmc.org.il/about/about-us/#anchor-1", "https://www.szmc.org.il/about/about-us/#anchor-4", "https://www.szmc.org.il/about/units/pituach-mashabim-vekishrey-chutz/", "https://www.szmc.org.il/about/units/hanhalat-hasiud/", "https://www.szmc.org.il/about/units/agaf-ksafim/"]</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>אמל תורעאני</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -889,7 +911,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>amalto@tlvmc.gov.il</t>
+          <t>dmitryk@szmc.org.il</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -902,7 +924,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/amal-tourani/</t>
+          <t>https://www.szmc.org.il/doctors/</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -912,12 +934,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>המטולוגיה פודקאסט שימו לב פודקאסט נוירולוגיה 1:1 פודקאסט וואלה אטמוספירה פגישות סגל 2026 פגישות סגל 25 פגישות סגל 23-24 פגישות סגל 21-22 הדרכה המטולוגיה מחויבים להעניק רפואה מובילה ואנושית באופן שווה לכל באמצעות טובי הרופאים והצוות הרפואי כולו, תוך הצטיינות בהוראה, מחקר ופיתוח ולמען בריאות כלל התושבים בארץ ובעולם. צור קשר עמותת הידידים עברית English العربية русский https://tasmc-search-82c272.ent.westeurope.azure.elastic-cloud.com tasmcprod search-zickmtrj5fe9qg3zgt8o8y2e /search-result/ /api/as</t>
+          <t xml:space="preserve"> הילד chertinb@szmc.org.il chertinb@szmc.org.il מחלקה 02-6666763 מחלקה: 02-6666763 + + פרופ'  טלי  צ'רנוביצקי רופאה בכירה + + פרופ' נתן צ'רני מנהל היחידה לטיפול תומך chernyn@szmc.org.il chernyn@szmc.org.il 02-6555682 02-6555682 + + ד"ר  שמרית  צבי-בר רופאה בכירה shimrittb@szmc.org.il shimrittb@szmc.org.il + + פרופ' דויד  צדוק מנהל מחלקת עיניים deyes@szmc.org.il deyes@szmc.org.il 02-6555897 :  02-6555897 + + ד"ר  בוריס צוקרמן מנהל יחידה לאנדוסקופיה גינקולוגית + + ד"ר  בתיה  צוקרמן רופאה בכירה + +</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>"אמל תורעאני" יילוד גינקולוג</t>
+          <t>"אבי צפריר" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -927,29 +949,32 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[{"email": "gen-c@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל", "matched_query": "\"אמל תורעאני\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"אמל תורעאני\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"אמל תורעאני\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+          <t>[{"email": "chernyn@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "י + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר מיכאל פשרסטניק רופא בכיר + + ד\"ר בשאר פתיחה מתמחה על + + ד\"ר  איליה צ'חנוביץ רופא בכיר + + ד\"ר נטליה צ'פל מתמחה על + + פרופ' בוריס צ'רטין מנ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "chertinb@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "\"ר מאיר  פרנקל מנהל היחידה לאנדוקרינולוגיה, סוכרת ומטבוליזם meirf@szmc.org.il meirf@szmc.org.il מחלקה 02-6555111 מחלקה: 02-6555111 + + ד\"ר סופיה פרנקל רופא תחומי + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה:", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "dmitryk@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": " הילד chertinb@szmc.org.il chertinb@szmc.org.il מחלקה 02-6666763 מחלקה: 02-6666763 + + פרופ'  טלי  צ'רנוביצקי רופאה בכירה + + פרופ' נתן צ'רני מנהל היחידה לטיפול תומך chernyn@szmc.org.il chernyn@szmc.org.il 02-6555682 02-6555682 + + ד\"ר  שמרית  צבי-בר רופאה בכירה shimrittb@szmc.org.il shimrittb@szmc.org.il + + פרופ' דויד  צדוק מנהל מחלקת עיניים deyes@szmc.org.il deyes@szmc.org.il 02-6555897 :  02-6555897 + + ד\"ר  בוריס צוקרמן מנהל יחידה לאנדוסקופיה גינקולוגית + + ד\"ר  בתיה  צוקרמן רופאה בכירה + +", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "ivfrec@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/tsafrir-avi/", "evidence": "אות הוראה תכנית הסטאז' בשערי צדק התמחות בית הספר האקדמי לאֲחָיוּת יחידת ההוראה לחינוך רפואי ספרייה רפואית מחקר הרשות למחקר ופיתוח ועדת הלסינקי תרומות יצירת קשר כל הזכויות שמורות © 2023 | חלק מן התמונות באדיבות יגאל סלבין Facebook Facebook YouTube YouTube twitter twitter Instagram Instagram Linkedin Linkedin Tiktok Tiktok נגישות נגישות עברית עברית עברית English عربيه Русский חיפוש מה אתם מחפשים? זימון תור מחלקות ויחידות הרופא.ה שלי הגעה והתמצאות נגישות עברית עברית עברית English عربيه Русский צרו ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P6" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.beok.co.il/doctors/Doctors-131383/", "https://knowmore.co.il/doctors/אבי-צפריר/", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.tiktok.com/@szmcwebsite", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.szmc.org.il/departments/clinics-and-institutes/", "https://www.szmc.org.il/doctors/", "https://www.szmc.org.il/contact/", "https://www.szmc.org.il/about/tney-hashimush-baatar/", "https://www.szmc.org.il/doctors/merin-ofer/", "https://www.szmc.org.il/doctors/halevy-jonathan/", "https://www.szmc.org.il/doctors/blumberg-nehemia/", "https://www.szmc.org.il/about/about-us/#anchor-1", "https://www.szmc.org.il/about/about-us/#anchor-4", "https://www.szmc.org.il/about/units/pituach-mashabim-vekishrey-chutz/", "https://www.szmc.org.il/about/units/hanhalat-hasiud/", "https://www.szmc.org.il/about/units/agaf-ksafim/"]</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
         <v>4</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://medpage.co.il/doctors/%D7%90%D7%9E%D7%9C-%D7%AA%D7%95%D7%A8%D7%A2%D7%90%D7%A0%D7%99-25696/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/", "https://www.tasmc.org.il/doctorssearch/dr/amal-tourani/", "https://www.tasmc.org.il/doctorssearch/dr/amal-tourani/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>אנה פטרוסב</t>
+          <t>אבי צפריר</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -974,7 +999,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>a_petruseva@rmc.gov.il</t>
+          <t>ivfrec@szmc.org.il</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -987,7 +1012,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D</t>
+          <t>https://www.szmc.org.il/doctors/tsafrir-avi/</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -997,44 +1022,47 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>דואר אלקטרוני ד"ר אנה פטרוסב [email protected]</t>
+          <t xml:space="preserve">אות הוראה תכנית הסטאז' בשערי צדק התמחות בית הספר האקדמי לאֲחָיוּת יחידת ההוראה לחינוך רפואי ספרייה רפואית מחקר הרשות למחקר ופיתוח ועדת הלסינקי תרומות יצירת קשר כל הזכויות שמורות © 2023 | חלק מן התמונות באדיבות יגאל סלבין Facebook Facebook YouTube YouTube twitter twitter Instagram Instagram Linkedin Linkedin Tiktok Tiktok נגישות נגישות עברית עברית עברית English عربيه Русский חיפוש מה אתם מחפשים? זימון תור מחלקות ויחידות הרופא.ה שלי הגעה והתמצאות נגישות עברית עברית עברית English عربيه Русский צרו </t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>"אנה פטרוסב" מרפאה פרטית</t>
+          <t>"אבי צפריר" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[{"email": "ks.m@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/contact-for-doctors/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "officeks@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "office@sharapplus.co.il", "confidence": 75, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+          <t>[{"email": "chernyn@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "י + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר מיכאל פשרסטניק רופא בכיר + + ד\"ר בשאר פתיחה מתמחה על + + ד\"ר  איליה צ'חנוביץ רופא בכיר + + ד\"ר נטליה צ'פל מתמחה על + + פרופ' בוריס צ'רטין מנ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "chertinb@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": "\"ר מאיר  פרנקל מנהל היחידה לאנדוקרינולוגיה, סוכרת ומטבוליזם meirf@szmc.org.il meirf@szmc.org.il מחלקה 02-6555111 מחלקה: 02-6555111 + + ד\"ר סופיה פרנקל רופא תחומי + + פרופ'  רונן פרץ מנהל היחידה לאוטולוגיה (מחלות וניתוחי האוזן) | מנהל המרכז לשתל השבלול מחלקה 02-6555360 מחלקה: 02-6555360 + + ד\"ר  אדם  פרקש מנהל יחידת אנגיוגרפיה adamf@szmc.org.il adamf@szmc.org.il מחלקה 02-6555014 מחלקה: 02-6555014 + + ד\"ר  אנטוני  פרשטנדיג רופא בכיר anthonyv@szmc.org.il anthonyv@szmc.org.il מחלקה 02-6555014 מחלקה:", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "dmitryk@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/", "evidence": " הילד chertinb@szmc.org.il chertinb@szmc.org.il מחלקה 02-6666763 מחלקה: 02-6666763 + + פרופ'  טלי  צ'רנוביצקי רופאה בכירה + + פרופ' נתן צ'רני מנהל היחידה לטיפול תומך chernyn@szmc.org.il chernyn@szmc.org.il 02-6555682 02-6555682 + + ד\"ר  שמרית  צבי-בר רופאה בכירה shimrittb@szmc.org.il shimrittb@szmc.org.il + + פרופ' דויד  צדוק מנהל מחלקת עיניים deyes@szmc.org.il deyes@szmc.org.il 02-6555897 :  02-6555897 + + ד\"ר  בוריס צוקרמן מנהל יחידה לאנדוסקופיה גינקולוגית + + ד\"ר  בתיה  צוקרמן רופאה בכירה + +", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "ivfrec@szmc.org.il", "confidence": 100, "source_url": "https://www.szmc.org.il/doctors/tsafrir-avi/", "evidence": "אות הוראה תכנית הסטאז' בשערי צדק התמחות בית הספר האקדמי לאֲחָיוּת יחידת ההוראה לחינוך רפואי ספרייה רפואית מחקר הרשות למחקר ופיתוח ועדת הלסינקי תרומות יצירת קשר כל הזכויות שמורות © 2023 | חלק מן התמונות באדיבות יגאל סלבין Facebook Facebook YouTube YouTube twitter twitter Instagram Instagram Linkedin Linkedin Tiktok Tiktok נגישות נגישות עברית עברית עברית English عربيه Русский חיפוש מה אתם מחפשים? זימון תור מחלקות ויחידות הרופא.ה שלי הגעה והתמצאות נגישות עברית עברית עברית English عربيه Русский צרו ", "matched_query": "\"אבי צפריר\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://sharapplus.co.il/doctors/anna-petruseva/", "https://sharapplus.co.il/terms-and-conditions/", "https://sharapplus.co.il/all-doctors/", "https://sharapplus.co.il/contact-for-doctors/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#f19e9797989294b1829990839081819d8482df929edf989d", "https://sharapplus.co.il/cdn-cgi/l/email-protection#84ebe2e2ede7e1c4f7ece5f6e5f4f4e8f1f7aae7ebaaede8", "https://sharapplus.co.il/about/", "https://sharapplus.co.il/contact-us/", "https://sharapplus.co.il/doctors/%D7%98%D7%9C%D7%99-%D7%90%D7%A0%D7%92%D7%95%D7%A8/", "https://sharapplus.co.il/doctors/moaad-slieman/", "https://sharapplus.co.il/doctors/dr_eti_fiora/", "https://sharapplus.co.il/doctors/dr_manevitz/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%90%D7%99%D7%A8-%D7%A7%D7%A1%D7%98%D7%A0%D7%91%D7%90%D7%95%D7%9D/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%A8%D7%96/", "https://sharapplus.co.il/doctors/nail-abaya/", "https://sharapplus.co.il/doctors/med-balance-institute/", "https://sharapplus.co.il/doctors/nahum-eliyahu/", "https://sharapplus.co.il/doctors/eyal-zipman/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#551e067b3815263d34273425253920267b363a7b3c39", "https://sharapplus.co.il/cdn-cgi/l/email-protection", "https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/entandheadandnecksurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/ambulatory_operating_room/", "https://www.rambam.org.il/departmentsandclinics/trauma-and-emergency-surgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/generalsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/breastsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/vascularsurgeryandtransplantation/"]</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>1</v>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>["https://www.infomed.co.il/experts/73913/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.beok.co.il/doctors/Doctors-131383/", "https://knowmore.co.il/doctors/אבי-צפריר/", "https://www.szmc.org.il/doctors/tsafrir-avi/", "https://www.tiktok.com/@szmcwebsite", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.szmc.org.il/departments/clinics-and-institutes/", "https://www.szmc.org.il/doctors/", "https://www.szmc.org.il/contact/", "https://www.szmc.org.il/about/tney-hashimush-baatar/", "https://www.szmc.org.il/doctors/merin-ofer/", "https://www.szmc.org.il/doctors/halevy-jonathan/", "https://www.szmc.org.il/doctors/blumberg-nehemia/", "https://www.szmc.org.il/about/about-us/#anchor-1", "https://www.szmc.org.il/about/about-us/#anchor-4", "https://www.szmc.org.il/about/units/pituach-mashabim-vekishrey-chutz/", "https://www.szmc.org.il/about/units/hanhalat-hasiud/", "https://www.szmc.org.il/about/units/agaf-ksafim/"]</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>אסנת גרוץ</t>
+          <t>אבישג שמחה אבקסיס</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1059,7 +1087,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>asnatg@tlvmc.gov.il</t>
+          <t>avishaga@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1072,7 +1100,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/garuz-osnat/</t>
+          <t>https://www.bgu.ac.il/ar/people/avishaga/</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1082,12 +1110,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ך - פרופסור חבר קליני, בית הספר לרפואה ע"ש סאקלר, אוניברסיטת תל אביב 2002-2011 מרצה בכירה, בית הספר לרפואה ע"ש סאקלר, אוניברסיטת תל אביב פרסומים מקצועיים ​מעל 100 פרסומים בנושאי אורוגינקולוגיה ורצפת אגן בכתבי עת מקצועיים בינלאומיים רשימת פרסומים באתר PUBMED חברות באיגודים מקצועיים ההסתדרות הרפואית האיגוד הישראלי לגינקולוגיה ומיילדות האיגוד הישראלי לאורוגינקולוגיה איגודים מקצועיים בינלאומיים:  ICS, AUA, SUFU, IUGA שטחי התעניינות ועיסוק מיוחדים ​דליפת שתן צניחת אברי אגן זיהומים בשתן ניתוחי שיקום ר</t>
+          <t>التسجيل شروط القبول للقب الأول معلومات شخصية للذين سجلوا للتعليم إجراءات دفع الرسوم الدراسية الأسئلة المتداولة حول الرسوم الدراسية عمادة شؤون الطلبة خدمات تُقدم لطلبة عمادة شؤون الطلاب قسم الخدمات للطلاب العرب منح دراسية وقروض قسم الخدمات النفسية للطلاب مركز التوجيه المهني أصحاب الوظائف مساعدة في قضايا اكاديمية خدمات مركز الدعم خدمات لطلاب مع إعاقة جسدية دائمة او مؤقتة معهد تشخيص وظائف تعليمية تسهيلات في حال الحمل والولادة ماذا كنت تريد البحث عنه؟ ماذا كنت تريد البحث عنه؟ الصفحة الرئيسية جامعة أ</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>"אסנת גרוץ" יילוד גינקולוג</t>
+          <t>"אבישג שמחה אבקסיס" צור קשר מרפאה</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1097,29 +1125,32 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[{"email": "gen-c@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל", "matched_query": "\"אסנת גרוץ\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"אסנת גרוץ\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"אסנת גרוץ\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אסנת גרוץ\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctors.assuta.co.il/doctor/osnat-groutz-21406?readmore=true", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=BAC416C76666AA9839921027807F370D31B95A90A98BBF38FC3ED4D51A7FB863&amp;RequestId=00000000-0000-0000-0001-000000000300", "https://www.maccabi4u.co.il/kosher", "https://go.serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%92%D7%A8%D7%95%D7%A5%20%D7%90%D7%A1%D7%A0%D7%AA", "https://go.serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=57323214&amp;ProviderProfession=W&amp;docClinic=74053&amp;Service=1&amp;NewObjectId=70028074&amp;NewObjectType=S&amp;NewPerNr=90002206&amp;ol1=70028074&amp;ol2=S&amp;ol3=90002206&amp;isKosher=1&amp;beginDate=2026-09-01T01:25:02&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.infomed.co.il/experts/93699/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.tasmc.org.il/doctorssearch/dr/garuz-osnat/", "https://www.tasmc.org.il/doctorssearch/dr/garuz-osnat/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>["https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx", "https://www.clalit.co.il/he/sefersherut/pages/clinicdetails.aspx", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A9%D7%92-%D7%A9%D7%9E%D7%97%D7%94-%D7%90%D7%91%D7%A7%D7%A1%D7%99%D7%A1-19278/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/", "https://drtor.co.il/doctor/19865", "https://www.bgu.ac.il/people/avishaga/", "https://www.bgu.ac.il/en/people/avishaga/", "https://knowmore.co.il/doctors/אבישג-שמחה-אבקסיס-2/", "https://knowmore.co.il/doctors/אבישג-שמחה-אבקסיס-4/", "https://www.bgu.ac.il/ar/people/avishaga/", "https://www.yazamut360.bgu.ac.il/?utm_campaign=alongtheyear&amp;utm_medium=BGUwebsite&amp;utm_source=BGUwebsite&amp;utm_term=Botton&amp;utm_content=Botton", "https://www.bgu.ac.il/ar/general/registration-website/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>אלון טל</t>
+          <t>אבי בן-הרוש</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1144,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>dralontal@gmail.com</t>
+          <t>baruchik@tauex.tau.ac.il</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1153,11 +1184,11 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://dr-alontal.co.il/</t>
+          <t>https://med.tau.ac.il/Information_for_dentists</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1167,44 +1198,47 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בתהליך. קטלוג האתר שירותי העסק בלוג ומאמרים אודות ד״ר אלון טל כירורגיה גינקולוגית ואונקולוגית ד״ר אלון טל מתמחה בכירורגיה גינקולוגית ואונקולוגית ומנהל מרפאה גינקולוגית מתקדמת בחיפה. המרפאה מציעה שירותים מקצועיים בתחום הגינקולוגיה והגינקואונקולוגיה, לרבות ייעוץ גינקולוגי, ניתוחים מתקדמים, מרפאת צוואר הרחם, קולפוסקופיה, היסטרוסקופיות וקוניזציה של צוואר הרחם. המרפאה מספקת מענה רפואי מקיף לנשים מכל רחבי הארץ, בשיתוף פעולה עם קופות החולים מכבי, מאוחדת וכללית וביטוחים פרטיים, תוך הקפדה על איכות הטיפו</t>
+          <t>ברוך קסנטיני baruchik@tauex.tau.ac.il 03-6409187/5980</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>"אלון טל" יילוד גינקולוג</t>
+          <t>"אבי בן-הרוש" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>mailto</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אלון טל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[{"email": "baruchik@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/Information_for_dentists", "evidence": "ברוך קסנטיני baruchik@tauex.tau.ac.il 03-6409187/5980", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "erezavis@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "galavishai@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "haniabutziam@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>["https://www.doctorim.co.il/doctor-35894/פרופ-אבי-בןהרוש/מומחה-יילוד-וגניקולוגיה", "https://med.tau.ac.il/profile/avibenh", "http://www.avibh.co.il", "https://med.tau.ac.il/HR-%20academic-staff-2019", "https://med.tau.ac.il/info-HR-administration-new-staff-2019", "https://med.tau.ac.il/research-projects-staff-2019", "https://med.tau.ac.il/HR-%20academic-new-staff-2019", "https://med.tau.ac.il/staff-faculty-of-medicine", "https://med.tau.ac.il/profile/avibenh#anchor_general_info", "https://med.tau.ac.il/profile/avibenh#anchor_cv", "https://med.tau.ac.il/profile/avibenh#anchor_publications", "http://new.tau.ac.il/about", "https://medicine-cms.tau.ac.il/HR- academic-staff-2019", "https://med.tau.ac.il/Information_for_dentists", "https://medicine-cms.tau.ac.il/HR- academic-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-pre-clinical-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-administrativ-new-staff-2019", "https://medicine-cms.tau.ac.il/new-research-projects-staff-2019", "https://medicine-cms.tau.ac.il/HR-junior-acdemic-staff-2019", "https://med.tau.ac.il/info-pre-clinical-researcers-2019", "https://med.tau.ac.il/info-pre-clinical-teachers-2019"]</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
         <v>2</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/153548/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://dr-alontal.co.il/", "https://dr-alontal.co.il/about"]</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>אלון קדם</t>
+          <t>אבי בן-הרוש</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1229,7 +1263,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>doctorkedem@gmail.com</t>
+          <t>erezavis@tauex.tau.ac.il</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1238,11 +1272,11 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.kedemalon.co.il/</t>
+          <t>https://med.tau.ac.il/staff-faculty-of-medicine</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1250,46 +1284,45 @@
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ים לא שגרתיים בכל שאלה ותהיה שהיתה לי וידע תמיד לתת מענה מקצועי ואישי. להריון הראשון נכנסנו לאחר סבב הטיפולים השני ולאחר 9 חודשים נולדה לנו בת מדהימה, לאורך כל ההריון דוקטור קדם ליווה אותנו דרך כל הפחדים והלבטים שכל מי שעבר אינספור נסיונות כושלים וודאי מכיר. לאחר שנתיים, כשהחלטנו שאנחנו מוכנים לעוד 'תוספת' למשפחה, מיד חזרנו לד'ר קדם והפעם הוא הצליח אפילו יותר – ונכנסנו להריון כבר אחרי סבב טיפולים בודד. בתהליך הכל כך קשה ומורכב שעברנו עם אינספור טיפולים וגם הפלות ד'ר קדם היה האדם שהחזיר לנו את הא</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>"אלון קדם" יילוד גינקולוג</t>
+          <t>"אבי בן-הרוש" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>mailto</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[{"email": "info@medico.co.il", "confidence": 95, "source_url": "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%A7%D7%93%D7%9D/", "evidence": "כז, השרון חברות ביטוח: פרטי 5.0/5 1 גולשים דירגו מעוניינים לדרג את ד\"ר אלון קדם במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד\"ר אלון קדם רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. שימור פוריות: מתי מומלץ להקפיא ביציות- סטטוסקופ להתייעצות עם ד\"ר אלון קדם השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל", "matched_query": "\"אלון קדם\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+          <t>[{"email": "baruchik@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/Information_for_dentists", "evidence": "ברוך קסנטיני baruchik@tauex.tau.ac.il 03-6409187/5980", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "erezavis@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "galavishai@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "haniabutziam@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.kedemalon.co.il/", "https://www.waze.com/live-map/directions/il/tel-aviv-district/herzliya/ramat-yam-st-4?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.ChIJc2kUjZtIHRURffNez5FjSTo", "https://www.waze.com/live-map/directions/il/tel-aviv-district/%D7%A8%D7%92/shalem-st-3?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.ChIJ48cAeANLHRURhP10NlTZb-k", "https://www.kedemalon.co.il/about", "https://www.kedemalon.co.il/contact", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%A7%D7%93%D7%9D/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%94%D7%A8%D7%A6%D7%9C%D7%99%D7%94/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>1</v>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>["https://www.doctorim.co.il/doctor-35894/פרופ-אבי-בןהרוש/מומחה-יילוד-וגניקולוגיה", "https://med.tau.ac.il/profile/avibenh", "http://www.avibh.co.il", "https://med.tau.ac.il/HR-%20academic-staff-2019", "https://med.tau.ac.il/info-HR-administration-new-staff-2019", "https://med.tau.ac.il/research-projects-staff-2019", "https://med.tau.ac.il/HR-%20academic-new-staff-2019", "https://med.tau.ac.il/staff-faculty-of-medicine", "https://med.tau.ac.il/profile/avibenh#anchor_general_info", "https://med.tau.ac.il/profile/avibenh#anchor_cv", "https://med.tau.ac.il/profile/avibenh#anchor_publications", "http://new.tau.ac.il/about", "https://medicine-cms.tau.ac.il/HR- academic-staff-2019", "https://med.tau.ac.il/Information_for_dentists", "https://medicine-cms.tau.ac.il/HR- academic-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-pre-clinical-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-administrativ-new-staff-2019", "https://medicine-cms.tau.ac.il/new-research-projects-staff-2019", "https://medicine-cms.tau.ac.il/HR-junior-acdemic-staff-2019", "https://med.tau.ac.il/info-pre-clinical-researcers-2019", "https://med.tau.ac.il/info-pre-clinical-teachers-2019"]</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>אריאל זילברליכט</t>
+          <t>אבי בן-הרוש</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1314,7 +1347,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>arielzilberlicht@gmail.com</t>
+          <t>galavishai@tauex.tau.ac.il</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1323,11 +1356,11 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://doctor-ariel.co.il/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA/</t>
+          <t>https://med.tau.ac.il/staff-faculty-of-medicine</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1335,131 +1368,129 @@
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> גיל המעבר אסתטיקה גינקולוגית אודות בלוג מתוך התקשורת יצירת קשר דף הבית שירותי המרפאה גינקולוגיה כללית אורוגינקולוגיה גיל המעבר אסתטיקה גינקולוגית אודות בלוג מתוך התקשורת יצירת קשר 073-3990235 להזמנת תור דף הבית שירותי המרפאה גינקולוגיה כללית אורוגינקולוגיה גיל המעבר אסתטיקה גינקולוגית אודות בלוג מתוך התקשורת יצירת קשר דף הבית שירותי המרפאה גינקולוגיה כללית אורוגינקולוגיה גיל המעבר אסתטיקה גינקולוגית אודות בלוג מתוך התקשורת יצירת קשר דף הבית שירותי המרפאה גינקולוגיה כללית אורוגינקולוגיה גיל המעב</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>"אריאל זילברליכט" יילוד גינקולוג</t>
+          <t>"אבי בן-הרוש" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>mailto</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>[{"email": "doctor.zilberlicht@gmail.com", "confidence": 95, "source_url": "https://doctor-ariel.co.il/", "evidence": "צמוד, החל משלב התשאול הראשוני, ביצוע ניתוחים ועד לסיום המעקבים לאחר הטיפול. להמשך קריאה אני מאמין: רפואה בגובה העיניים​ הזכות ללוות נשים בכל אחד משלבי חייהן צופנת בחובה אחריות כבדה מאוד. הגישה שלי מבוססת על אוזן קשבת, הישרת מבט ומתן אפשרות לכל מטופלת לספר את סיפורה בקצב שלה. המפגש עם רופא הנשים חייב להיות מכבד, לא שיפוטי ומותאם אישית בשפה ברורה. אני סבור כי תחושת הביטחון והאמון של המטופלת הן בעלות חשיבות מכרעת להצלחת הטיפול הרפואי. שירותי המרפאה גינקולוגיה אורוגינקולוגיה גיל המעבר אסתטיקה גינקול", "matched_query": "\"אריאל זילברליכט\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+          <t>[{"email": "baruchik@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/Information_for_dentists", "evidence": "ברוך קסנטיני baruchik@tauex.tau.ac.il 03-6409187/5980", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "erezavis@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "galavishai@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "haniabutziam@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctor-ariel.co.il/", "https://yosseftiran.com/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%90%D7%95%D7%A8%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%92%D7%99%D7%9C-%D7%94%D7%9E%D7%A2%D7%91%D7%A8/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%90%D7%A1%D7%AA%D7%98%D7%99%D7%A7%D7%94-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://doctor-ariel.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://doctor-ariel.co.il/%D7%91%D7%9C%D7%95%D7%92/", "https://doctor-ariel.co.il/%D7%9E%D7%9F-%D7%94%D7%AA%D7%A7%D7%A9%D7%95%D7%A8%D7%AA/", "https://doctor-ariel.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://doctor-ariel.co.il/%d7%a9%d7%99%d7%a8%d7%95%d7%aa%d7%99-%d7%94%d7%9e%d7%a8%d7%a4%d7%90%d7%94/%d7%92%d7%99%d7%a0%d7%a7%d7%95%d7%9c%d7%95%d7%92%d7%99%d7%94/", "https://doctor-ariel.co.il/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA/", "https://doctor-ariel.co.il/%d7%a9%d7%99%d7%a8%d7%95%d7%aa%d7%99-%d7%94%d7%9e%d7%a8%d7%a4%d7%90%d7%94/%d7%90%d7%95%d7%a8%d7%95%d7%92%d7%99%d7%a0%d7%a7%d7%95%d7%9c%d7%95%d7%92%d7%99%d7%94/%d7%a6%d7%a0%d7%99%d7%97%d7%aa-%d7%a8%d7%97%d7%9d/", "https://doctor-ariel.co.il/wp-content/uploads/2022/04/updated-CV-nov-2021.pdf", "https://doctor-ariel.co.il/dr-zilberlicht-clinic-faq/"]</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>1</v>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>["https://www.doctorim.co.il/doctor-35894/פרופ-אבי-בןהרוש/מומחה-יילוד-וגניקולוגיה", "https://med.tau.ac.il/profile/avibenh", "http://www.avibh.co.il", "https://med.tau.ac.il/HR-%20academic-staff-2019", "https://med.tau.ac.il/info-HR-administration-new-staff-2019", "https://med.tau.ac.il/research-projects-staff-2019", "https://med.tau.ac.il/HR-%20academic-new-staff-2019", "https://med.tau.ac.il/staff-faculty-of-medicine", "https://med.tau.ac.il/profile/avibenh#anchor_general_info", "https://med.tau.ac.il/profile/avibenh#anchor_cv", "https://med.tau.ac.il/profile/avibenh#anchor_publications", "http://new.tau.ac.il/about", "https://medicine-cms.tau.ac.il/HR- academic-staff-2019", "https://med.tau.ac.il/Information_for_dentists", "https://medicine-cms.tau.ac.il/HR- academic-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-pre-clinical-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-administrativ-new-staff-2019", "https://medicine-cms.tau.ac.il/new-research-projects-staff-2019", "https://medicine-cms.tau.ac.il/HR-junior-acdemic-staff-2019", "https://med.tau.ac.il/info-pre-clinical-researcers-2019", "https://med.tau.ac.il/info-pre-clinical-teachers-2019"]</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>אבי בן-הרוש</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>haniabutziam@tauex.tau.ac.il</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>90</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://med.tau.ac.il/staff-faculty-of-medicine</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>"אבי בן-הרוש" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>[{"email": "baruchik@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/Information_for_dentists", "evidence": "ברוך קסנטיני baruchik@tauex.tau.ac.il 03-6409187/5980", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "erezavis@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "galavishai@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}, {"email": "haniabutziam@tauex.tau.ac.il", "confidence": 90, "source_url": "https://med.tau.ac.il/staff-faculty-of-medicine", "evidence": "", "matched_query": "\"אבי בן-הרוש\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>["https://www.doctorim.co.il/doctor-35894/פרופ-אבי-בןהרוש/מומחה-יילוד-וגניקולוגיה", "https://med.tau.ac.il/profile/avibenh", "http://www.avibh.co.il", "https://med.tau.ac.il/HR-%20academic-staff-2019", "https://med.tau.ac.il/info-HR-administration-new-staff-2019", "https://med.tau.ac.il/research-projects-staff-2019", "https://med.tau.ac.il/HR-%20academic-new-staff-2019", "https://med.tau.ac.il/staff-faculty-of-medicine", "https://med.tau.ac.il/profile/avibenh#anchor_general_info", "https://med.tau.ac.il/profile/avibenh#anchor_cv", "https://med.tau.ac.il/profile/avibenh#anchor_publications", "http://new.tau.ac.il/about", "https://medicine-cms.tau.ac.il/HR- academic-staff-2019", "https://med.tau.ac.il/Information_for_dentists", "https://medicine-cms.tau.ac.il/HR- academic-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-pre-clinical-new-staff-2019", "https://medicine-cms.tau.ac.il/HR-administrativ-new-staff-2019", "https://medicine-cms.tau.ac.il/new-research-projects-staff-2019", "https://medicine-cms.tau.ac.il/HR-junior-acdemic-staff-2019", "https://med.tau.ac.il/info-pre-clinical-researcers-2019", "https://med.tau.ac.il/info-pre-clinical-teachers-2019"]</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>5</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>אריאל זילברליכט</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>gynecologist</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>doctor.zilberlicht@gmail.com</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PERSONAL_PROFESSIONAL</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>95</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>https://doctor-ariel.co.il/</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>צמוד, החל משלב התשאול הראשוני, ביצוע ניתוחים ועד לסיום המעקבים לאחר הטיפול. להמשך קריאה אני מאמין: רפואה בגובה העיניים​ הזכות ללוות נשים בכל אחד משלבי חייהן צופנת בחובה אחריות כבדה מאוד. הגישה שלי מבוססת על אוזן קשבת, הישרת מבט ומתן אפשרות לכל מטופלת לספר את סיפורה בקצב שלה. המפגש עם רופא הנשים חייב להיות מכבד, לא שיפוטי ומותאם אישית בשפה ברורה. אני סבור כי תחושת הביטחון והאמון של המטופלת הן בעלות חשיבות מכרעת להצלחת הטיפול הרפואי. שירותי המרפאה גינקולוגיה אורוגינקולוגיה גיל המעבר אסתטיקה גינקול</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>"אריאל זילברליכט" יילוד גינקולוג</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>[{"email": "doctor.zilberlicht@gmail.com", "confidence": 95, "source_url": "https://doctor-ariel.co.il/", "evidence": "צמוד, החל משלב התשאול הראשוני, ביצוע ניתוחים ועד לסיום המעקבים לאחר הטיפול. להמשך קריאה אני מאמין: רפואה בגובה העיניים​ הזכות ללוות נשים בכל אחד משלבי חייהן צופנת בחובה אחריות כבדה מאוד. הגישה שלי מבוססת על אוזן קשבת, הישרת מבט ומתן אפשרות לכל מטופלת לספר את סיפורה בקצב שלה. המפגש עם רופא הנשים חייב להיות מכבד, לא שיפוטי ומותאם אישית בשפה ברורה. אני סבור כי תחושת הביטחון והאמון של המטופלת הן בעלות חשיבות מכרעת להצלחת הטיפול הרפואי. שירותי המרפאה גינקולוגיה אורוגינקולוגיה גיל המעבר אסתטיקה גינקול", "matched_query": "\"אריאל זילברליכט\" יילוד גינקולוג", "extraction_method": "text"}]</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctor-ariel.co.il/", "https://yosseftiran.com/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%90%D7%95%D7%A8%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%92%D7%99%D7%9C-%D7%94%D7%9E%D7%A2%D7%91%D7%A8/", "https://doctor-ariel.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/%D7%90%D7%A1%D7%AA%D7%98%D7%99%D7%A7%D7%94-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://doctor-ariel.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://doctor-ariel.co.il/%D7%91%D7%9C%D7%95%D7%92/", "https://doctor-ariel.co.il/%D7%9E%D7%9F-%D7%94%D7%AA%D7%A7%D7%A9%D7%95%D7%A8%D7%AA/", "https://doctor-ariel.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://doctor-ariel.co.il/%d7%a9%d7%99%d7%a8%d7%95%d7%aa%d7%99-%d7%94%d7%9e%d7%a8%d7%a4%d7%90%d7%94/%d7%92%d7%99%d7%a0%d7%a7%d7%95%d7%9c%d7%95%d7%92%d7%99%d7%94/", "https://doctor-ariel.co.il/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA/", "https://doctor-ariel.co.il/%d7%a9%d7%99%d7%a8%d7%95%d7%aa%d7%99-%d7%94%d7%9e%d7%a8%d7%a4%d7%90%d7%94/%d7%90%d7%95%d7%a8%d7%95%d7%92%d7%99%d7%a0%d7%a7%d7%95%d7%9c%d7%95%d7%92%d7%99%d7%94/%d7%a6%d7%a0%d7%99%d7%97%d7%aa-%d7%a8%d7%97%d7%9d/", "https://doctor-ariel.co.il/wp-content/uploads/2022/04/updated-CV-nov-2021.pdf", "https://doctor-ariel.co.il/dr-zilberlicht-clinic-faq/"]</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>אמיר רבהון</t>
+          <t>אביטל ורטהיימר</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1484,7 +1515,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ravhon.clinic@gmail.com</t>
+          <t>avital.wer@gmail.com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1497,7 +1528,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.dr-ravhon.co.il/</t>
+          <t>https://www.dravitalwertheimer.com/contact</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1507,12 +1538,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ד"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצירת קשר תפריט דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת בי</t>
+          <t>צור קשר | Dr Avital Wertheimer top of page צור קשר מעקבי הריון ומעקב גניקולוגי שוטף אבחון וטיפול בתת פוריות הפריה חוץ גופית הזרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>"אמיר רבהון" יילוד גינקולוג</t>
+          <t>"אביטל ורטהיימר" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1522,29 +1553,32 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>[{"email": "ravhon.clinic@gmail.com", "confidence": 90, "source_url": "https://www.dr-ravhon.co.il/", "evidence": "ד\"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצירת קשר תפריט דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת בי", "matched_query": "\"אמיר רבהון\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+          <t>[{"email": "sec101@bri.co.il", "confidence": 90, "source_url": "https://www.dravitalwertheimer.com/contact", "evidence": "צור קשר | Dr Avital Wertheimer top of page צור קשר מעקבי הריון ומעקב גניקולוגי שוטף אבחון וטיפול בתת פוריות הפריה חוץ גופית הזרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז", "matched_query": "\"אביטל ורטהיימר\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9E%D7%99%D7%A8-%D7%A8%D7%91%D7%94%D7%95%D7%9F/", "https://www.dr-ravhon.co.il/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%A8%D7%97%D7%95%D7%91%D7%95%D7%AA/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>2</v>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_a_wertheimer.aspx", "https://www.medreviews.co.il/provider/dr-wertheimer-avital", "https://www.dravitalwertheimer.com/", "https://www.medreviews.co.il/provider/dr-wertheimer-avital#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://www.dravitalwertheimer.com/contact"]</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>איתי גת</t>
+          <t>אביטל ורטהיימר</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1569,7 +1603,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>itaigatclinic@gmail.com</t>
+          <t>sec101@bri.co.il</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1582,7 +1616,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://prof-itaigat.co.il/</t>
+          <t>https://www.dravitalwertheimer.com/contact</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1592,12 +1626,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ני וטיפולים רפואיים מתישים אלא גם בהתמודדות רגשית מורכב ביותר בהיבטים מגוונים -אישי, זוגי, משפחתי וחברתי. הטכנולוגיה הרפואית אמנם מאפשרת השגת הריון ולידה במרבית המקרים אולם לעיתים קרובות מחייבת התמדה וסבלנות וגם יכולות להתמודד עם חוסר הצלחה עד השגת התוצאה המיוחלת. רופא פוריות חייב בעיני להיות בעל שילוב תכונות. נדרשת מקצוענות מהשורה הראשונה, דיוק וקפדנות בפרטי הטיפול תוך התעדכנות שוטפת בחידושים הרפואיים. בנוסף יש צורך לשמור על הפרספקטיבה הרחבה – לראות את מכלול התמונה של שני בני הזוג ונתוניהם הביו</t>
+          <t>צור קשר | Dr Avital Wertheimer top of page צור קשר מעקבי הריון ומעקב גניקולוגי שוטף אבחון וטיפול בתת פוריות הפריה חוץ גופית הזרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>"איתי גת" יילוד גינקולוג</t>
+          <t>"אביטל ורטהיימר" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1607,29 +1641,32 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"איתי גת\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[{"email": "sec101@bri.co.il", "confidence": 90, "source_url": "https://www.dravitalwertheimer.com/contact", "evidence": "צור קשר | Dr Avital Wertheimer top of page צור קשר מעקבי הריון ומעקב גניקולוגי שוטף אבחון וטיפול בתת פוריות הפריה חוץ גופית הזרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז", "matched_query": "\"אביטל ורטהיימר\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/איתי-גת", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%AA-%D7%90%D7%99%D7%AA%D7%99/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://doctors.assuta.co.il/search/doctor/itai-gat-38246", "https://www.facebook.com/itaigatfertility/", "https://www.infomed.co.il/experts/146101/", "https://prof-itaigat.co.il/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/146101/#clinics", "https://www.infomed.co.il/experts/146101/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>1</v>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_a_wertheimer.aspx", "https://www.medreviews.co.il/provider/dr-wertheimer-avital", "https://www.dravitalwertheimer.com/", "https://www.medreviews.co.il/provider/dr-wertheimer-avital#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://www.dravitalwertheimer.com/contact"]</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>אנה פטרוסב</t>
+          <t>אביעד כהן</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1654,7 +1691,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ks.m@sharapplus.co.il</t>
+          <t>aviadc@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1663,11 +1700,11 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://sharapplus.co.il/contact-for-doctors/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1677,44 +1714,47 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>ה ופריון השתלמויות ​2016-2017 תת-התמחות קלינית בכירורגיה אנדוסקופית, אונברסיטת מקגייל, מונטראול, קנדה. ניסיון קליני 2015-2016 רופא בכיר, מחלקת נשים, ביה"ח ליס, המרכז הרפואי תל-אביב 2016-2017 תת-התמחות קלינית בכירורגיה אנדוסקופית, אונברסיטת מקגייל, מונטראול, קנדה. 2017- סגן מנהל בכיר, מחלקת נשים, ביה"ח ליס, המרכז הרפואי תל-אביב פרסומים מקצועיים ​כ- 26 פרסומים מקצועיים רשימת הפרסומים כפי שמופיעה באתר Pubmed חברות באיגודים מקצועיים האיגוד הישראלי למיילדות וגינקולוגיה האיגוד הישראלי לאנדוסקופיה גינק</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>"אנה פטרוסב" מרפאה פרטית</t>
+          <t>"אביעד כהן" צור קשר מרפאה</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[{"email": "ks.m@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/contact-for-doctors/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "officeks@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "office@sharapplus.co.il", "confidence": 75, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+          <t>[{"email": "gen-c@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}, {"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P15" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://sharapplus.co.il/doctors/anna-petruseva/", "https://sharapplus.co.il/terms-and-conditions/", "https://sharapplus.co.il/all-doctors/", "https://sharapplus.co.il/contact-for-doctors/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#f19e9797989294b1829990839081819d8482df929edf989d", "https://sharapplus.co.il/cdn-cgi/l/email-protection#84ebe2e2ede7e1c4f7ece5f6e5f4f4e8f1f7aae7ebaaede8", "https://sharapplus.co.il/about/", "https://sharapplus.co.il/contact-us/", "https://sharapplus.co.il/doctors/%D7%98%D7%9C%D7%99-%D7%90%D7%A0%D7%92%D7%95%D7%A8/", "https://sharapplus.co.il/doctors/moaad-slieman/", "https://sharapplus.co.il/doctors/dr_eti_fiora/", "https://sharapplus.co.il/doctors/dr_manevitz/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%90%D7%99%D7%A8-%D7%A7%D7%A1%D7%98%D7%A0%D7%91%D7%90%D7%95%D7%9D/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%A8%D7%96/", "https://sharapplus.co.il/doctors/nail-abaya/", "https://sharapplus.co.il/doctors/med-balance-institute/", "https://sharapplus.co.il/doctors/nahum-eliyahu/", "https://sharapplus.co.il/doctors/eyal-zipman/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#551e067b3815263d34273425253920267b363a7b3c39", "https://sharapplus.co.il/cdn-cgi/l/email-protection", "https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/entandheadandnecksurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/ambulatory_operating_room/", "https://www.rambam.org.il/departmentsandclinics/trauma-and-emergency-surgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/generalsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/breastsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/vascularsurgeryandtransplantation/"]</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>2</v>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>["https://www.medreviews.co.il/provider/dr-cohen-aviad", "https://www.medreviews.co.il/provider/dr-cohen-aviad#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://urbanstudies.huji.ac.il/people/%D7%90%D7%91%D7%99%D7%A2%D7%93-%D7%9B%D7%94%D7%9F", "https://chabadpedia.co.il/wiki/%D7%A2%D7%9E%D7%95%D7%93_%D7%A8%D7%90%D7%A9%D7%99", "https://ibasketball.co.il/staff/19-%D7%90%D7%91%D7%99%D7%A2%D7%93-%D7%9B%D7%94%D7%9F/", "https://hoops.co.il/", "https://www.kib.co.il/%D7%9E%D7%99%D7%A0%D7%95%D7%99%D7%99%D7%9D-%D7%97%D7%93%D7%A9%D7%99%D7%9D-%D7%91%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9B%D7%A9%D7%99%D7%A8%D7%99-%D7%AA%D7%A0%D7%95%D7%A2%D7%94-%D7%90%D7%91/", "https://med.tau.ac.il/tau/index", "https://doctors.assuta.co.il/doctor/aviad-cohen-97475", "https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>אנה פטרוסב</t>
+          <t>אביעד כהן</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1739,7 +1779,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>officeks@sharapplus.co.il</t>
+          <t>gen-c@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1748,11 +1788,11 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://sharapplus.co.il/doctors/anna-petruseva/</t>
+          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1762,44 +1802,47 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>"אנה פטרוסב" מרפאה פרטית</t>
+          <t>"אביעד כהן" צור קשר מרפאה</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[{"email": "ks.m@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/contact-for-doctors/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "officeks@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "office@sharapplus.co.il", "confidence": 75, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+          <t>[{"email": "gen-c@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}, {"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>4</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://sharapplus.co.il/doctors/anna-petruseva/", "https://sharapplus.co.il/terms-and-conditions/", "https://sharapplus.co.il/all-doctors/", "https://sharapplus.co.il/contact-for-doctors/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#f19e9797989294b1829990839081819d8482df929edf989d", "https://sharapplus.co.il/cdn-cgi/l/email-protection#84ebe2e2ede7e1c4f7ece5f6e5f4f4e8f1f7aae7ebaaede8", "https://sharapplus.co.il/about/", "https://sharapplus.co.il/contact-us/", "https://sharapplus.co.il/doctors/%D7%98%D7%9C%D7%99-%D7%90%D7%A0%D7%92%D7%95%D7%A8/", "https://sharapplus.co.il/doctors/moaad-slieman/", "https://sharapplus.co.il/doctors/dr_eti_fiora/", "https://sharapplus.co.il/doctors/dr_manevitz/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%90%D7%99%D7%A8-%D7%A7%D7%A1%D7%98%D7%A0%D7%91%D7%90%D7%95%D7%9D/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%A8%D7%96/", "https://sharapplus.co.il/doctors/nail-abaya/", "https://sharapplus.co.il/doctors/med-balance-institute/", "https://sharapplus.co.il/doctors/nahum-eliyahu/", "https://sharapplus.co.il/doctors/eyal-zipman/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#551e067b3815263d34273425253920267b363a7b3c39", "https://sharapplus.co.il/cdn-cgi/l/email-protection", "https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/entandheadandnecksurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/ambulatory_operating_room/", "https://www.rambam.org.il/departmentsandclinics/trauma-and-emergency-surgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/generalsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/breastsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/vascularsurgeryandtransplantation/"]</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>3</v>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>["https://www.medreviews.co.il/provider/dr-cohen-aviad", "https://www.medreviews.co.il/provider/dr-cohen-aviad#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://urbanstudies.huji.ac.il/people/%D7%90%D7%91%D7%99%D7%A2%D7%93-%D7%9B%D7%94%D7%9F", "https://chabadpedia.co.il/wiki/%D7%A2%D7%9E%D7%95%D7%93_%D7%A8%D7%90%D7%A9%D7%99", "https://ibasketball.co.il/staff/19-%D7%90%D7%91%D7%99%D7%A2%D7%93-%D7%9B%D7%94%D7%9F/", "https://hoops.co.il/", "https://www.kib.co.il/%D7%9E%D7%99%D7%A0%D7%95%D7%99%D7%99%D7%9D-%D7%97%D7%93%D7%A9%D7%99%D7%9D-%D7%91%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9B%D7%A9%D7%99%D7%A8%D7%99-%D7%AA%D7%A0%D7%95%D7%A2%D7%94-%D7%90%D7%91/", "https://med.tau.ac.il/tau/index", "https://doctors.assuta.co.il/doctor/aviad-cohen-97475", "https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>אלנה דיקופולצב</t>
+          <t>אביעד כהן</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1824,7 +1867,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>app@forty.co.il</t>
+          <t>og-clinic@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1833,11 +1876,11 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.forty.co.il/contact</t>
+          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1847,44 +1890,47 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>app@forty.co.il fortyapp @fortyapp</t>
+          <t>ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>"אלנה דיקופולצב" יילוד גינקולוג</t>
+          <t>"אביעד כהן" צור קשר מרפאה</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[{"email": "info@medreviews.co.il", "confidence": 75, "source_url": "https://www.medreviews.co.il/contact-us", "evidence": "MedReviews - יצירת קשר יצירת קשר קשר עם MedReviews פנחס ספיר 8, נס ציונה 055-4548554 info@medreviews.co.il Loading... מלאו  פרטים ונציג שלנו יצור עמך קשר בהקדם שם * שם * טלפון * טלפון * אימייל אימייל הערות * הערות * בהשארת פרטים אני מאשר כי אני מעוניין לקבל התקשרות חוזרת מהמרפאה, וכן מאשר את תנאי השימוש ומדיניות הפרטיות באתר MedReviews. אני מעוניין לקבל דברי פרסומת כהגדרתם בחוק מ-MedReviews ומהמרפאה ובאפשרותי לחזור בי מהסכמה זו בכל עת. שליחה אודות MedReviews היא אינדקס לרופאים המתקדם והאמין בישר", "matched_query": "\"אלנה דיקופולצב\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+          <t>[{"email": "gen-c@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}, {"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלנה-דיקופולצב", "https://www.medreviews.co.il/provider/dr-dikopoltsev-elena", "https://www.medreviews.co.il/provider/dr-dikopoltsev-elena#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=692190DF7EC470C8FF9D9F2B9878620353AD1BEFAF4991E1A7C44949E6817E31&amp;RequestId=00000000-0000-0000-0001-000000000209", "https://www.maccabi4u.co.il/kosher", "https://go.serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%93%D7%99%D7%A7%D7%95%D7%A4%D7%95%D7%9C%D7%A6%D7%91%20%D7%90%D7%9C%D7%A0%D7%94", "https://go.serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=304433089&amp;ProviderProfession=1&amp;docClinic=4000709&amp;Service=1&amp;NewObjectId=70055539&amp;NewObjectType=S&amp;NewPerNr=90016439&amp;ol1=70055539&amp;ol2=S&amp;ol3=90016439&amp;isKosher=1&amp;beginDate=2026-08-31T23:33:18&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.meuhedet.co.il/poi/Doctors/001358170152100049000000000000_0", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/3fbb8ab2-b9bd-48f0-bc8e-2261da2804db", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21", "https://www.forty.co.il/contact", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/a1ead677-fdde-4351-8e64-db92c279edd1", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/39f9ebe2-8b41-4c7f-8af3-dfe03652f60a", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/3abed105-4564-4cc4-9587-718d9018a641", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/eb18fcb9-5088-4a87-8e32-7868b77de072", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/4027b022-22b5-4b14-8323-8f6590eaf560", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/405cdeae-9149-4a27-ac1b-2098a2d3abec", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/44f6e8d6-d3be-4757-8126-c3f3f76c2da9", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/e6c264ca-e2b6-4a27-87d9-2e993b557397", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/e4c95cc5-ddc5-4547-9a11-50f0d5e39641", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/74c7d262-c9cb-4900-8f25-7f7f5e9e402a", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/ce430b6f-9d65-4141-a213-16b3afb8f8c4", "https://www.forty.co.il/ranking/da94c110-6da5-4df4-92c1-c8b784ed6d21/7f3bc8ba-dfa4-4767-aaae-b74e63af2650"]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>1</v>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>["https://www.medreviews.co.il/provider/dr-cohen-aviad", "https://www.medreviews.co.il/provider/dr-cohen-aviad#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://urbanstudies.huji.ac.il/people/%D7%90%D7%91%D7%99%D7%A2%D7%93-%D7%9B%D7%94%D7%9F", "https://chabadpedia.co.il/wiki/%D7%A2%D7%9E%D7%95%D7%93_%D7%A8%D7%90%D7%A9%D7%99", "https://ibasketball.co.il/staff/19-%D7%90%D7%91%D7%99%D7%A2%D7%93-%D7%9B%D7%94%D7%9F/", "https://hoops.co.il/", "https://www.kib.co.il/%D7%9E%D7%99%D7%A0%D7%95%D7%99%D7%99%D7%9D-%D7%97%D7%93%D7%A9%D7%99%D7%9D-%D7%91%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9B%D7%A9%D7%99%D7%A8%D7%99-%D7%AA%D7%A0%D7%95%D7%A2%D7%94-%D7%90%D7%91/", "https://med.tau.ac.il/tau/index", "https://doctors.assuta.co.il/doctor/aviad-cohen-97475", "https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>אנה פטרוסב</t>
+          <t>אביעד כהן</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1909,20 +1955,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>office@sharapplus.co.il</t>
+          <t>usw@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://sharapplus.co.il/doctors/anna-petruseva/</t>
+          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1932,35 +1978,214 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t xml:space="preserve">רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון </t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>"אנה פטרוסב" מרפאה פרטית</t>
+          <t>"אביעד כהן" צור קשר מרפאה</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[{"email": "ks.m@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/contact-for-doctors/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "officeks@sharapplus.co.il", "confidence": 85, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}, {"email": "office@sharapplus.co.il", "confidence": 75, "source_url": "https://sharapplus.co.il/doctors/anna-petruseva/", "evidence": "[email protected]", "matched_query": "\"אנה פטרוסב\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+          <t>[{"email": "gen-c@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}, {"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"אביעד כהן\" צור קשר מרפאה", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://sharapplus.co.il/doctors/anna-petruseva/", "https://sharapplus.co.il/terms-and-conditions/", "https://sharapplus.co.il/all-doctors/", "https://sharapplus.co.il/contact-for-doctors/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#f19e9797989294b1829990839081819d8482df929edf989d", "https://sharapplus.co.il/cdn-cgi/l/email-protection#84ebe2e2ede7e1c4f7ece5f6e5f4f4e8f1f7aae7ebaaede8", "https://sharapplus.co.il/about/", "https://sharapplus.co.il/contact-us/", "https://sharapplus.co.il/doctors/%D7%98%D7%9C%D7%99-%D7%90%D7%A0%D7%92%D7%95%D7%A8/", "https://sharapplus.co.il/doctors/moaad-slieman/", "https://sharapplus.co.il/doctors/dr_eti_fiora/", "https://sharapplus.co.il/doctors/dr_manevitz/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%90%D7%99%D7%A8-%D7%A7%D7%A1%D7%98%D7%A0%D7%91%D7%90%D7%95%D7%9D/", "https://sharapplus.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%A8%D7%96/", "https://sharapplus.co.il/doctors/nail-abaya/", "https://sharapplus.co.il/doctors/med-balance-institute/", "https://sharapplus.co.il/doctors/nahum-eliyahu/", "https://sharapplus.co.il/doctors/eyal-zipman/", "https://sharapplus.co.il/cdn-cgi/l/email-protection#551e067b3815263d34273425253920267b363a7b3c39", "https://sharapplus.co.il/cdn-cgi/l/email-protection", "https://www.rambam.org.il/?catid=%7B41FBCAE5-9C06-407A-8A14-A123F94348AE%7D&amp;itemid=%7BB3778AD9-AA3F-4E56-8CA4-86B02A748FD4%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/entandheadandnecksurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/ambulatory_operating_room/", "https://www.rambam.org.il/departmentsandclinics/trauma-and-emergency-surgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/generalsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/breastsurgery/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/vascularsurgeryandtransplantation/"]</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>["https://www.medreviews.co.il/provider/dr-cohen-aviad", "https://www.medreviews.co.il/provider/dr-cohen-aviad#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://urbanstudies.huji.ac.il/people/%D7%90%D7%91%D7%99%D7%A2%D7%93-%D7%9B%D7%94%D7%9F", "https://chabadpedia.co.il/wiki/%D7%A2%D7%9E%D7%95%D7%93_%D7%A8%D7%90%D7%A9%D7%99", "https://ibasketball.co.il/staff/19-%D7%90%D7%91%D7%99%D7%A2%D7%93-%D7%9B%D7%94%D7%9F/", "https://hoops.co.il/", "https://www.kib.co.il/%D7%9E%D7%99%D7%A0%D7%95%D7%99%D7%99%D7%9D-%D7%97%D7%93%D7%A9%D7%99%D7%9D-%D7%91%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9B%D7%A9%D7%99%D7%A8%D7%99-%D7%AA%D7%A0%D7%95%D7%A2%D7%94-%D7%90%D7%91/", "https://med.tau.ac.il/tau/index", "https://doctors.assuta.co.il/doctor/aviad-cohen-97475", "https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/", "https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>אביגיל מעיני</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1800@d.co.il</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>85</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80213191/46500/</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>"אביגיל מעיני" מייל email</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>["https://easy.co.il/list/Gynecologist", "https://www.beok.co.il/index/", "https://knowmore.co.il/doctors/אביגיל-מעיני-2/", "https://www.beok.co.il/doctors/Doctors-119861/", "https://drtor.co.il/doctor/3148", "https://drtor.co.il/cdn-cgi/l/email-protection#85e6eaebf1e4e6f1c5e1f7f1eaf7abe6eaabece9", "https://drtor.co.il/search/koopa/all/city/all/type/all/name/all/page/1", "https://drtor.co.il/doctor/758", "https://drtor.co.il/doctor/3145", "https://drtor.co.il/doctor/3149", "https://drtor.co.il/doctor/8190", "https://drtor.co.il/doctor/8192", "https://drtor.co.il/doctor/12796", "https://drtor.co.il/cdn-cgi/l/email-protection#8ae9e5e4feebe9fecaeef8fee5f8a4e9e5a4e3e6", "https://drtor.co.il/doctor/1", "https://drtor.co.il/doctor/2", "https://drtor.co.il/doctor/3", "https://drtor.co.il/doctor/4", "https://drtor.co.il/doctor/5", "https://drtor.co.il/doctor/6", "https://drtor.co.il/doctor/7", "https://drtor.co.il/doctor/8", "https://www.d.co.il/80213191/46500/", "https://zapgroup.wixsite.com/website-868", "https://www.d.co.il/h-c2530-e0-p0-l0/", "https://www.d.co.il/cdn-cgi/l/email-protection#a996dadccbc3cccadd947e037e017e397e3d897e397e03897e387e307e03897e3d7e0b7e087e0e897e3d7e3f7e3d897e387e3a7e0d7e30897e3f7e3d7e388fc8c4d992cbc6cdd0948ccd9e8c909a8fd8dcc6dd928ccd9e8cc8918c9b998ccd9e8c90998ccd9e8c90988ccd9e8c90908ccd9e8c909b8ccd9e8c90908ccd9e8c90ca8c9b998ccd9e8c90cc8ccd9e8cc89b8ccd9e8c90908ccd9e8cc8998ccd9e8c90908c99c88ccd9e8cc8918ccd9e8c90cb8ccd9e8cc8988ccd9e8c90908ccd9e8c90cd8c9b999b9b858c9b998ccd9e8cc89f8ccd9e8c909c8ccd9e8cc8918c9b998ccd9e8c909d8ccd9e8c909a8ccd9e8cc8988ccd9e8c909d8c99c8999b849c9e999a9a91918c99c8", "https://www.d.co.il/cdn-cgi/l/email-protection#605158505020044e030f4e090c", "https://www.d.co.il/LandingPage/AboutPage/", "https://www.d.co.il/LandingPage/ContactUs/", "https://www.d.co.il/cdn-cgi/l/email-protection#5d6c656d6d1d39733e32733431", "https://www.d.co.il/cdn-cgi/l/email-protection#4879707878082c662b27662124", "https://www.d.co.il/cdn-cgi/l/email-protection#7b4a434b4b3b1f551814551217", "https://www.d.co.il/cdn-cgi/l/email-protection#e8d9d0d8d8a88cc68b87c68184", "https://www.d.co.il/cdn-cgi/l/email-protection#81b0b9b1b1c1e5afe2eeafe8ed", "https://www.d.co.il/cdn-cgi/l/email-protection#c7f6fff7f787a3e9a4a8e9aeab"]</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>אביה רוזנטל</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>nashim@laniado.org.il</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>80</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.laniado.org.il/departments/%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%92%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>מרפאה גניקולוגית - בית חולים לניאדו נתניה Skip to content Toggle navigation בית אודות חדשות סטאז’ והתמחות התנדבות בלניאדו צור קשר עברית English ( אנגלית ) Français ( צרפתית ) 09-860-4666 מרפאות ומכונים מחלקות אגף נשים ויולדות מידע למטופל בית ספר לאחיוּת תרמו לנו עברית English ( אנגלית ) Français ( צרפתית ) איתור רופא מרפאות ומכונים קבע תור לבדיקה / מכון התמצאות  בלניאדו צור איתנו קשר בית מרפאות ומכונים מרפאה גניקולוגית מרפאה גניקולוגית תפריט צרו קשר מיקום המרפאה זמני פעילות צוות מטפל אחיות: 09-8</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>"אביה רוזנטל" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>["https://dr-aviya.co.il/", "https://www.medreviews.co.il/provider/dr-rozental-aviya/treatment/gynecology-fertility", "https://www.medreviews.co.il/provider/dr-rozental-aviya/treatment/gynecology-fertility#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rozental-aviya/treatment/gynecologist-clinic", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-rozental-aviya/treatment/gynecologist-clinic#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%90%D7%91%D7%99%D7%94-%D7%A8%D7%95%D7%96%D7%A0%D7%98%D7%9C/", "https://www.laniado.org.il/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%95%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9/", "https://www.laniado.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.laniado.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A2%D7%9D-%D7%91%D7%99%D7%AA-%D7%94%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/", "https://www.laniado.org.il/doctor/", "https://www.laniado.org.il", "https://www.laniado.org.il/departments/%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%92%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://www.laniado.org.il/departments/%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%94%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://www.laniado.org.il/en/about/", "https://www.laniado.org.il/en/contact/", "https://www.laniado.org.il/fr/fr_contact/", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%91%D7%A8%D7%A1%D7%95%D7%A7%D7%91%D7%99%D7%A5-%D7%93%D7%9E%D7%99%D7%98%D7%A8%D7%99/", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%A7%D7%9C%D7%95%D7%93-%D7%A4%D7%99%D7%A7%D7%90%D7%A8/", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%90%D7%91%D7%95-%D7%A2%D7%A8%D7%99%D7%A9%D7%94-%D7%A2%D7%9E%D7%90%D7%93/", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%90%D7%91%D7%99%D7%A0%D7%93%D7%91-%D7%90%D7%A4%D7%A8%D7%AA/", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%90%D7%91%D7%A9%D7%9C%D7%95%D7%9D-%D7%9B%D7%A8%D7%9E%D7%9C/", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%90%D7%92%D7%91%D7%90%D7%A8%D7%99%D7%94-%D7%90%D7%9E%D7%99%D7%A8/", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%90%D7%92%D7%A8%D7%A1%D7%98-%D7%95%D7%9C%D7%A8%D7%99%D7%94/", "https://www.laniado.org.il/doctor/%D7%93%D7%A8-%D7%90%D7%94%D7%A8%D7%95%D7%9F-%D7%9C%D7%99%D7%91%D7%A8%D7%96%D7%95%D7%9F/"]</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5.943390679798868e+16</v>
+        <v>1.78301720393966e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.822485035801138e+16</v>
+        <v>1.446745510740341e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>4.822427849505779e+16</v>
+        <v>1.446728354851734e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>5.945424172461531e+16</v>
+        <v>1.783627251738459e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>4.822485035801146e+16</v>
+        <v>1.446745510740344e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>4.822485035801146e+16</v>
+        <v>1.446745510740344e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4.822427849505779e+16</v>
+        <v>1.446728354851734e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>4.819434796805247e+16</v>
+        <v>1.445830439041574e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>6.684598755339604e+16</v>
+        <v>2.005379626601881e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>5.943390679798868e+16</v>
+        <v>1.78301720393966e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4.81943479680715e+16</v>
+        <v>1.445830439042145e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>5.56431375593407e+16</v>
+        <v>1.669294126780221e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>4.819434796805247e+16</v>
+        <v>1.445830439041574e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>6.68510712850527e+16</v>
+        <v>2.005532138551581e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE53" t="n">
         <v>7</v>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>4.461540088176475e+16</v>
+        <v>1.338462026452943e+17</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.461482901883061e+16</v>
+        <v>1.338444870564918e+17</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>4.461482901883061e+16</v>
+        <v>1.338444870564918e+17</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9968,7 +9968,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.45182381173541e+16</v>
+        <v>1.335547143520623e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4.451993269457299e+16</v>
+        <v>1.33559798083719e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10440,7 +10440,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>17</v>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10899,7 +10899,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -11526,7 +11526,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE69" t="n">
         <v>3</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE70" t="n">
         <v>3</v>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12138,7 +12138,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12288,7 +12288,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13044,7 +13044,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13358,7 +13358,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13516,7 +13516,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>5.563692410953811e+16</v>
+        <v>1.669107723286143e+17</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13966,7 +13966,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE85" t="n">
         <v>9</v>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>7.041476717636996e+16</v>
+        <v>2.112443015291099e+17</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14450,7 +14450,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE89" t="n">
         <v>4</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE90" t="n">
         <v>7</v>
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -15066,7 +15066,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -15216,7 +15216,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15520,7 +15520,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE95" t="n">
         <v>3</v>
@@ -15670,7 +15670,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15973,7 +15973,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE99" t="n">
         <v>3</v>
@@ -16285,7 +16285,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE100" t="n">
         <v>4</v>
@@ -16435,7 +16435,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE101" t="n">
         <v>4</v>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE102" t="n">
         <v>4</v>
@@ -16735,7 +16735,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE103" t="n">
         <v>4</v>
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -17361,7 +17361,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17513,7 +17513,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17663,7 +17663,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17963,7 +17963,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -18113,7 +18113,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE112" t="n">
         <v>4</v>
@@ -18273,7 +18273,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18585,7 +18585,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>4.460974528876827e+16</v>
+        <v>1.338292358663048e+17</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18737,7 +18737,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>4.451993269457299e+16</v>
+        <v>1.33559798083719e+17</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -19219,7 +19219,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>5.929664604485323e+16</v>
+        <v>1.778899381345597e+17</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -19367,7 +19367,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -19517,7 +19517,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19667,7 +19667,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19817,7 +19817,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -20267,7 +20267,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -20417,7 +20417,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20567,7 +20567,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20717,7 +20717,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20867,7 +20867,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -21017,7 +21017,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -21167,7 +21167,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21617,7 +21617,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21917,7 +21917,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -22067,7 +22067,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -22367,7 +22367,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22517,7 +22517,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22667,7 +22667,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22817,7 +22817,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22967,7 +22967,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -23117,7 +23117,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -23267,7 +23267,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23417,7 +23417,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23567,7 +23567,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23717,7 +23717,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23867,7 +23867,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -24017,7 +24017,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -24167,7 +24167,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -24317,7 +24317,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24467,7 +24467,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24617,7 +24617,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24767,7 +24767,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24917,7 +24917,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -25067,7 +25067,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -25367,7 +25367,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25517,7 +25517,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25667,7 +25667,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25817,7 +25817,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25967,7 +25967,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -26117,7 +26117,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -26267,7 +26267,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26417,7 +26417,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26567,7 +26567,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26717,7 +26717,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26867,7 +26867,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -27017,7 +27017,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -27167,7 +27167,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -27317,7 +27317,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27467,7 +27467,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27617,7 +27617,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27767,7 +27767,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27917,7 +27917,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -28067,7 +28067,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -28217,7 +28217,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -28367,7 +28367,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28517,7 +28517,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28667,7 +28667,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28817,7 +28817,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28967,7 +28967,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -29267,7 +29267,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29417,7 +29417,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29567,7 +29567,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29717,7 +29717,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29867,7 +29867,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -30017,7 +30017,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -30167,7 +30167,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE192" t="n">
         <v>1</v>
@@ -30317,7 +30317,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30617,7 +30617,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30767,7 +30767,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30917,7 +30917,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -31067,7 +31067,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -31217,7 +31217,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -31367,7 +31367,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31517,7 +31517,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31667,7 +31667,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31817,7 +31817,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31967,7 +31967,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -32117,7 +32117,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -32267,7 +32267,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32417,7 +32417,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32567,7 +32567,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32717,7 +32717,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32867,7 +32867,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE210" t="n">
         <v>1</v>
@@ -33017,7 +33017,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -33167,7 +33167,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -33317,7 +33317,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33467,7 +33467,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33617,7 +33617,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33767,7 +33767,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33917,7 +33917,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -34067,7 +34067,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -34217,7 +34217,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34517,7 +34517,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34667,7 +34667,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34817,7 +34817,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34967,7 +34967,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -35117,7 +35117,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -35267,7 +35267,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35417,7 +35417,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -35567,7 +35567,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35717,7 +35717,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35867,7 +35867,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -36017,7 +36017,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -36167,7 +36167,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -36317,7 +36317,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36467,7 +36467,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36617,7 +36617,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36767,7 +36767,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36917,7 +36917,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -37067,7 +37067,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -37367,7 +37367,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37517,7 +37517,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37667,7 +37667,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37817,7 +37817,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37967,7 +37967,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -38117,7 +38117,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38417,7 +38417,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38567,7 +38567,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38717,7 +38717,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -38867,7 +38867,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -39017,7 +39017,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -39167,7 +39167,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -39317,7 +39317,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39467,7 +39467,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39617,7 +39617,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39767,7 +39767,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -39917,7 +39917,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -40067,7 +40067,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -40217,7 +40217,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -40367,7 +40367,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -40517,7 +40517,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40667,7 +40667,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40817,7 +40817,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -40967,7 +40967,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -41117,7 +41117,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -41267,7 +41267,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41417,7 +41417,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -41567,7 +41567,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41717,7 +41717,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41867,7 +41867,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -42017,7 +42017,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -42167,7 +42167,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -42317,7 +42317,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42617,7 +42617,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -42767,7 +42767,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -42917,7 +42917,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -43067,7 +43067,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -43217,7 +43217,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -43367,7 +43367,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -43667,7 +43667,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -43817,7 +43817,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -43967,7 +43967,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -44117,7 +44117,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -44267,7 +44267,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44417,7 +44417,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44567,7 +44567,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -44717,7 +44717,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -44867,7 +44867,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -45017,7 +45017,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -45167,7 +45167,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -45317,7 +45317,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -45467,7 +45467,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -45617,7 +45617,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -45767,7 +45767,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -45917,7 +45917,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -46067,7 +46067,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -46217,7 +46217,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -46367,7 +46367,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -46517,7 +46517,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE301" t="n">
         <v>3</v>
@@ -46667,7 +46667,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -46817,7 +46817,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -46967,7 +46967,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -47117,7 +47117,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE305" t="n">
         <v>3</v>
@@ -47267,7 +47267,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -47417,7 +47417,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -47567,7 +47567,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -47717,7 +47717,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -47867,7 +47867,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -48017,7 +48017,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -48167,7 +48167,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE312" t="n">
         <v>229</v>
@@ -48317,7 +48317,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -48467,7 +48467,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -48617,7 +48617,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -48767,7 +48767,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -48917,7 +48917,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -49067,7 +49067,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -49217,7 +49217,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -49367,7 +49367,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -49517,7 +49517,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -49667,7 +49667,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -49817,7 +49817,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -49967,7 +49967,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -50117,7 +50117,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -50267,7 +50267,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -50417,7 +50417,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -50567,7 +50567,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -50717,7 +50717,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -50867,7 +50867,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -51027,7 +51027,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE331" t="n">
         <v>1</v>
@@ -51189,7 +51189,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE332" t="n">
         <v>1</v>
@@ -51351,7 +51351,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE333" t="n">
         <v>1</v>
@@ -51513,7 +51513,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE334" t="n">
         <v>1</v>
@@ -51665,7 +51665,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE335" t="n">
         <v>1</v>
@@ -51825,7 +51825,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>5.600238792974453e+16</v>
+        <v>1.680071637892336e+17</v>
       </c>
       <c r="AE336" t="n">
         <v>1</v>
@@ -51981,7 +51981,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>5.559117052462819e+16</v>
+        <v>1.667735115738846e+17</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -52141,7 +52141,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE338" t="n">
         <v>1</v>
@@ -52301,7 +52301,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>4.448773572741416e+16</v>
+        <v>1.334632071822425e+17</v>
       </c>
       <c r="AE339" t="n">
         <v>1</v>
@@ -52463,7 +52463,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>4.448773572741416e+16</v>
+        <v>1.334632071822425e+17</v>
       </c>
       <c r="AE340" t="n">
         <v>1</v>
@@ -52615,7 +52615,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -52765,7 +52765,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -52915,7 +52915,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE343" t="n">
         <v>1</v>
@@ -53065,7 +53065,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -53215,7 +53215,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -53365,7 +53365,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -53515,7 +53515,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -53665,7 +53665,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -53815,7 +53815,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -53965,7 +53965,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -54115,7 +54115,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54265,7 +54265,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54415,7 +54415,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE353" t="n">
         <v>2</v>
@@ -54565,7 +54565,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -54715,7 +54715,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -54865,7 +54865,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -55015,7 +55015,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE357" t="n">
         <v>2</v>
@@ -55165,7 +55165,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE358" t="n">
         <v>2</v>
@@ -55315,7 +55315,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -55465,7 +55465,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -55615,7 +55615,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -55775,7 +55775,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -55925,7 +55925,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -56075,7 +56075,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -56233,7 +56233,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -56392,7 +56392,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -56542,7 +56542,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -56692,7 +56692,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -56850,7 +56850,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -57000,7 +57000,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE370" t="n">
         <v>2</v>
@@ -57150,7 +57150,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -57308,7 +57308,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -57458,7 +57458,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -57614,7 +57614,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>5.559117052462819e+16</v>
+        <v>1.667735115738846e+17</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -57772,7 +57772,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -57922,7 +57922,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -58068,7 +58068,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -58218,7 +58218,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -58368,7 +58368,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -58518,7 +58518,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -58814,7 +58814,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -59122,7 +59122,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -59282,7 +59282,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>5.559117749819699e+16</v>
+        <v>1.66773532494591e+17</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -59442,7 +59442,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -59595,7 +59595,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -59755,7 +59755,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>5.563693111180473e+16</v>
+        <v>1.669107933354142e+17</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -59915,7 +59915,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>5.563693111180473e+16</v>
+        <v>1.669107933354142e+17</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -60075,7 +60075,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>5.563693111180473e+16</v>
+        <v>1.669107933354142e+17</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -60225,7 +60225,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -60385,7 +60385,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>5.600238792974453e+16</v>
+        <v>1.680071637892336e+17</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -60543,7 +60543,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -60701,7 +60701,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -60859,7 +60859,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -61009,7 +61009,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -61167,7 +61167,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -61317,7 +61317,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -61467,7 +61467,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE399" t="n">
         <v>2</v>
@@ -61625,7 +61625,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -61775,7 +61775,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -61925,7 +61925,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE402" t="n">
         <v>2</v>
@@ -62083,7 +62083,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -62243,7 +62243,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE404" t="n">
         <v>4</v>
@@ -62393,7 +62393,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -62547,7 +62547,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -62697,7 +62697,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE407" t="n">
         <v>2</v>
@@ -62855,7 +62855,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -63013,7 +63013,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -63163,7 +63163,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -63313,7 +63313,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -63473,7 +63473,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -63633,7 +63633,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -63793,7 +63793,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -63951,7 +63951,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -64112,7 +64112,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -64270,7 +64270,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -64420,7 +64420,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -64566,7 +64566,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -64716,7 +64716,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -64866,7 +64866,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -65016,7 +65016,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -65166,7 +65166,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -65324,7 +65324,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -65484,7 +65484,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -65644,7 +65644,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.903742185412251e+18</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.604715483545694e+18</v>
+        <v>4.814146450637083e+18</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.302070959666307e+18</v>
+        <v>3.906212878998921e+18</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.30205551936656e+18</v>
+        <v>3.906166558099681e+18</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.605264526564613e+18</v>
+        <v>4.81579357969384e+18</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.302070959666309e+18</v>
+        <v>3.906212878998928e+18</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.302070959666309e+18</v>
+        <v>3.906212878998928e+18</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.30205551936656e+18</v>
+        <v>3.906166558099681e+18</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.90374218541225e+18</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.804841663941693e+18</v>
+        <v>5.414524991825079e+18</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6586,7 +6586,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.604715483545694e+18</v>
+        <v>4.814146450637083e+18</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.201184304939929e+18</v>
+        <v>3.603552914819788e+18</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.301247395137931e+18</v>
+        <v>3.903742185413792e+18</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.502364714102199e+18</v>
+        <v>4.507094142306596e+18</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.90374218541225e+18</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.804978924696423e+18</v>
+        <v>5.414936774089268e+18</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9016,7 +9016,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE55" t="n">
         <v>7</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.204615823807648e+18</v>
+        <v>3.613847471422945e+18</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.204600383508426e+18</v>
+        <v>3.613801150525279e+18</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9822,7 +9822,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.204600383508426e+18</v>
+        <v>3.613801150525279e+18</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9984,7 +9984,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.201992429168561e+18</v>
+        <v>3.605977287505682e+18</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.202038182753471e+18</v>
+        <v>3.606114548260412e+18</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE64" t="n">
         <v>17</v>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -11397,7 +11397,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE71" t="n">
         <v>3</v>
@@ -12020,7 +12020,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE72" t="n">
         <v>3</v>
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13092,7 +13092,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1.502196950957529e+18</v>
+        <v>4.506590852872587e+18</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -14006,7 +14006,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -14156,7 +14156,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14316,7 +14316,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1.234264146800576e+18</v>
+        <v>3.702792440401727e+18</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE88" t="n">
         <v>9</v>
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1.901198713761989e+18</v>
+        <v>5.703596141285967e+18</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE92" t="n">
         <v>4</v>
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE93" t="n">
         <v>7</v>
@@ -15427,7 +15427,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE94" t="n">
         <v>11</v>
@@ -15577,7 +15577,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15727,7 +15727,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15877,7 +15877,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -16031,7 +16031,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE98" t="n">
         <v>3</v>
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -16334,7 +16334,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16484,7 +16484,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -16638,7 +16638,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE102" t="n">
         <v>3</v>
@@ -16796,7 +16796,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE103" t="n">
         <v>4</v>
@@ -16946,7 +16946,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -17246,7 +17246,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE106" t="n">
         <v>4</v>
@@ -17396,7 +17396,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17556,7 +17556,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1.234538668338751e+18</v>
+        <v>3.703616005016253e+18</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17724,7 +17724,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17882,7 +17882,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -18042,7 +18042,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -18194,7 +18194,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -18344,7 +18344,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18494,7 +18494,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18644,7 +18644,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18794,7 +18794,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE116" t="n">
         <v>4</v>
@@ -18954,7 +18954,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -19106,7 +19106,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1.204463122796743e+18</v>
+        <v>3.61338936839023e+18</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19738,7 +19738,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1.202038182753471e+18</v>
+        <v>3.606114548260412e+18</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -19900,7 +19900,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1.601009443211037e+18</v>
+        <v>4.803028329633112e+18</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -20048,7 +20048,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -20198,7 +20198,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -20348,7 +20348,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -20498,7 +20498,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20648,7 +20648,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20798,7 +20798,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20948,7 +20948,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -21548,7 +21548,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21848,7 +21848,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -22148,7 +22148,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -22298,7 +22298,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -22448,7 +22448,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22598,7 +22598,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22748,7 +22748,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22898,7 +22898,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -23048,7 +23048,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -23198,7 +23198,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -23348,7 +23348,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23498,7 +23498,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23798,7 +23798,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23948,7 +23948,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -24098,7 +24098,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -24248,7 +24248,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -24398,7 +24398,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24548,7 +24548,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24698,7 +24698,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24848,7 +24848,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24998,7 +24998,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -25148,7 +25148,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -25298,7 +25298,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -25448,7 +25448,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25598,7 +25598,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25748,7 +25748,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25898,7 +25898,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -26048,7 +26048,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -26198,7 +26198,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -26348,7 +26348,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26648,7 +26648,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26798,7 +26798,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26948,7 +26948,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -27098,7 +27098,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -27248,7 +27248,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -27398,7 +27398,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27698,7 +27698,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27848,7 +27848,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27998,7 +27998,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -28148,7 +28148,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -28298,7 +28298,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -28448,7 +28448,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28598,7 +28598,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28748,7 +28748,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28898,7 +28898,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -29048,7 +29048,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -29198,7 +29198,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -29348,7 +29348,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29498,7 +29498,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29648,7 +29648,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29798,7 +29798,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29948,7 +29948,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -30098,7 +30098,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -30248,7 +30248,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30548,7 +30548,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30698,7 +30698,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30848,7 +30848,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE196" t="n">
         <v>1</v>
@@ -30998,7 +30998,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -31148,7 +31148,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -31298,7 +31298,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -31448,7 +31448,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31598,7 +31598,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31748,7 +31748,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31898,7 +31898,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -32048,7 +32048,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -32198,7 +32198,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -32348,7 +32348,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32498,7 +32498,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32648,7 +32648,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32798,7 +32798,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32948,7 +32948,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -33098,7 +33098,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -33248,7 +33248,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -33398,7 +33398,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33548,7 +33548,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE214" t="n">
         <v>1</v>
@@ -33698,7 +33698,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33848,7 +33848,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33998,7 +33998,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -34148,7 +34148,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -34298,7 +34298,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -34448,7 +34448,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34598,7 +34598,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34748,7 +34748,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34898,7 +34898,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -35048,7 +35048,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -35198,7 +35198,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -35348,7 +35348,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35498,7 +35498,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35798,7 +35798,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35948,7 +35948,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -36098,7 +36098,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -36248,7 +36248,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -36398,7 +36398,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36548,7 +36548,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36698,7 +36698,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36848,7 +36848,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36998,7 +36998,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -37148,7 +37148,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -37298,7 +37298,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -37448,7 +37448,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37598,7 +37598,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37748,7 +37748,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37898,7 +37898,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -38048,7 +38048,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -38198,7 +38198,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -38348,7 +38348,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38498,7 +38498,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38648,7 +38648,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38798,7 +38798,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -38948,7 +38948,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -39098,7 +39098,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -39248,7 +39248,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -39398,7 +39398,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39548,7 +39548,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39698,7 +39698,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39848,7 +39848,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -39998,7 +39998,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -40148,7 +40148,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -40298,7 +40298,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -40448,7 +40448,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -40598,7 +40598,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40748,7 +40748,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40898,7 +40898,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -41048,7 +41048,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -41198,7 +41198,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -41348,7 +41348,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41498,7 +41498,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -41648,7 +41648,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41798,7 +41798,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41948,7 +41948,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -42098,7 +42098,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -42248,7 +42248,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -42398,7 +42398,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42548,7 +42548,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42698,7 +42698,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -42848,7 +42848,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -42998,7 +42998,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -43148,7 +43148,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -43298,7 +43298,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -43448,7 +43448,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43598,7 +43598,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -43748,7 +43748,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -44048,7 +44048,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -44198,7 +44198,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -44348,7 +44348,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44498,7 +44498,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44648,7 +44648,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -44948,7 +44948,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -45098,7 +45098,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -45248,7 +45248,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -45398,7 +45398,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -45548,7 +45548,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -45698,7 +45698,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -45848,7 +45848,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -45998,7 +45998,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -46148,7 +46148,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -46298,7 +46298,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -46448,7 +46448,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -46598,7 +46598,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -46748,7 +46748,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -46898,7 +46898,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -47048,7 +47048,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -47198,7 +47198,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE305" t="n">
         <v>3</v>
@@ -47348,7 +47348,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -47498,7 +47498,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -47648,7 +47648,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -47798,7 +47798,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE309" t="n">
         <v>3</v>
@@ -47948,7 +47948,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -48098,7 +48098,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -48248,7 +48248,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -48398,7 +48398,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -48548,7 +48548,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -48698,7 +48698,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -48848,7 +48848,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE316" t="n">
         <v>229</v>
@@ -48998,7 +48998,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -49148,7 +49148,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -49298,7 +49298,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -49448,7 +49448,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -49598,7 +49598,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -49748,7 +49748,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -49898,7 +49898,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -50048,7 +50048,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -50198,7 +50198,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -50348,7 +50348,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -50498,7 +50498,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -50648,7 +50648,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -50798,7 +50798,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -50948,7 +50948,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -51098,7 +51098,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -51248,7 +51248,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -51548,7 +51548,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51708,7 +51708,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE335" t="n">
         <v>1</v>
@@ -51870,7 +51870,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE336" t="n">
         <v>1</v>
@@ -52032,7 +52032,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE337" t="n">
         <v>1</v>
@@ -52194,7 +52194,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE338" t="n">
         <v>1</v>
@@ -52346,7 +52346,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE339" t="n">
         <v>1</v>
@@ -52506,7 +52506,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>1.512064474103102e+18</v>
+        <v>4.536193422309307e+18</v>
       </c>
       <c r="AE340" t="n">
         <v>1</v>
@@ -52662,7 +52662,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>1.500961604164961e+18</v>
+        <v>4.502884812494883e+18</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -52822,7 +52822,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -52982,7 +52982,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>1.201168864640182e+18</v>
+        <v>3.603506593920547e+18</v>
       </c>
       <c r="AE343" t="n">
         <v>1</v>
@@ -53144,7 +53144,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>1.201168864640182e+18</v>
+        <v>3.603506593920547e+18</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -53296,7 +53296,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -53446,7 +53446,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE346" t="n">
         <v>1</v>
@@ -53596,7 +53596,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -53746,7 +53746,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -53896,7 +53896,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -54046,7 +54046,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE350" t="n">
         <v>2</v>
@@ -54196,7 +54196,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54346,7 +54346,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54496,7 +54496,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54646,7 +54646,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -54796,7 +54796,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -54946,7 +54946,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -55096,7 +55096,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE357" t="n">
         <v>2</v>
@@ -55246,7 +55246,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -55396,7 +55396,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -55546,7 +55546,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -55696,7 +55696,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE361" t="n">
         <v>2</v>
@@ -55846,7 +55846,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE362" t="n">
         <v>2</v>
@@ -55996,7 +55996,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -56146,7 +56146,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -56296,7 +56296,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -56456,7 +56456,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -56606,7 +56606,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -56756,7 +56756,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -56914,7 +56914,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -57073,7 +57073,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -57223,7 +57223,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -57373,7 +57373,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -57531,7 +57531,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -57681,7 +57681,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE374" t="n">
         <v>2</v>
@@ -57831,7 +57831,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -57989,7 +57989,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -58139,7 +58139,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -58295,7 +58295,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>1.500961604164961e+18</v>
+        <v>4.502884812494883e+18</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -58453,7 +58453,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -58603,7 +58603,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -58749,7 +58749,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -58899,7 +58899,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -59049,7 +59049,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -59199,7 +59199,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -59349,7 +59349,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -59495,7 +59495,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -59653,7 +59653,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -59803,7 +59803,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -59963,7 +59963,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>1.500961792451319e+18</v>
+        <v>4.502885377353956e+18</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -60123,7 +60123,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -60276,7 +60276,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -60436,7 +60436,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>1.502197140018728e+18</v>
+        <v>4.506591420056183e+18</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -60596,7 +60596,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>1.502197140018728e+18</v>
+        <v>4.506591420056183e+18</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -60756,7 +60756,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>1.502197140018728e+18</v>
+        <v>4.506591420056183e+18</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -60906,7 +60906,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -61066,7 +61066,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>1.512064474103102e+18</v>
+        <v>4.536193422309307e+18</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -61224,7 +61224,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -61382,7 +61382,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -61540,7 +61540,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -61690,7 +61690,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -61848,7 +61848,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -61998,7 +61998,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -62148,7 +62148,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE403" t="n">
         <v>2</v>
@@ -62306,7 +62306,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -62456,7 +62456,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -62606,7 +62606,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE406" t="n">
         <v>2</v>
@@ -62764,7 +62764,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE408" t="n">
         <v>4</v>
@@ -63074,7 +63074,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -63378,7 +63378,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE411" t="n">
         <v>2</v>
@@ -63536,7 +63536,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -63694,7 +63694,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -63844,7 +63844,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -63994,7 +63994,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -64154,7 +64154,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -64314,7 +64314,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -64474,7 +64474,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -64632,7 +64632,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -64793,7 +64793,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -64951,7 +64951,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -65101,7 +65101,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -65247,7 +65247,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -65397,7 +65397,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -65547,7 +65547,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -65697,7 +65697,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>
@@ -65847,7 +65847,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -66005,7 +66005,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE428" t="n">
         <v>1</v>
@@ -66165,7 +66165,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -66325,7 +66325,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE430" t="n">
         <v>1</v>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.054010390061308e+20</v>
+        <v>3.162031170183923e+20</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.299819541672012e+20</v>
+        <v>3.899458625016037e+20</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.054677477329709e+20</v>
+        <v>3.164032431989126e+20</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.054664970686914e+20</v>
+        <v>3.163994912060741e+20</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.300264266517337e+20</v>
+        <v>3.90079279955201e+20</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>21879</v>
+        <v>65637</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.05467747732971e+20</v>
+        <v>3.164032431989131e+20</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.05467747732971e+20</v>
+        <v>3.164032431989131e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.054664970686914e+20</v>
+        <v>3.163994912060741e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.054010390061307e+20</v>
+        <v>3.162031170183922e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.461921747792771e+20</v>
+        <v>4.385765243378314e+20</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.299819541672012e+20</v>
+        <v>3.899458625016037e+20</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>9.729592870013428e+19</v>
+        <v>2.918877861004028e+20</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>9.729592870009283e+19</v>
+        <v>2.918877861002785e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.054010390061724e+20</v>
+        <v>3.162031170185171e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.053997883418927e+20</v>
+        <v>3.161993650256782e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.053997883418927e+20</v>
+        <v>3.161993650256782e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.053997883418927e+20</v>
+        <v>3.161993650256782e+20</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.216915418422781e+20</v>
+        <v>3.650746255268343e+20</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.054010390061307e+20</v>
+        <v>3.162031170183922e+20</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.462032929004103e+20</v>
+        <v>4.386098787012308e+20</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE59" t="n">
         <v>7</v>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>9.757388172841951e+19</v>
+        <v>2.927216451852586e+20</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>9.757263106418254e+19</v>
+        <v>2.927178931925476e+20</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>9.757263106418254e+19</v>
+        <v>2.927178931925476e+20</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>9.729592870009283e+19</v>
+        <v>2.918877861002785e+20</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>9.736138676265343e+19</v>
+        <v>2.920841602879603e+20</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>9.736509280303114e+19</v>
+        <v>2.920952784090934e+20</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11480,7 +11480,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE69" t="n">
         <v>17</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11947,7 +11947,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12414,7 +12414,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE76" t="n">
         <v>3</v>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE77" t="n">
         <v>3</v>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -14120,7 +14120,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>9.736263742693297e+19</v>
+        <v>2.920879122807989e+20</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1.216779530275598e+20</v>
+        <v>3.650338590826795e+20</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE95" t="n">
         <v>4</v>
@@ -15856,7 +15856,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>9.997539589084663e+19</v>
+        <v>2.999261876725399e+20</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE97" t="n">
         <v>9</v>
@@ -16177,7 +16177,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -16520,7 +16520,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.539970958147211e+20</v>
+        <v>4.619912874441633e+20</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -17333,7 +17333,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE105" t="n">
         <v>7</v>
@@ -17483,7 +17483,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE106" t="n">
         <v>11</v>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -18087,7 +18087,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE110" t="n">
         <v>3</v>
@@ -18237,7 +18237,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE114" t="n">
         <v>3</v>
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE115" t="n">
         <v>4</v>
@@ -19002,7 +19002,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE116" t="n">
         <v>4</v>
@@ -19152,7 +19152,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE117" t="n">
         <v>4</v>
@@ -19302,7 +19302,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE118" t="n">
         <v>4</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -19612,7 +19612,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>9.999763213543884e+19</v>
+        <v>2.999928964063166e+20</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -20550,7 +20550,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -20700,7 +20700,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20850,7 +20850,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE128" t="n">
         <v>4</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -21322,7 +21322,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>9.756151294653622e+19</v>
+        <v>2.926845388396086e+20</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -21794,7 +21794,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>9.736509280303114e+19</v>
+        <v>2.920952784090934e+20</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -21956,7 +21956,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.29681764900094e+20</v>
+        <v>3.890452947002821e+20</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -22104,7 +22104,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -22254,7 +22254,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE137" t="n">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE138" t="n">
         <v>1</v>
@@ -22574,7 +22574,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -23324,7 +23324,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -23474,7 +23474,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -23624,7 +23624,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23924,7 +23924,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -24074,7 +24074,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -24224,7 +24224,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -24374,7 +24374,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -24524,7 +24524,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -24674,7 +24674,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24974,7 +24974,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -25124,7 +25124,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -25424,7 +25424,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -25574,7 +25574,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -25724,7 +25724,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -26024,7 +26024,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -26324,7 +26324,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26774,7 +26774,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -27224,7 +27224,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -27374,7 +27374,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -27524,7 +27524,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -27674,7 +27674,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27824,7 +27824,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27974,7 +27974,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -28124,7 +28124,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -28424,7 +28424,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -28574,7 +28574,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -28724,7 +28724,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -29174,7 +29174,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -29324,7 +29324,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -29624,7 +29624,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29774,7 +29774,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29924,7 +29924,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -30074,7 +30074,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -30224,7 +30224,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -30374,7 +30374,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -30674,7 +30674,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30824,7 +30824,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30974,7 +30974,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -31124,7 +31124,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -31274,7 +31274,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -31424,7 +31424,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -31574,7 +31574,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -31724,7 +31724,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31874,7 +31874,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -32024,7 +32024,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -32174,7 +32174,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -32324,7 +32324,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -32624,7 +32624,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32774,7 +32774,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32924,7 +32924,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -33074,7 +33074,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE209" t="n">
         <v>1</v>
@@ -33224,7 +33224,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -33374,7 +33374,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -33524,7 +33524,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -33674,7 +33674,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33824,7 +33824,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33974,7 +33974,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -34124,7 +34124,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -34574,7 +34574,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -34724,7 +34724,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34874,7 +34874,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -35024,7 +35024,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -35174,7 +35174,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -35324,7 +35324,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -35474,7 +35474,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -35624,7 +35624,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE227" t="n">
         <v>1</v>
@@ -35924,7 +35924,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -36074,7 +36074,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -36224,7 +36224,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -36374,7 +36374,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -36524,7 +36524,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -36674,7 +36674,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36824,7 +36824,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36974,7 +36974,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -37124,7 +37124,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -37424,7 +37424,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -37574,7 +37574,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -37724,7 +37724,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37874,7 +37874,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -38024,7 +38024,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -38174,7 +38174,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -38474,7 +38474,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -38624,7 +38624,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38774,7 +38774,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38924,7 +38924,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -39074,7 +39074,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -39224,7 +39224,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -39374,7 +39374,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -39524,7 +39524,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39974,7 +39974,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -40124,7 +40124,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -40274,7 +40274,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -40574,7 +40574,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -40724,7 +40724,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -40874,7 +40874,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -41024,7 +41024,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -41174,7 +41174,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -41474,7 +41474,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -41624,7 +41624,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41774,7 +41774,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -41924,7 +41924,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -42074,7 +42074,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -42674,7 +42674,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42974,7 +42974,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -43124,7 +43124,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -43274,7 +43274,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -43424,7 +43424,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43874,7 +43874,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -44024,7 +44024,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -44324,7 +44324,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44774,7 +44774,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -45074,7 +45074,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -45224,7 +45224,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -45374,7 +45374,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -45524,7 +45524,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -45674,7 +45674,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -45824,7 +45824,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -45974,7 +45974,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -46124,7 +46124,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -46274,7 +46274,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -46424,7 +46424,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -46574,7 +46574,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -46874,7 +46874,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -47024,7 +47024,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -47174,7 +47174,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -47324,7 +47324,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -47474,7 +47474,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -47624,7 +47624,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -47774,7 +47774,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -47924,7 +47924,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -48074,7 +48074,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -48224,7 +48224,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -48374,7 +48374,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -48524,7 +48524,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -48674,7 +48674,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -48974,7 +48974,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -49124,7 +49124,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -49274,7 +49274,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -49424,7 +49424,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE318" t="n">
         <v>3</v>
@@ -49574,7 +49574,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -49724,7 +49724,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -49874,7 +49874,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -50024,7 +50024,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE322" t="n">
         <v>3</v>
@@ -50174,7 +50174,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -50324,7 +50324,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -50474,7 +50474,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -50624,7 +50624,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -50774,7 +50774,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -50924,7 +50924,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -51074,7 +51074,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE329" t="n">
         <v>229</v>
@@ -51224,7 +51224,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -51374,7 +51374,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -51524,7 +51524,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -51674,7 +51674,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -51824,7 +51824,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51974,7 +51974,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -52124,7 +52124,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -52274,7 +52274,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -52574,7 +52574,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -52724,7 +52724,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -52874,7 +52874,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -53024,7 +53024,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -53174,7 +53174,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -53324,7 +53324,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -53474,7 +53474,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -53774,7 +53774,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>1.053775520996265e+20</v>
+        <v>3.161326562988795e+20</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -54096,7 +54096,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>1.053775520996265e+20</v>
+        <v>3.161326562988795e+20</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -54258,7 +54258,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -54420,7 +54420,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>1.053664339784934e+20</v>
+        <v>3.160993019354802e+20</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54572,7 +54572,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54732,7 +54732,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>1.224772224023513e+20</v>
+        <v>3.674316672070538e+20</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54888,7 +54888,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>1.215778899373619e+20</v>
+        <v>3.647336698120856e+20</v>
       </c>
       <c r="AE354" t="n">
         <v>2</v>
@@ -55048,7 +55048,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -55208,7 +55208,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>9.729467803585477e+19</v>
+        <v>2.918840341075643e+20</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -55370,7 +55370,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>9.729467803585477e+19</v>
+        <v>2.918840341075643e+20</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -55522,7 +55522,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -55672,7 +55672,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -55822,7 +55822,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -55972,7 +55972,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -56122,7 +56122,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -56272,7 +56272,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE363" t="n">
         <v>2</v>
@@ -56422,7 +56422,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -56572,7 +56572,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -56872,7 +56872,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -57022,7 +57022,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -57172,7 +57172,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -57322,7 +57322,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE370" t="n">
         <v>2</v>
@@ -57472,7 +57472,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -57622,7 +57622,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -57772,7 +57772,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -57922,7 +57922,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE374" t="n">
         <v>2</v>
@@ -58072,7 +58072,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE375" t="n">
         <v>2</v>
@@ -58222,7 +58222,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -58372,7 +58372,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -58522,7 +58522,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -58682,7 +58682,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -58832,7 +58832,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -59140,7 +59140,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -59449,7 +59449,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -59599,7 +59599,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -59757,7 +59757,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -59907,7 +59907,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE387" t="n">
         <v>2</v>
@@ -60057,7 +60057,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -60215,7 +60215,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -60365,7 +60365,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -60521,7 +60521,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>1.215778899373619e+20</v>
+        <v>3.647336698120856e+20</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -60679,7 +60679,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -60829,7 +60829,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -60975,7 +60975,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -61125,7 +61125,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -61275,7 +61275,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -61425,7 +61425,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -61575,7 +61575,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -61721,7 +61721,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -61879,7 +61879,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -62029,7 +62029,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -62189,7 +62189,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>1.215779051885568e+20</v>
+        <v>3.647337155656705e+20</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -62349,7 +62349,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>1.053775520996265e+20</v>
+        <v>3.161326562988795e+20</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -62502,7 +62502,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -62662,7 +62662,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>1.216779683415169e+20</v>
+        <v>3.650339050245508e+20</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -62822,7 +62822,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>1.216779683415169e+20</v>
+        <v>3.650339050245508e+20</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -62982,7 +62982,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>1.216779683415169e+20</v>
+        <v>3.650339050245508e+20</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -63132,7 +63132,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -63292,7 +63292,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>1.224772224023513e+20</v>
+        <v>3.674316672070538e+20</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -63450,7 +63450,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -63766,7 +63766,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -63916,7 +63916,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -64074,7 +64074,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -64224,7 +64224,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -64374,7 +64374,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE416" t="n">
         <v>2</v>
@@ -64532,7 +64532,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -64682,7 +64682,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -64832,7 +64832,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE419" t="n">
         <v>2</v>
@@ -64990,7 +64990,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -65150,7 +65150,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE421" t="n">
         <v>4</v>
@@ -65300,7 +65300,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -65454,7 +65454,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -65604,7 +65604,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE424" t="n">
         <v>2</v>
@@ -65762,7 +65762,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -65920,7 +65920,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>
@@ -66070,7 +66070,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -66220,7 +66220,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE428" t="n">
         <v>1</v>
@@ -66380,7 +66380,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -66540,7 +66540,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE430" t="n">
         <v>1</v>
@@ -66700,7 +66700,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -66858,7 +66858,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -67019,7 +67019,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -67169,7 +67169,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -67315,7 +67315,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -67465,7 +67465,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -67615,7 +67615,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -67765,7 +67765,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -67915,7 +67915,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -68073,7 +68073,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -68233,7 +68233,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -68393,7 +68393,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.162031170183923e+20</v>
+        <v>9.486093510551769e+20</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>3.899458625016037e+20</v>
+        <v>1.169837587504811e+21</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.164032431989126e+20</v>
+        <v>9.492097295967378e+20</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>3.163994912060741e+20</v>
+        <v>9.491984736182225e+20</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>3.90079279955201e+20</v>
+        <v>1.170237839865603e+21</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>65637</v>
+        <v>196911</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.164032431989131e+20</v>
+        <v>9.492097295967394e+20</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>3.164032431989131e+20</v>
+        <v>9.492097295967394e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>3.163994912060741e+20</v>
+        <v>9.491984736182225e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>3.162031170183922e+20</v>
+        <v>9.486093510551768e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.385765243378314e+20</v>
+        <v>1.315729573013494e+21</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>3.899458625016037e+20</v>
+        <v>1.169837587504811e+21</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2.918877861004028e+20</v>
+        <v>8.756633583012084e+20</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2.918877861002785e+20</v>
+        <v>8.756633583008354e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>3.162031170185171e+20</v>
+        <v>9.486093510555515e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>3.161993650256782e+20</v>
+        <v>9.485980950770344e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>3.161993650256782e+20</v>
+        <v>9.485980950770344e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>3.161993650256782e+20</v>
+        <v>9.485980950770344e+20</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>3.650746255268343e+20</v>
+        <v>1.095223876580503e+21</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>3.162031170183922e+20</v>
+        <v>9.486093510551768e+20</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.386098787012308e+20</v>
+        <v>1.315829636103692e+21</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE59" t="n">
         <v>7</v>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2.927216451852586e+20</v>
+        <v>8.781649355557756e+20</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2.927178931925476e+20</v>
+        <v>8.781536795776428e+20</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>2.927178931925476e+20</v>
+        <v>8.781536795776428e+20</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2.918877861002785e+20</v>
+        <v>8.756633583008354e+20</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2.920841602879603e+20</v>
+        <v>8.762524808638809e+20</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2.920952784090934e+20</v>
+        <v>8.762858352272802e+20</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11480,7 +11480,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE69" t="n">
         <v>17</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11947,7 +11947,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12414,7 +12414,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE76" t="n">
         <v>3</v>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE77" t="n">
         <v>3</v>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -14120,7 +14120,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2.920879122807989e+20</v>
+        <v>8.762637368423968e+20</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>3.650338590826795e+20</v>
+        <v>1.095101577248039e+21</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE95" t="n">
         <v>4</v>
@@ -15856,7 +15856,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2.999261876725399e+20</v>
+        <v>8.997785630176197e+20</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE97" t="n">
         <v>9</v>
@@ -16177,7 +16177,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -16520,7 +16520,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>4.619912874441633e+20</v>
+        <v>1.38597386233249e+21</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -17333,7 +17333,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE105" t="n">
         <v>7</v>
@@ -17483,7 +17483,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE106" t="n">
         <v>11</v>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -18087,7 +18087,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE110" t="n">
         <v>3</v>
@@ -18237,7 +18237,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE114" t="n">
         <v>3</v>
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE115" t="n">
         <v>4</v>
@@ -19002,7 +19002,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE116" t="n">
         <v>4</v>
@@ -19152,7 +19152,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE117" t="n">
         <v>4</v>
@@ -19302,7 +19302,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE118" t="n">
         <v>4</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -19612,7 +19612,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>2.999928964063166e+20</v>
+        <v>8.999786892189497e+20</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -20550,7 +20550,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -20700,7 +20700,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20850,7 +20850,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE128" t="n">
         <v>4</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -21322,7 +21322,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>2.926845388396086e+20</v>
+        <v>8.780536165188259e+20</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -21794,7 +21794,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>2.920952784090934e+20</v>
+        <v>8.762858352272802e+20</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -21956,7 +21956,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>3.890452947002821e+20</v>
+        <v>1.167135884100846e+21</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -22104,7 +22104,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -22254,7 +22254,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE137" t="n">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE138" t="n">
         <v>1</v>
@@ -22574,7 +22574,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -23324,7 +23324,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -23474,7 +23474,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -23624,7 +23624,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23924,7 +23924,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -24074,7 +24074,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -24224,7 +24224,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -24374,7 +24374,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -24524,7 +24524,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -24674,7 +24674,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24974,7 +24974,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -25124,7 +25124,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -25424,7 +25424,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -25574,7 +25574,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -25724,7 +25724,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -26024,7 +26024,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -26324,7 +26324,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26774,7 +26774,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -27224,7 +27224,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -27374,7 +27374,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -27524,7 +27524,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -27674,7 +27674,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27824,7 +27824,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27974,7 +27974,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -28124,7 +28124,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -28424,7 +28424,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -28574,7 +28574,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -28724,7 +28724,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -29174,7 +29174,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -29324,7 +29324,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -29624,7 +29624,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29774,7 +29774,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29924,7 +29924,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -30074,7 +30074,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -30224,7 +30224,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -30374,7 +30374,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -30674,7 +30674,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30824,7 +30824,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30974,7 +30974,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -31124,7 +31124,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -31274,7 +31274,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -31424,7 +31424,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -31574,7 +31574,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -31724,7 +31724,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31874,7 +31874,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -32024,7 +32024,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -32174,7 +32174,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -32324,7 +32324,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -32624,7 +32624,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32774,7 +32774,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32924,7 +32924,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -33074,7 +33074,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE209" t="n">
         <v>1</v>
@@ -33224,7 +33224,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -33374,7 +33374,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -33524,7 +33524,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -33674,7 +33674,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33824,7 +33824,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33974,7 +33974,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -34124,7 +34124,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -34574,7 +34574,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -34724,7 +34724,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34874,7 +34874,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -35024,7 +35024,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -35174,7 +35174,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -35324,7 +35324,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -35474,7 +35474,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -35624,7 +35624,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE227" t="n">
         <v>1</v>
@@ -35924,7 +35924,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -36074,7 +36074,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -36224,7 +36224,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -36374,7 +36374,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -36524,7 +36524,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -36674,7 +36674,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36824,7 +36824,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36974,7 +36974,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -37124,7 +37124,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -37424,7 +37424,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -37574,7 +37574,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -37724,7 +37724,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37874,7 +37874,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -38024,7 +38024,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -38174,7 +38174,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -38474,7 +38474,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -38624,7 +38624,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38774,7 +38774,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38924,7 +38924,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -39074,7 +39074,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -39224,7 +39224,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -39374,7 +39374,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -39524,7 +39524,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39974,7 +39974,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -40124,7 +40124,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -40274,7 +40274,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -40574,7 +40574,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -40724,7 +40724,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -40874,7 +40874,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -41024,7 +41024,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -41174,7 +41174,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -41474,7 +41474,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -41624,7 +41624,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41774,7 +41774,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -41924,7 +41924,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -42074,7 +42074,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -42674,7 +42674,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42974,7 +42974,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -43124,7 +43124,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -43274,7 +43274,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -43424,7 +43424,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43874,7 +43874,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -44024,7 +44024,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -44324,7 +44324,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44774,7 +44774,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -45074,7 +45074,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -45224,7 +45224,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -45374,7 +45374,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -45524,7 +45524,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -45674,7 +45674,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -45824,7 +45824,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -45974,7 +45974,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -46124,7 +46124,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -46274,7 +46274,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -46424,7 +46424,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -46574,7 +46574,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -46874,7 +46874,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -47024,7 +47024,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -47174,7 +47174,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -47324,7 +47324,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -47474,7 +47474,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -47624,7 +47624,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -47774,7 +47774,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -47924,7 +47924,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -48074,7 +48074,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -48224,7 +48224,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -48374,7 +48374,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -48524,7 +48524,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -48674,7 +48674,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -48974,7 +48974,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -49124,7 +49124,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -49274,7 +49274,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -49424,7 +49424,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE318" t="n">
         <v>3</v>
@@ -49574,7 +49574,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -49724,7 +49724,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -49874,7 +49874,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -50024,7 +50024,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE322" t="n">
         <v>3</v>
@@ -50174,7 +50174,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -50324,7 +50324,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -50474,7 +50474,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -50624,7 +50624,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -50774,7 +50774,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -50924,7 +50924,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -51074,7 +51074,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE329" t="n">
         <v>229</v>
@@ -51224,7 +51224,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -51374,7 +51374,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -51524,7 +51524,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -51674,7 +51674,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -51824,7 +51824,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51974,7 +51974,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -52124,7 +52124,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -52274,7 +52274,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -52574,7 +52574,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -52724,7 +52724,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -52874,7 +52874,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -53024,7 +53024,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -53174,7 +53174,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -53324,7 +53324,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -53474,7 +53474,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -53774,7 +53774,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>3.161326562988795e+20</v>
+        <v>9.483979688966385e+20</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -54096,7 +54096,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>3.161326562988795e+20</v>
+        <v>9.483979688966385e+20</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -54258,7 +54258,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -54420,7 +54420,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>3.160993019354802e+20</v>
+        <v>9.482979058064404e+20</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54572,7 +54572,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54732,7 +54732,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>3.674316672070538e+20</v>
+        <v>1.102295001621162e+21</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54888,7 +54888,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>3.647336698120856e+20</v>
+        <v>1.094201009436257e+21</v>
       </c>
       <c r="AE354" t="n">
         <v>2</v>
@@ -55048,7 +55048,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -55208,7 +55208,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>2.918840341075643e+20</v>
+        <v>8.756521023226928e+20</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -55370,7 +55370,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>2.918840341075643e+20</v>
+        <v>8.756521023226928e+20</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -55522,7 +55522,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -55672,7 +55672,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -55822,7 +55822,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -55972,7 +55972,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -56122,7 +56122,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -56272,7 +56272,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE363" t="n">
         <v>2</v>
@@ -56422,7 +56422,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -56572,7 +56572,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -56872,7 +56872,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -57022,7 +57022,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -57172,7 +57172,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -57322,7 +57322,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE370" t="n">
         <v>2</v>
@@ -57472,7 +57472,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -57622,7 +57622,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -57772,7 +57772,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -57922,7 +57922,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE374" t="n">
         <v>2</v>
@@ -58072,7 +58072,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE375" t="n">
         <v>2</v>
@@ -58222,7 +58222,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -58372,7 +58372,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -58522,7 +58522,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -58682,7 +58682,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -58832,7 +58832,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -59140,7 +59140,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -59449,7 +59449,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -59599,7 +59599,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -59757,7 +59757,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -59907,7 +59907,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE387" t="n">
         <v>2</v>
@@ -60057,7 +60057,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -60215,7 +60215,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -60365,7 +60365,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -60521,7 +60521,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>3.647336698120856e+20</v>
+        <v>1.094201009436257e+21</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -60679,7 +60679,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -60829,7 +60829,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -60975,7 +60975,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -61125,7 +61125,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -61275,7 +61275,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -61425,7 +61425,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -61575,7 +61575,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -61721,7 +61721,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -61879,7 +61879,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -62029,7 +62029,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -62189,7 +62189,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>3.647337155656705e+20</v>
+        <v>1.094201146697011e+21</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -62349,7 +62349,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>3.161326562988795e+20</v>
+        <v>9.483979688966385e+20</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -62502,7 +62502,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -62662,7 +62662,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>3.650339050245508e+20</v>
+        <v>1.095101715073652e+21</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -62822,7 +62822,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>3.650339050245508e+20</v>
+        <v>1.095101715073652e+21</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -62982,7 +62982,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>3.650339050245508e+20</v>
+        <v>1.095101715073652e+21</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -63132,7 +63132,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -63292,7 +63292,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>3.674316672070538e+20</v>
+        <v>1.102295001621162e+21</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -63450,7 +63450,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -63766,7 +63766,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -63916,7 +63916,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -64074,7 +64074,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -64224,7 +64224,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -64374,7 +64374,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE416" t="n">
         <v>2</v>
@@ -64532,7 +64532,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -64682,7 +64682,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -64832,7 +64832,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE419" t="n">
         <v>2</v>
@@ -64990,7 +64990,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -65150,7 +65150,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE421" t="n">
         <v>4</v>
@@ -65300,7 +65300,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -65454,7 +65454,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -65604,7 +65604,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE424" t="n">
         <v>2</v>
@@ -65762,7 +65762,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -65920,7 +65920,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>
@@ -66070,7 +66070,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -66220,7 +66220,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE428" t="n">
         <v>1</v>
@@ -66380,7 +66380,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -66540,7 +66540,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE430" t="n">
         <v>1</v>
@@ -66700,7 +66700,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -66858,7 +66858,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -67019,7 +67019,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -67169,7 +67169,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -67315,7 +67315,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -67465,7 +67465,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -67615,7 +67615,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -67765,7 +67765,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -67915,7 +67915,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -68073,7 +68073,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -68233,7 +68233,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -68393,7 +68393,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>9.486093510551769e+20</v>
+        <v>2.845828053165531e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.169837587504811e+21</v>
+        <v>3.509512762514434e+21</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>9.492097295967378e+20</v>
+        <v>2.847629188790213e+21</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>9.491984736182225e+20</v>
+        <v>2.847595420854667e+21</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.170237839865603e+21</v>
+        <v>3.510713519596809e+21</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>196911</v>
+        <v>590733</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>9.492097295967394e+20</v>
+        <v>2.847629188790218e+21</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>9.492097295967394e+20</v>
+        <v>2.847629188790218e+21</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>9.491984736182225e+20</v>
+        <v>2.847595420854667e+21</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>9.486093510551768e+20</v>
+        <v>2.84582805316553e+21</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.315729573013494e+21</v>
+        <v>3.947188719040483e+21</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.169837587504811e+21</v>
+        <v>3.509512762514434e+21</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>8.756633583012084e+20</v>
+        <v>2.626990074903625e+21</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>8.756633583008354e+20</v>
+        <v>2.626990074902506e+21</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>9.486093510555515e+20</v>
+        <v>2.845828053166654e+21</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>9.485980950770344e+20</v>
+        <v>2.845794285231104e+21</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>9.485980950770344e+20</v>
+        <v>2.845794285231104e+21</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>9.485980950770344e+20</v>
+        <v>2.845794285231104e+21</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.095223876580503e+21</v>
+        <v>3.285671629741509e+21</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>9.486093510551768e+20</v>
+        <v>2.84582805316553e+21</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.315829636103692e+21</v>
+        <v>3.947488908311077e+21</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE59" t="n">
         <v>7</v>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>8.781649355557756e+20</v>
+        <v>2.634494806667327e+21</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>8.781536795776428e+20</v>
+        <v>2.634461038732929e+21</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>8.781536795776428e+20</v>
+        <v>2.634461038732929e+21</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>8.756633583008354e+20</v>
+        <v>2.626990074902506e+21</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>8.762524808638809e+20</v>
+        <v>2.628757442591642e+21</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>8.762858352272802e+20</v>
+        <v>2.628857505681841e+21</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11480,7 +11480,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE69" t="n">
         <v>17</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11947,7 +11947,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12414,7 +12414,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE76" t="n">
         <v>3</v>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE77" t="n">
         <v>3</v>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -14120,7 +14120,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>8.762637368423968e+20</v>
+        <v>2.62879121052719e+21</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1.095101577248039e+21</v>
+        <v>3.285304731744116e+21</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE95" t="n">
         <v>4</v>
@@ -15856,7 +15856,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>8.997785630176197e+20</v>
+        <v>2.699335689052859e+21</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE97" t="n">
         <v>9</v>
@@ -16177,7 +16177,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -16520,7 +16520,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.38597386233249e+21</v>
+        <v>4.15792158699747e+21</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -17333,7 +17333,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE105" t="n">
         <v>7</v>
@@ -17483,7 +17483,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE106" t="n">
         <v>11</v>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -18087,7 +18087,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE110" t="n">
         <v>3</v>
@@ -18237,7 +18237,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE114" t="n">
         <v>3</v>
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE115" t="n">
         <v>4</v>
@@ -19002,7 +19002,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE116" t="n">
         <v>4</v>
@@ -19152,7 +19152,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE117" t="n">
         <v>4</v>
@@ -19302,7 +19302,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE118" t="n">
         <v>4</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -19612,7 +19612,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>8.999786892189497e+20</v>
+        <v>2.699936067656849e+21</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -20550,7 +20550,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -20700,7 +20700,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20850,7 +20850,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE128" t="n">
         <v>4</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -21322,7 +21322,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>8.780536165188259e+20</v>
+        <v>2.634160849556478e+21</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -21794,7 +21794,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>8.762858352272802e+20</v>
+        <v>2.628857505681841e+21</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -21956,7 +21956,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.167135884100846e+21</v>
+        <v>3.501407652302539e+21</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -22104,7 +22104,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -22254,7 +22254,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE137" t="n">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE138" t="n">
         <v>1</v>
@@ -22574,7 +22574,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -23324,7 +23324,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -23474,7 +23474,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -23624,7 +23624,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23924,7 +23924,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -24074,7 +24074,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -24224,7 +24224,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -24374,7 +24374,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -24524,7 +24524,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -24674,7 +24674,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24974,7 +24974,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -25124,7 +25124,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -25424,7 +25424,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -25574,7 +25574,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -25724,7 +25724,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -26024,7 +26024,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -26324,7 +26324,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26774,7 +26774,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -27224,7 +27224,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -27374,7 +27374,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -27524,7 +27524,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -27674,7 +27674,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27824,7 +27824,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27974,7 +27974,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -28124,7 +28124,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -28424,7 +28424,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -28574,7 +28574,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -28724,7 +28724,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -29174,7 +29174,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -29324,7 +29324,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -29624,7 +29624,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29774,7 +29774,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29924,7 +29924,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -30074,7 +30074,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -30224,7 +30224,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -30374,7 +30374,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -30674,7 +30674,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30824,7 +30824,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30974,7 +30974,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -31124,7 +31124,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -31274,7 +31274,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -31424,7 +31424,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -31574,7 +31574,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -31724,7 +31724,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31874,7 +31874,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -32024,7 +32024,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -32174,7 +32174,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -32324,7 +32324,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -32624,7 +32624,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32774,7 +32774,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32924,7 +32924,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -33074,7 +33074,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE209" t="n">
         <v>1</v>
@@ -33224,7 +33224,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -33374,7 +33374,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -33524,7 +33524,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -33674,7 +33674,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33824,7 +33824,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33974,7 +33974,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -34124,7 +34124,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -34574,7 +34574,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -34724,7 +34724,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34874,7 +34874,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -35024,7 +35024,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -35174,7 +35174,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -35324,7 +35324,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -35474,7 +35474,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -35624,7 +35624,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE227" t="n">
         <v>1</v>
@@ -35924,7 +35924,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -36074,7 +36074,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -36224,7 +36224,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -36374,7 +36374,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -36524,7 +36524,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -36674,7 +36674,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36824,7 +36824,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36974,7 +36974,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -37124,7 +37124,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -37424,7 +37424,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -37574,7 +37574,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -37724,7 +37724,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37874,7 +37874,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -38024,7 +38024,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -38174,7 +38174,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -38474,7 +38474,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -38624,7 +38624,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38774,7 +38774,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38924,7 +38924,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -39074,7 +39074,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -39224,7 +39224,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -39374,7 +39374,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -39524,7 +39524,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39974,7 +39974,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -40124,7 +40124,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -40274,7 +40274,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -40574,7 +40574,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -40724,7 +40724,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -40874,7 +40874,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -41024,7 +41024,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -41174,7 +41174,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -41474,7 +41474,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -41624,7 +41624,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41774,7 +41774,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -41924,7 +41924,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -42074,7 +42074,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -42674,7 +42674,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42974,7 +42974,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -43124,7 +43124,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -43274,7 +43274,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -43424,7 +43424,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43874,7 +43874,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -44024,7 +44024,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -44324,7 +44324,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44774,7 +44774,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -45074,7 +45074,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -45224,7 +45224,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -45374,7 +45374,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -45524,7 +45524,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -45674,7 +45674,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -45824,7 +45824,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -45974,7 +45974,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -46124,7 +46124,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -46274,7 +46274,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -46424,7 +46424,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -46574,7 +46574,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -46874,7 +46874,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -47024,7 +47024,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -47174,7 +47174,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -47324,7 +47324,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -47474,7 +47474,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -47624,7 +47624,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -47774,7 +47774,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -47924,7 +47924,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -48074,7 +48074,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -48224,7 +48224,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -48374,7 +48374,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -48524,7 +48524,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -48674,7 +48674,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -48974,7 +48974,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -49124,7 +49124,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -49274,7 +49274,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -49424,7 +49424,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE318" t="n">
         <v>3</v>
@@ -49574,7 +49574,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -49724,7 +49724,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -49874,7 +49874,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -50024,7 +50024,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE322" t="n">
         <v>3</v>
@@ -50174,7 +50174,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -50324,7 +50324,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -50474,7 +50474,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -50624,7 +50624,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -50774,7 +50774,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -50924,7 +50924,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -51074,7 +51074,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE329" t="n">
         <v>229</v>
@@ -51224,7 +51224,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -51374,7 +51374,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -51524,7 +51524,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -51674,7 +51674,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -51824,7 +51824,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51974,7 +51974,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -52124,7 +52124,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -52274,7 +52274,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -52574,7 +52574,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -52724,7 +52724,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -52874,7 +52874,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -53024,7 +53024,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -53174,7 +53174,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -53324,7 +53324,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -53474,7 +53474,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -53774,7 +53774,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>9.483979688966385e+20</v>
+        <v>2.845193906689915e+21</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -54096,7 +54096,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>9.483979688966385e+20</v>
+        <v>2.845193906689915e+21</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -54258,7 +54258,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -54420,7 +54420,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>9.482979058064404e+20</v>
+        <v>2.844893717419321e+21</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54572,7 +54572,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54732,7 +54732,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>1.102295001621162e+21</v>
+        <v>3.306885004863485e+21</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54888,7 +54888,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>1.094201009436257e+21</v>
+        <v>3.28260302830877e+21</v>
       </c>
       <c r="AE354" t="n">
         <v>2</v>
@@ -55048,7 +55048,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -55208,7 +55208,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>8.756521023226928e+20</v>
+        <v>2.626956306968079e+21</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -55370,7 +55370,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>8.756521023226928e+20</v>
+        <v>2.626956306968079e+21</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -55522,7 +55522,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -55672,7 +55672,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -55822,7 +55822,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -55972,7 +55972,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -56122,7 +56122,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -56272,7 +56272,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE363" t="n">
         <v>2</v>
@@ -56422,7 +56422,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -56572,7 +56572,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -56872,7 +56872,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -57022,7 +57022,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -57172,7 +57172,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -57322,7 +57322,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE370" t="n">
         <v>2</v>
@@ -57472,7 +57472,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -57622,7 +57622,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -57772,7 +57772,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -57922,7 +57922,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE374" t="n">
         <v>2</v>
@@ -58072,7 +58072,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE375" t="n">
         <v>2</v>
@@ -58222,7 +58222,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -58372,7 +58372,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -58522,7 +58522,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -58682,7 +58682,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -58832,7 +58832,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -59140,7 +59140,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -59449,7 +59449,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -59599,7 +59599,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -59757,7 +59757,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -59907,7 +59907,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE387" t="n">
         <v>2</v>
@@ -60057,7 +60057,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -60215,7 +60215,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -60365,7 +60365,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -60521,7 +60521,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>1.094201009436257e+21</v>
+        <v>3.28260302830877e+21</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -60679,7 +60679,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -60829,7 +60829,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -60975,7 +60975,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -61125,7 +61125,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -61275,7 +61275,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -61425,7 +61425,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -61575,7 +61575,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -61721,7 +61721,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -61879,7 +61879,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -62029,7 +62029,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -62189,7 +62189,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>1.094201146697011e+21</v>
+        <v>3.282603440091035e+21</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -62349,7 +62349,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>9.483979688966385e+20</v>
+        <v>2.845193906689915e+21</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -62502,7 +62502,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -62662,7 +62662,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>1.095101715073652e+21</v>
+        <v>3.285305145220957e+21</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -62822,7 +62822,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>1.095101715073652e+21</v>
+        <v>3.285305145220957e+21</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -62982,7 +62982,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>1.095101715073652e+21</v>
+        <v>3.285305145220957e+21</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -63132,7 +63132,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -63292,7 +63292,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>1.102295001621162e+21</v>
+        <v>3.306885004863485e+21</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -63450,7 +63450,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -63766,7 +63766,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -63916,7 +63916,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -64074,7 +64074,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -64224,7 +64224,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -64374,7 +64374,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE416" t="n">
         <v>2</v>
@@ -64532,7 +64532,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -64682,7 +64682,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -64832,7 +64832,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE419" t="n">
         <v>2</v>
@@ -64990,7 +64990,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -65150,7 +65150,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE421" t="n">
         <v>4</v>
@@ -65300,7 +65300,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -65454,7 +65454,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -65604,7 +65604,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE424" t="n">
         <v>2</v>
@@ -65762,7 +65762,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -65920,7 +65920,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>
@@ -66070,7 +66070,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -66220,7 +66220,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE428" t="n">
         <v>1</v>
@@ -66380,7 +66380,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -66540,7 +66540,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE430" t="n">
         <v>1</v>
@@ -66700,7 +66700,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -66858,7 +66858,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -67019,7 +67019,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -67169,7 +67169,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -67315,7 +67315,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -67465,7 +67465,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -67615,7 +67615,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -67765,7 +67765,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -67915,7 +67915,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -68073,7 +68073,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -68233,7 +68233,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -68393,7 +68393,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2.845828053165531e+21</v>
+        <v>8.537484159496593e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>3.509512762514434e+21</v>
+        <v>1.05285382875433e+22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2.847629188790213e+21</v>
+        <v>8.54288756637064e+21</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2.847595420854667e+21</v>
+        <v>8.542786262564002e+21</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>3.510713519596809e+21</v>
+        <v>1.053214055879043e+22</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>590733</v>
+        <v>1772199</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2.847629188790218e+21</v>
+        <v>8.542887566370655e+21</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2.847629188790218e+21</v>
+        <v>8.542887566370655e+21</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2.847595420854667e+21</v>
+        <v>8.542786262564002e+21</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2.84582805316553e+21</v>
+        <v>8.537484159496591e+21</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>3.947188719040483e+21</v>
+        <v>1.184156615712145e+22</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>3.509512762514434e+21</v>
+        <v>1.05285382875433e+22</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2.626990074903625e+21</v>
+        <v>7.880970224710876e+21</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2.626990074902506e+21</v>
+        <v>7.880970224707518e+21</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2.845828053166654e+21</v>
+        <v>8.537484159499963e+21</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2.845794285231104e+21</v>
+        <v>8.53738285569331e+21</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2.845794285231104e+21</v>
+        <v>8.53738285569331e+21</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2.845794285231104e+21</v>
+        <v>8.53738285569331e+21</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>3.285671629741509e+21</v>
+        <v>9.857014889224526e+21</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2.84582805316553e+21</v>
+        <v>8.537484159496591e+21</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>3.947488908311077e+21</v>
+        <v>1.184246672493323e+22</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE59" t="n">
         <v>7</v>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2.634494806667327e+21</v>
+        <v>7.90348442000198e+21</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2.634461038732929e+21</v>
+        <v>7.903383116198786e+21</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>2.634461038732929e+21</v>
+        <v>7.903383116198786e+21</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2.626990074902506e+21</v>
+        <v>7.880970224707518e+21</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2.628757442591642e+21</v>
+        <v>7.886272327774928e+21</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2.628857505681841e+21</v>
+        <v>7.886572517045521e+21</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11480,7 +11480,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE69" t="n">
         <v>17</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11947,7 +11947,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12414,7 +12414,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE76" t="n">
         <v>3</v>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE77" t="n">
         <v>3</v>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -14120,7 +14120,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2.62879121052719e+21</v>
+        <v>7.886373631581571e+21</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>3.285304731744116e+21</v>
+        <v>9.855914195232349e+21</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE95" t="n">
         <v>4</v>
@@ -15856,7 +15856,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2.699335689052859e+21</v>
+        <v>8.098007067158577e+21</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE97" t="n">
         <v>9</v>
@@ -16177,7 +16177,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -16520,7 +16520,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>4.15792158699747e+21</v>
+        <v>1.247376476099241e+22</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -17333,7 +17333,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE105" t="n">
         <v>7</v>
@@ -17483,7 +17483,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE106" t="n">
         <v>11</v>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -18087,7 +18087,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE110" t="n">
         <v>3</v>
@@ -18237,7 +18237,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE114" t="n">
         <v>3</v>
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE115" t="n">
         <v>4</v>
@@ -19002,7 +19002,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE116" t="n">
         <v>4</v>
@@ -19152,7 +19152,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE117" t="n">
         <v>4</v>
@@ -19302,7 +19302,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE118" t="n">
         <v>4</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -19612,7 +19612,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>2.699936067656849e+21</v>
+        <v>8.099808202970546e+21</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -20550,7 +20550,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -20700,7 +20700,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20850,7 +20850,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE128" t="n">
         <v>4</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -21322,7 +21322,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>2.634160849556478e+21</v>
+        <v>7.902482548669433e+21</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -21794,7 +21794,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>2.628857505681841e+21</v>
+        <v>7.886572517045521e+21</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -21956,7 +21956,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>3.501407652302539e+21</v>
+        <v>1.050422295690762e+22</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -22104,7 +22104,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -22254,7 +22254,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE137" t="n">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE138" t="n">
         <v>1</v>
@@ -22574,7 +22574,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -23324,7 +23324,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -23474,7 +23474,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -23624,7 +23624,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23924,7 +23924,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -24074,7 +24074,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -24224,7 +24224,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -24374,7 +24374,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -24524,7 +24524,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -24674,7 +24674,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24974,7 +24974,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -25124,7 +25124,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -25424,7 +25424,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -25574,7 +25574,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -25724,7 +25724,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -26024,7 +26024,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -26324,7 +26324,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26774,7 +26774,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -27224,7 +27224,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -27374,7 +27374,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -27524,7 +27524,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -27674,7 +27674,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27824,7 +27824,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27974,7 +27974,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -28124,7 +28124,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -28424,7 +28424,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -28574,7 +28574,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -28724,7 +28724,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -29174,7 +29174,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -29324,7 +29324,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -29624,7 +29624,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29774,7 +29774,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29924,7 +29924,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -30074,7 +30074,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -30224,7 +30224,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -30374,7 +30374,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -30674,7 +30674,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30824,7 +30824,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30974,7 +30974,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -31124,7 +31124,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -31274,7 +31274,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -31424,7 +31424,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -31574,7 +31574,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -31724,7 +31724,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31874,7 +31874,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -32024,7 +32024,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -32174,7 +32174,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -32324,7 +32324,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -32624,7 +32624,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32774,7 +32774,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32924,7 +32924,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -33074,7 +33074,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE209" t="n">
         <v>1</v>
@@ -33224,7 +33224,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -33374,7 +33374,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -33524,7 +33524,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -33674,7 +33674,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33824,7 +33824,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33974,7 +33974,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -34124,7 +34124,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -34574,7 +34574,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -34724,7 +34724,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34874,7 +34874,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -35024,7 +35024,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -35174,7 +35174,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -35324,7 +35324,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -35474,7 +35474,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -35624,7 +35624,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE227" t="n">
         <v>1</v>
@@ -35924,7 +35924,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -36074,7 +36074,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -36224,7 +36224,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -36374,7 +36374,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -36524,7 +36524,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -36674,7 +36674,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36824,7 +36824,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36974,7 +36974,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -37124,7 +37124,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -37424,7 +37424,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -37574,7 +37574,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -37724,7 +37724,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37874,7 +37874,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -38024,7 +38024,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -38174,7 +38174,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -38474,7 +38474,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -38624,7 +38624,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38774,7 +38774,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38924,7 +38924,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -39074,7 +39074,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -39224,7 +39224,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -39374,7 +39374,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -39524,7 +39524,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39974,7 +39974,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -40124,7 +40124,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -40274,7 +40274,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -40574,7 +40574,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -40724,7 +40724,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -40874,7 +40874,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -41024,7 +41024,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -41174,7 +41174,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -41474,7 +41474,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -41624,7 +41624,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41774,7 +41774,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -41924,7 +41924,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -42074,7 +42074,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -42674,7 +42674,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42974,7 +42974,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -43124,7 +43124,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -43274,7 +43274,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -43424,7 +43424,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43874,7 +43874,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -44024,7 +44024,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -44324,7 +44324,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44774,7 +44774,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -45074,7 +45074,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -45224,7 +45224,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -45374,7 +45374,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -45524,7 +45524,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -45674,7 +45674,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -45824,7 +45824,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -45974,7 +45974,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -46124,7 +46124,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -46274,7 +46274,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -46424,7 +46424,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -46574,7 +46574,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -46874,7 +46874,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -47024,7 +47024,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -47174,7 +47174,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -47324,7 +47324,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -47474,7 +47474,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -47624,7 +47624,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -47774,7 +47774,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -47924,7 +47924,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -48074,7 +48074,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -48224,7 +48224,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -48374,7 +48374,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -48524,7 +48524,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -48674,7 +48674,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -48974,7 +48974,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -49124,7 +49124,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -49274,7 +49274,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -49424,7 +49424,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE318" t="n">
         <v>3</v>
@@ -49574,7 +49574,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -49724,7 +49724,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -49874,7 +49874,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -50024,7 +50024,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE322" t="n">
         <v>3</v>
@@ -50174,7 +50174,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -50324,7 +50324,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -50474,7 +50474,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -50624,7 +50624,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -50774,7 +50774,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -50924,7 +50924,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -51074,7 +51074,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE329" t="n">
         <v>229</v>
@@ -51224,7 +51224,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -51374,7 +51374,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -51524,7 +51524,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -51674,7 +51674,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -51824,7 +51824,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51974,7 +51974,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -52124,7 +52124,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -52274,7 +52274,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -52574,7 +52574,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -52724,7 +52724,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -52874,7 +52874,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -53024,7 +53024,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -53174,7 +53174,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -53324,7 +53324,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -53474,7 +53474,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -53774,7 +53774,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>2.845193906689915e+21</v>
+        <v>8.535581720069746e+21</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -54096,7 +54096,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>2.845193906689915e+21</v>
+        <v>8.535581720069746e+21</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -54258,7 +54258,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -54420,7 +54420,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>2.844893717419321e+21</v>
+        <v>8.534681152257964e+21</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54572,7 +54572,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54732,7 +54732,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>3.306885004863485e+21</v>
+        <v>9.920655014590455e+21</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54888,7 +54888,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>3.28260302830877e+21</v>
+        <v>9.847809084926311e+21</v>
       </c>
       <c r="AE354" t="n">
         <v>2</v>
@@ -55048,7 +55048,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -55208,7 +55208,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>2.626956306968079e+21</v>
+        <v>7.880868920904236e+21</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -55370,7 +55370,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>2.626956306968079e+21</v>
+        <v>7.880868920904236e+21</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -55522,7 +55522,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -55672,7 +55672,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -55822,7 +55822,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -55972,7 +55972,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -56122,7 +56122,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -56272,7 +56272,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE363" t="n">
         <v>2</v>
@@ -56422,7 +56422,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -56572,7 +56572,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -56872,7 +56872,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -57022,7 +57022,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -57172,7 +57172,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -57322,7 +57322,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE370" t="n">
         <v>2</v>
@@ -57472,7 +57472,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -57622,7 +57622,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -57772,7 +57772,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -57922,7 +57922,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE374" t="n">
         <v>2</v>
@@ -58072,7 +58072,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE375" t="n">
         <v>2</v>
@@ -58222,7 +58222,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -58372,7 +58372,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -58522,7 +58522,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -58682,7 +58682,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -58832,7 +58832,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -59140,7 +59140,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -59449,7 +59449,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -59599,7 +59599,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -59757,7 +59757,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -59907,7 +59907,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE387" t="n">
         <v>2</v>
@@ -60057,7 +60057,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -60215,7 +60215,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -60365,7 +60365,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -60521,7 +60521,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>3.28260302830877e+21</v>
+        <v>9.847809084926311e+21</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -60679,7 +60679,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -60829,7 +60829,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -60975,7 +60975,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -61125,7 +61125,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -61275,7 +61275,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -61425,7 +61425,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -61575,7 +61575,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -61721,7 +61721,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -61879,7 +61879,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -62029,7 +62029,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -62189,7 +62189,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>3.282603440091035e+21</v>
+        <v>9.847810320273104e+21</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -62349,7 +62349,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>2.845193906689915e+21</v>
+        <v>8.535581720069746e+21</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -62502,7 +62502,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -62662,7 +62662,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>3.285305145220957e+21</v>
+        <v>9.855915435662873e+21</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -62822,7 +62822,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>3.285305145220957e+21</v>
+        <v>9.855915435662873e+21</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -62982,7 +62982,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>3.285305145220957e+21</v>
+        <v>9.855915435662873e+21</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -63132,7 +63132,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -63292,7 +63292,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>3.306885004863485e+21</v>
+        <v>9.920655014590455e+21</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -63450,7 +63450,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -63766,7 +63766,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -63916,7 +63916,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -64074,7 +64074,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -64224,7 +64224,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -64374,7 +64374,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE416" t="n">
         <v>2</v>
@@ -64532,7 +64532,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -64682,7 +64682,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -64832,7 +64832,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE419" t="n">
         <v>2</v>
@@ -64990,7 +64990,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -65150,7 +65150,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE421" t="n">
         <v>4</v>
@@ -65300,7 +65300,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -65454,7 +65454,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -65604,7 +65604,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE424" t="n">
         <v>2</v>
@@ -65762,7 +65762,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -65920,7 +65920,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>
@@ -66070,7 +66070,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -66220,7 +66220,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE428" t="n">
         <v>1</v>
@@ -66380,7 +66380,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -66540,7 +66540,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE430" t="n">
         <v>1</v>
@@ -66700,7 +66700,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -66858,7 +66858,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -67019,7 +67019,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -67169,7 +67169,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -67315,7 +67315,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -67465,7 +67465,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -67615,7 +67615,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -67765,7 +67765,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -67915,7 +67915,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -68073,7 +68073,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -68233,7 +68233,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -68393,7 +68393,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>

--- a/output/contacts.xlsx
+++ b/output/contacts.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>8.537484159496593e+21</v>
+        <v>2.561245247848978e+22</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.05285382875433e+22</v>
+        <v>3.15856148626299e+22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>8.54288756637064e+21</v>
+        <v>2.562866269911192e+22</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>8.542786262564002e+21</v>
+        <v>2.562835878769201e+22</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.053214055879043e+22</v>
+        <v>3.159642167637128e+22</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1772199</v>
+        <v>5316597</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>8.542887566370655e+21</v>
+        <v>2.562866269911196e+22</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>8.542887566370655e+21</v>
+        <v>2.562866269911196e+22</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>8.542786262564002e+21</v>
+        <v>2.562835878769201e+22</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>8.537484159496591e+21</v>
+        <v>2.561245247848977e+22</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.184156615712145e+22</v>
+        <v>3.552469847136435e+22</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.05285382875433e+22</v>
+        <v>3.15856148626299e+22</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>7.880970224710876e+21</v>
+        <v>2.364291067413263e+22</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>7.880970224707518e+21</v>
+        <v>2.364291067412256e+22</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>8.537484159499963e+21</v>
+        <v>2.561245247849989e+22</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>8.53738285569331e+21</v>
+        <v>2.561214856707993e+22</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>8.53738285569331e+21</v>
+        <v>2.561214856707993e+22</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>8.53738285569331e+21</v>
+        <v>2.561214856707993e+22</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>9.857014889224526e+21</v>
+        <v>2.957104466767358e+22</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>8.537484159496591e+21</v>
+        <v>2.561245247848977e+22</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.184246672493323e+22</v>
+        <v>3.552740017479969e+22</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE59" t="n">
         <v>7</v>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>7.90348442000198e+21</v>
+        <v>2.371045326000594e+22</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>7.903383116198786e+21</v>
+        <v>2.371014934859636e+22</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>7.903383116198786e+21</v>
+        <v>2.371014934859636e+22</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>7.902482548387003e+21</v>
+        <v>2.370744764516101e+22</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>7.880970224707518e+21</v>
+        <v>2.364291067412256e+22</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>7.886272327774928e+21</v>
+        <v>2.365881698332478e+22</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>7.886572517045521e+21</v>
+        <v>2.365971755113657e+22</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11480,7 +11480,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE69" t="n">
         <v>17</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11947,7 +11947,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12414,7 +12414,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE76" t="n">
         <v>3</v>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE77" t="n">
         <v>3</v>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -14120,7 +14120,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>7.886373631581571e+21</v>
+        <v>2.365912089474472e+22</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>9.855914195232349e+21</v>
+        <v>2.956774258569704e+22</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE95" t="n">
         <v>4</v>
@@ -15856,7 +15856,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>8.098007067158577e+21</v>
+        <v>2.429402120147573e+22</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE97" t="n">
         <v>9</v>
@@ -16177,7 +16177,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -16520,7 +16520,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.247376476099241e+22</v>
+        <v>3.742129428297723e+22</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.050422295662519e+22</v>
+        <v>3.151266886987556e+22</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -17333,7 +17333,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE105" t="n">
         <v>7</v>
@@ -17483,7 +17483,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE106" t="n">
         <v>11</v>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -18087,7 +18087,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE110" t="n">
         <v>3</v>
@@ -18237,7 +18237,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE114" t="n">
         <v>3</v>
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE115" t="n">
         <v>4</v>
@@ -19002,7 +19002,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE116" t="n">
         <v>4</v>
@@ -19152,7 +19152,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE117" t="n">
         <v>4</v>
@@ -19302,7 +19302,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE118" t="n">
         <v>4</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -19612,7 +19612,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>8.099808202970546e+21</v>
+        <v>2.429942460891164e+22</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -20550,7 +20550,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -20700,7 +20700,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20850,7 +20850,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE128" t="n">
         <v>4</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>8.09970689916726e+21</v>
+        <v>2.429912069750178e+22</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -21322,7 +21322,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>7.902482548669433e+21</v>
+        <v>2.37074476460083e+22</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -21794,7 +21794,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>7.886572517045521e+21</v>
+        <v>2.365971755113657e+22</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -21956,7 +21956,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.050422295690762e+22</v>
+        <v>3.151266887072285e+22</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -22104,7 +22104,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -22254,7 +22254,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE137" t="n">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1653615</v>
+        <v>4960845</v>
       </c>
       <c r="AE138" t="n">
         <v>1</v>
@@ -22574,7 +22574,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -23324,7 +23324,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -23474,7 +23474,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -23624,7 +23624,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23924,7 +23924,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -24074,7 +24074,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -24224,7 +24224,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -24374,7 +24374,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -24524,7 +24524,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -24674,7 +24674,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24974,7 +24974,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -25124,7 +25124,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -25424,7 +25424,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -25574,7 +25574,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -25724,7 +25724,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -26024,7 +26024,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -26324,7 +26324,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26774,7 +26774,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -27224,7 +27224,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -27374,7 +27374,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -27524,7 +27524,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -27674,7 +27674,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27824,7 +27824,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27974,7 +27974,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -28124,7 +28124,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -28424,7 +28424,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -28574,7 +28574,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -28724,7 +28724,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -29174,7 +29174,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -29324,7 +29324,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -29624,7 +29624,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29774,7 +29774,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29924,7 +29924,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -30074,7 +30074,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -30224,7 +30224,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -30374,7 +30374,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -30674,7 +30674,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30824,7 +30824,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30974,7 +30974,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -31124,7 +31124,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -31274,7 +31274,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -31424,7 +31424,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -31574,7 +31574,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -31724,7 +31724,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31874,7 +31874,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -32024,7 +32024,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -32174,7 +32174,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -32324,7 +32324,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -32624,7 +32624,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32774,7 +32774,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32924,7 +32924,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -33074,7 +33074,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE209" t="n">
         <v>1</v>
@@ -33224,7 +33224,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -33374,7 +33374,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -33524,7 +33524,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -33674,7 +33674,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33824,7 +33824,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33974,7 +33974,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -34124,7 +34124,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -34574,7 +34574,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -34724,7 +34724,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34874,7 +34874,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -35024,7 +35024,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -35174,7 +35174,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -35324,7 +35324,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -35474,7 +35474,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -35624,7 +35624,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE227" t="n">
         <v>1</v>
@@ -35924,7 +35924,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -36074,7 +36074,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -36224,7 +36224,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -36374,7 +36374,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -36524,7 +36524,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -36674,7 +36674,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36824,7 +36824,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36974,7 +36974,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -37124,7 +37124,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -37424,7 +37424,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -37574,7 +37574,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -37724,7 +37724,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37874,7 +37874,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -38024,7 +38024,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -38174,7 +38174,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -38474,7 +38474,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -38624,7 +38624,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38774,7 +38774,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38924,7 +38924,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -39074,7 +39074,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -39224,7 +39224,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -39374,7 +39374,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -39524,7 +39524,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39974,7 +39974,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -40124,7 +40124,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -40274,7 +40274,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -40574,7 +40574,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -40724,7 +40724,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -40874,7 +40874,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -41024,7 +41024,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -41174,7 +41174,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -41474,7 +41474,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -41624,7 +41624,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41774,7 +41774,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -41924,7 +41924,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -42074,7 +42074,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -42674,7 +42674,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42974,7 +42974,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -43124,7 +43124,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -43274,7 +43274,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -43424,7 +43424,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43874,7 +43874,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -44024,7 +44024,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -44324,7 +44324,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44774,7 +44774,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -45074,7 +45074,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -45224,7 +45224,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -45374,7 +45374,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -45524,7 +45524,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -45674,7 +45674,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -45824,7 +45824,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -45974,7 +45974,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -46124,7 +46124,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -46274,7 +46274,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -46424,7 +46424,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -46574,7 +46574,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -46874,7 +46874,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -47024,7 +47024,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -47174,7 +47174,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -47324,7 +47324,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -47474,7 +47474,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -47624,7 +47624,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -47774,7 +47774,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -47924,7 +47924,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -48074,7 +48074,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -48224,7 +48224,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -48374,7 +48374,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -48524,7 +48524,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -48674,7 +48674,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -48974,7 +48974,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -49124,7 +49124,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -49274,7 +49274,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -49424,7 +49424,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE318" t="n">
         <v>3</v>
@@ -49574,7 +49574,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -49724,7 +49724,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -49874,7 +49874,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -50024,7 +50024,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE322" t="n">
         <v>3</v>
@@ -50174,7 +50174,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -50324,7 +50324,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -50474,7 +50474,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -50624,7 +50624,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -50774,7 +50774,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -50924,7 +50924,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -51074,7 +51074,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE329" t="n">
         <v>229</v>
@@ -51224,7 +51224,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -51374,7 +51374,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -51524,7 +51524,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -51674,7 +51674,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -51824,7 +51824,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51974,7 +51974,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -52124,7 +52124,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -52274,7 +52274,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -52574,7 +52574,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -52724,7 +52724,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -52874,7 +52874,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -53024,7 +53024,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -53174,7 +53174,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -53324,7 +53324,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -53474,7 +53474,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -53624,7 +53624,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -53774,7 +53774,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>8.535581720069746e+21</v>
+        <v>2.560674516020924e+22</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -54096,7 +54096,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>8.535581720069746e+21</v>
+        <v>2.560674516020924e+22</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -54258,7 +54258,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -54420,7 +54420,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>8.534681152257964e+21</v>
+        <v>2.560404345677389e+22</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54572,7 +54572,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54732,7 +54732,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>9.920655014590455e+21</v>
+        <v>2.976196504377136e+22</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54888,7 +54888,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>9.847809084926311e+21</v>
+        <v>2.954342725477893e+22</v>
       </c>
       <c r="AE354" t="n">
         <v>2</v>
@@ -55048,7 +55048,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -55208,7 +55208,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>7.880868920904236e+21</v>
+        <v>2.364260676271271e+22</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -55370,7 +55370,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>7.880868920904236e+21</v>
+        <v>2.364260676271271e+22</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -55522,7 +55522,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -55672,7 +55672,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -55822,7 +55822,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -55972,7 +55972,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -56122,7 +56122,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -56272,7 +56272,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE363" t="n">
         <v>2</v>
@@ -56422,7 +56422,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -56572,7 +56572,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -56872,7 +56872,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -57022,7 +57022,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -57172,7 +57172,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -57322,7 +57322,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE370" t="n">
         <v>2</v>
@@ -57472,7 +57472,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -57622,7 +57622,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -57772,7 +57772,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -57922,7 +57922,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE374" t="n">
         <v>2</v>
@@ -58072,7 +58072,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE375" t="n">
         <v>2</v>
@@ -58222,7 +58222,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -58372,7 +58372,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -58522,7 +58522,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -58682,7 +58682,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -58832,7 +58832,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -59140,7 +59140,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -59449,7 +59449,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -59599,7 +59599,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -59757,7 +59757,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -59907,7 +59907,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE387" t="n">
         <v>2</v>
@@ -60057,7 +60057,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -60215,7 +60215,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -60365,7 +60365,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -60521,7 +60521,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>9.847809084926311e+21</v>
+        <v>2.954342725477893e+22</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -60679,7 +60679,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -60829,7 +60829,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -60975,7 +60975,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -61125,7 +61125,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -61275,7 +61275,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -61425,7 +61425,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -61575,7 +61575,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -61721,7 +61721,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -61879,7 +61879,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -62029,7 +62029,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -62189,7 +62189,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>9.847810320273104e+21</v>
+        <v>2.954343096081931e+22</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -62349,7 +62349,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>8.535581720069746e+21</v>
+        <v>2.560674516020924e+22</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -62502,7 +62502,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -62662,7 +62662,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>9.855915435662873e+21</v>
+        <v>2.956774630698862e+22</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -62822,7 +62822,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>9.855915435662873e+21</v>
+        <v>2.956774630698862e+22</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -62982,7 +62982,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>9.855915435662873e+21</v>
+        <v>2.956774630698862e+22</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -63132,7 +63132,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -63292,7 +63292,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>9.920655014590455e+21</v>
+        <v>2.976196504377136e+22</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -63450,7 +63450,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -63766,7 +63766,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -63916,7 +63916,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -64074,7 +64074,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -64224,7 +64224,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -64374,7 +64374,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE416" t="n">
         <v>2</v>
@@ -64532,7 +64532,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -64682,7 +64682,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -64832,7 +64832,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE419" t="n">
         <v>2</v>
@@ -64990,7 +64990,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -65150,7 +65150,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE421" t="n">
         <v>4</v>
@@ -65300,7 +65300,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -65454,7 +65454,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -65604,7 +65604,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE424" t="n">
         <v>2</v>
@@ -65762,7 +65762,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -65920,7 +65920,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>
@@ -66070,7 +66070,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -66220,7 +66220,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE428" t="n">
         <v>1</v>
@@ -66380,7 +66380,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -66540,7 +66540,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE430" t="n">
         <v>1</v>
@@ -66700,7 +66700,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -66858,7 +66858,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -67019,7 +67019,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -67169,7 +67169,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -67315,7 +67315,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -67465,7 +67465,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -67615,7 +67615,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -67765,7 +67765,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -67915,7 +67915,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>7.87816721746889e+21</v>
+        <v>2.363450165240667e+22</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -68073,7 +68073,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>9.847709021836113e+21</v>
+        <v>2.954312706550834e+22</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -68233,7 +68233,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -68393,7 +68393,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>9.855814132142151e+21</v>
+        <v>2.956744239642645e+22</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
